--- a/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\FLORES DE ESTRADA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EFF313-387A-4EA0-B578-70B1EB62047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DD6F64-20B1-4571-B8CA-919279834616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -135,15 +135,6 @@
     <t>SUELDO SRA. FERNANDA</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>AUMENTARON LOS HONORARIOS EN 0ct 2025</t>
-  </si>
-  <si>
-    <t>Renovacion anual de cable</t>
-  </si>
-  <si>
     <t>SAC</t>
   </si>
   <si>
@@ -169,6 +160,12 @@
   </si>
   <si>
     <t>Alterini Guido -Mes de DICIEMBRE - Jardineria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUMENTARON LOS HONORARIOS EN en3r0 </t>
+  </si>
+  <si>
+    <t>Pendiente articulos de limpieza de enero</t>
   </si>
 </sst>
 </file>
@@ -181,7 +178,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +263,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -463,7 +468,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -526,10 +531,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -557,6 +558,9 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -895,15 +899,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="24"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -913,7 +917,7 @@
       <c r="G1" s="25"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -927,7 +931,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -941,7 +945,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -955,7 +959,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -967,7 +971,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -977,7 +981,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
@@ -985,13 +989,13 @@
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
       <c r="E7" s="30" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F7" s="30"/>
       <c r="G7" s="31"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -1001,7 +1005,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="26"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>6</v>
       </c>
@@ -1015,7 +1019,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>8</v>
       </c>
@@ -1029,7 +1033,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1039,19 +1043,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>34</v>
       </c>
@@ -1066,22 +1070,22 @@
         <v>239800</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
       <c r="H14" s="40">
         <f>H13/2</f>
         <v>119900</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>9</v>
       </c>
@@ -1096,21 +1100,21 @@
         <v>359700</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="57" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" s="39"/>
       <c r="C17" s="39"/>
@@ -1118,11 +1122,11 @@
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="39"/>
-      <c r="H17" s="43">
-        <v>31461.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H17" s="59">
+        <v>31765.72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>11</v>
       </c>
@@ -1134,22 +1138,22 @@
       <c r="G18" s="41"/>
       <c r="H18" s="44">
         <f>SUM(H17:H17)</f>
-        <v>31461.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="57" t="s">
+        <v>31765.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
         <v>20</v>
       </c>
@@ -1163,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="39" t="s">
         <v>30</v>
       </c>
@@ -1175,7 +1179,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="43"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
         <v>9</v>
       </c>
@@ -1190,35 +1194,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="43">
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="59">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
@@ -1226,28 +1230,25 @@
       <c r="E25" s="48"/>
       <c r="F25" s="48"/>
       <c r="G25" s="48"/>
-      <c r="H25" s="43">
+      <c r="H25" s="59">
         <v>80000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="50" t="s">
-        <v>37</v>
-      </c>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
       <c r="D26" s="48"/>
       <c r="E26" s="48"/>
       <c r="F26" s="48"/>
       <c r="G26" s="48"/>
-      <c r="H26" s="43">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="s">
-        <v>35</v>
-      </c>
+      <c r="H26" s="43"/>
+      <c r="K26" s="61" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="49"/>
       <c r="B27" s="48"/>
       <c r="C27" s="48"/>
       <c r="D27" s="48"/>
@@ -1256,7 +1257,7 @@
       <c r="G27" s="48"/>
       <c r="H27" s="43"/>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>12</v>
       </c>
@@ -1268,22 +1269,22 @@
       <c r="G28" s="41"/>
       <c r="H28" s="44">
         <f>SUM(H24:H27)</f>
-        <v>350000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>13</v>
       </c>
@@ -1300,9 +1301,9 @@
       <c r="H30" s="39"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
@@ -1310,27 +1311,27 @@
       <c r="E31" s="41"/>
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
-      <c r="H31" s="51">
-        <v>156900</v>
+      <c r="H31" s="60">
+        <v>167800</v>
       </c>
       <c r="I31" s="20"/>
       <c r="K31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
         <v>27</v>
       </c>
@@ -1344,9 +1345,9 @@
         <v>99656</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" s="39"/>
       <c r="C34" s="39"/>
@@ -1358,7 +1359,7 @@
         <v>7486.06</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
         <v>24</v>
       </c>
@@ -1370,10 +1371,10 @@
       <c r="G35" s="36"/>
       <c r="H35" s="38">
         <f>H33+H31+H28+H22+H18+H15+H34</f>
-        <v>1005203.7400000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+        <v>816407.78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
         <v>32</v>
       </c>
@@ -1387,7 +1388,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
     </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
@@ -1399,46 +1400,46 @@
       <c r="G37" s="34"/>
       <c r="H37" s="35">
         <f>H35+H36</f>
-        <v>1005203.7400000001</v>
+        <v>816407.78</v>
       </c>
       <c r="I37" s="23"/>
     </row>
-    <row r="38" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="60" t="str">
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="58" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
       <c r="H38" s="33"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="53" t="s">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="53"/>
-      <c r="B40" s="53"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1448,18 +1449,18 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A42" s="54"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="56"/>
+    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="52"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="54"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>18</v>
       </c>
@@ -1470,10 +1471,10 @@
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
       <c r="H43" s="16">
-        <v>4653806.8540805168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>4790489.6140805166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>31</v>
       </c>
@@ -1484,10 +1485,10 @@
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="18">
-        <v>1141886.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>465293.924956</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>28</v>
       </c>
@@ -1500,9 +1501,9 @@
       <c r="H45" s="37"/>
       <c r="I45" s="19"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1512,12 +1513,12 @@
       <c r="G46" s="12"/>
       <c r="H46" s="13">
         <f>-( H35 )</f>
-        <v>-1005203.7400000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>-816407.78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -1527,7 +1528,7 @@
       <c r="G47" s="12"/>
       <c r="H47" s="13"/>
     </row>
-    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>17</v>
       </c>
@@ -1539,10 +1540,10 @@
       <c r="G48" s="15"/>
       <c r="H48" s="17">
         <f>SUM(H43:H47)</f>
-        <v>4790489.6140805166</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>4439375.7590365168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -1552,66 +1553,66 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="52" t="s">
+      <c r="B50" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="50"/>
+      <c r="E54" s="50"/>
+      <c r="F54" s="50"/>
+      <c r="G54" s="50"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
       <c r="H55" s="8"/>
     </row>
   </sheetData>

--- a/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
@@ -5,18 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DD6F64-20B1-4571-B8CA-919279834616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEB4485-3E9D-4D16-9D80-BEE28AD32E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilla" sheetId="2" r:id="rId2"/>
+    <sheet name="Edesur" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$M$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$63</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="139">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -129,9 +132,6 @@
     <t xml:space="preserve">PREVISION ORDINARIA </t>
   </si>
   <si>
-    <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
-  </si>
-  <si>
     <t>SUELDO SRA. FERNANDA</t>
   </si>
   <si>
@@ -166,19 +166,316 @@
   </si>
   <si>
     <t>Pendiente articulos de limpieza de enero</t>
+  </si>
+  <si>
+    <t>Estimados, buenos días / buenas tardes,
+A partir de las expensas emitidas desde diciembre de 2025, el consumo y pago de EDESUR deja de contabilizarse por separado y pasa a estar incluido dentro de los gastos ordinarios mensuales.
+De esta manera, el consorcio pasa a manejar una única caja, donde se reflejan todos los ingresos y egresos (EDESUR, seguros, AYSA, mantenimiento, sueldos, TSG, etc.), logrando mayor claridad y control.
+Desde ahora:
+ • El monto correspondiente a EDESUR figurará en el prorrateo de cada unidad.
+ • Estará incluido en el total a pagar.
+ • El pago mensual de EDESUR se verá reflejado dentro de la caja general de expensas.
+Esta unificación evita desbalances y cruces de fondos que se daban anteriormente.
+Quedamos a disposición por cualquier consulta.</t>
+  </si>
+  <si>
+    <t>Recupero deudores Edesur historicos - Leer cartel Naranja</t>
+  </si>
+  <si>
+    <t>TOTALES</t>
+  </si>
+  <si>
+    <t>PAWLAK, MARCOS</t>
+  </si>
+  <si>
+    <t>0-COCHO 8</t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>0-COCHO 7</t>
+  </si>
+  <si>
+    <t>NIEVA, PEDRO DANIEL</t>
+  </si>
+  <si>
+    <t>0-COCHO 6</t>
+  </si>
+  <si>
+    <t>ALCOLEAS, CRISTIAN</t>
+  </si>
+  <si>
+    <t>0-COCHO 5</t>
+  </si>
+  <si>
+    <t>BOSSIO, GERARDO</t>
+  </si>
+  <si>
+    <t>0-COCHO 4</t>
+  </si>
+  <si>
+    <t>BELON, SERGIO</t>
+  </si>
+  <si>
+    <t>0-COCHO 3</t>
+  </si>
+  <si>
+    <t>0-COCHO 2</t>
+  </si>
+  <si>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>BEARZOTTI, EDGARDO OSCAR</t>
+  </si>
+  <si>
+    <t>0-COCHO 1</t>
+  </si>
+  <si>
+    <t>Fausto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSQUERA FERNANDO </t>
+  </si>
+  <si>
+    <t>7-B</t>
+  </si>
+  <si>
+    <t>Raquel</t>
+  </si>
+  <si>
+    <t>STARK, CARLOS L. FRANCIS</t>
+  </si>
+  <si>
+    <t>7-A</t>
+  </si>
+  <si>
+    <t>SORIA, JUAN CRUZ</t>
+  </si>
+  <si>
+    <t>6-B</t>
+  </si>
+  <si>
+    <t>BRESCIA, MELODY ELIZABETH</t>
+  </si>
+  <si>
+    <t>6 -A</t>
+  </si>
+  <si>
+    <t>4-C</t>
+  </si>
+  <si>
+    <t>4-B</t>
+  </si>
+  <si>
+    <t>4 -A</t>
+  </si>
+  <si>
+    <t>Yoleidy</t>
+  </si>
+  <si>
+    <t>3-C</t>
+  </si>
+  <si>
+    <t>BALBIS, MARISA</t>
+  </si>
+  <si>
+    <t>3-B</t>
+  </si>
+  <si>
+    <t>Agustina</t>
+  </si>
+  <si>
+    <t>NIEVA, DANIELA ANTONELA</t>
+  </si>
+  <si>
+    <t>3-A</t>
+  </si>
+  <si>
+    <t>Romina</t>
+  </si>
+  <si>
+    <t>PUGLIESE, FRANCISCO</t>
+  </si>
+  <si>
+    <t>2-C</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>ALONSO,GUSTAVO OSAVALDO</t>
+  </si>
+  <si>
+    <t>2-B</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>2 -A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonella </t>
+  </si>
+  <si>
+    <t>1-C</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>1-B</t>
+  </si>
+  <si>
+    <t>NICOLAU, IGNACIO</t>
+  </si>
+  <si>
+    <t>1 -A</t>
+  </si>
+  <si>
+    <t>Total a Pagar</t>
+  </si>
+  <si>
+    <t>Gasto Extr.</t>
+  </si>
+  <si>
+    <t>Gasto Ordinario</t>
+  </si>
+  <si>
+    <t>Total con Mora</t>
+  </si>
+  <si>
+    <t>Interés por Mora 8,8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEUDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGOS </t>
+  </si>
+  <si>
+    <t>SALDO MES ANTERIOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% </t>
+  </si>
+  <si>
+    <t>INQUILINOS</t>
+  </si>
+  <si>
+    <t>PROPIETARIOS</t>
+  </si>
+  <si>
+    <t>PISO - DEPTO</t>
+  </si>
+  <si>
+    <t>U.F.</t>
+  </si>
+  <si>
+    <t>Gastos Extr.</t>
+  </si>
+  <si>
+    <t>Gastos Ord.</t>
+  </si>
+  <si>
+    <t>CUIT:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEL: </t>
+  </si>
+  <si>
+    <t>Localidad:</t>
+  </si>
+  <si>
+    <t>ADMINISTRADORA: CAROLINA CANCIANI</t>
+  </si>
+  <si>
+    <t>FLORES DE ESTRADA Nº 5065</t>
+  </si>
+  <si>
+    <t>Debido al incumplimiento por parte de EDESUR en el pago comprometido para los primeros días del mes, como se había acordado en años anteriores, y ante la necesidad de llegar a fin de mes sin contar con esos fondos en tiempo y forma, nos vimos en la obligación de solicitar un plan de pagos. Esta situación resalta la importancia de prever el gasto ordinario con mayor responsabilidad, a fin de evitar que este tipo de inconvenientes se repitan en el futuro. Se informa que quienes no abonen en tiempo y forma serán desconectados del servicio.</t>
+  </si>
+  <si>
+    <t>Señores propietarios e inquilinos; EDESUR vence en 10/08 por favor abonar facturas atrasadas. Debido al retraso de varias unidades funcionales, no se junta el monto para abonar dentro de la fecha estipulada la boleta, lo que trae intereses por mora. LA ADMINISTRACION.-</t>
+  </si>
+  <si>
+    <t>NOTA:</t>
+  </si>
+  <si>
+    <t>ALONSO,GUSTAVO OSVALDO</t>
+  </si>
+  <si>
+    <t>PRORRATEO FALTANTE</t>
+  </si>
+  <si>
+    <t>% CONSUMO REAL</t>
+  </si>
+  <si>
+    <t>EDESUR FINAL</t>
+  </si>
+  <si>
+    <t>KWH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDESUR </t>
+  </si>
+  <si>
+    <t>INTERES POR MORA 7%</t>
+  </si>
+  <si>
+    <t>DEUDA</t>
+  </si>
+  <si>
+    <t>CONSUMO ACTUAL</t>
+  </si>
+  <si>
+    <t>CONSUMO ANT.</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>B1824</t>
+  </si>
+  <si>
+    <t>C.P.:</t>
+  </si>
+  <si>
+    <t>0-000000-0</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>FLORES DE ESTRADA 5065</t>
+  </si>
+  <si>
+    <t>EDESUR - VENCIMIENTO 15/01</t>
+  </si>
+  <si>
+    <t>Edesur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="11">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,8 +568,128 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,8 +738,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B083"/>
+        <bgColor rgb="FFF4B083"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CC2E5"/>
+        <bgColor rgb="FF9CC2E5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -462,13 +915,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -493,7 +1056,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -531,9 +1093,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,14 +1120,203 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="21" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="21" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="21" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="21" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="28" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -632,6 +1383,99 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>91089</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3177891" cy="1210028"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BC26D6C-EBA6-43F4-8CEA-F50B5213DC54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3261009" y="249555"/>
+          <a:ext cx="3177891" cy="1210028"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>606425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1990725" cy="742950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image1.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E8D65B-61D5-4760-808A-50AB515074D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3578225" y="438785"/>
+          <a:ext cx="1990725" cy="742950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -898,30 +1742,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="8" t="s">
@@ -931,11 +1775,11 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="21"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="8">
@@ -945,25 +1789,25 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="21"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="22"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="26" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="8"/>
@@ -971,8 +1815,8 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="21"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -981,32 +1825,32 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="8"/>
@@ -1019,8 +1863,8 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -1033,7 +1877,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1043,403 +1887,403 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40">
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39">
         <f>218000+218000*10%</f>
         <v>239800</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="40">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="39">
         <f>H13/2</f>
         <v>119900</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41">
         <f>SUM(H13:H14)</f>
         <v>359700</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="59">
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="49">
         <v>31765.72</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44">
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="43">
         <f>SUM(H17:H17)</f>
         <v>31765.72</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="43"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="42"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="47">
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="46">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="59">
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="49">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="59">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="49">
         <v>80000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="49"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="43"/>
-      <c r="K26" s="61" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="43"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="48"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="42"/>
+      <c r="K26" s="51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="48"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="42"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44">
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="43">
         <f>SUM(H24:H27)</f>
         <v>150000</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="55" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="55"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39" t="s">
+      <c r="B30" s="38"/>
+      <c r="C30" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39" t="s">
+      <c r="D30" s="38"/>
+      <c r="E30" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="60">
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="19"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="50">
         <v>167800</v>
       </c>
-      <c r="I31" s="20"/>
+      <c r="I31" s="19"/>
       <c r="K31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="55"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="37">
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="36">
         <v>99656</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="37">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="36">
         <v>7486.06</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="38">
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="37">
         <f>H33+H31+H28+H22+H18+H15+H34</f>
         <v>816407.78</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="34" t="s">
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35">
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="34">
         <f>H35+H36</f>
         <v>816407.78</v>
       </c>
-      <c r="I37" s="23"/>
-    </row>
-    <row r="38" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="str">
+      <c r="I37" s="22"/>
+    </row>
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="59" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="33"/>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="51" t="s">
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="32"/>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+    </row>
+    <row r="40" spans="1:10" ht="0.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="52"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1449,177 +2293,258 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="52"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="199.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="60"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="60"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="60"/>
+      <c r="B46" s="60"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+    </row>
+    <row r="47" spans="1:10" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="60"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="60"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="60"/>
+      <c r="G48" s="60"/>
+      <c r="H48" s="60"/>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="60"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="60"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="60"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A53" s="53"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="55"/>
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A54" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="16">
-        <v>4790489.6140805166</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="16">
+        <v>4790489.6140805203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="18">
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="42">
+        <f>Planilla!G35</f>
         <v>465293.924956</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="19"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="13">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="18"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="36">
+        <v>-2892581.23</v>
+      </c>
+      <c r="I57" s="18"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="177">
+        <f>-Edesur!C8</f>
+        <v>-1030338.54</v>
+      </c>
+      <c r="I58" s="18"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="177">
         <f>-( H35 )</f>
         <v>-816407.78</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="13"/>
+    </row>
+    <row r="61" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A61" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="17">
-        <f>SUM(H43:H47)</f>
-        <v>4439375.7590365168</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="8"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="50"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="8"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50"/>
-      <c r="F54" s="50"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="8"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="50"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="8"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="17">
+        <f>SUM(H54:H60)</f>
+        <v>516455.98903652071</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B50:G55"/>
     <mergeCell ref="A39:H40"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
@@ -1629,6 +2554,7 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A43:H50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1637,4 +2563,7246 @@
   <pageSetup scale="95" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415D7022-5286-48BE-B3EA-F9F0CCFCF1F4}">
+  <dimension ref="A1:Q37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" style="62" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="61" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="61" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" style="61" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" customWidth="1"/>
+    <col min="11" max="12" width="12.109375" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="115" t="str">
+        <f>RESUMEN!E7</f>
+        <v>PERIODO: ENERO - Vto. 16/02</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="113"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="112"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="O2" s="99"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="I3" s="110" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="109"/>
+      <c r="O3" s="99"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="I4" s="105" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="108">
+        <v>1153202676</v>
+      </c>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="107"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="106"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="I5" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="104" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="99"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="101"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="O6" s="99"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="101"/>
+      <c r="B7" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="103">
+        <v>1005203.7400000001</v>
+      </c>
+      <c r="D7" s="102"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="O7" s="99"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="101"/>
+      <c r="B8" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="O8" s="99"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="98"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="93"/>
+    </row>
+    <row r="10" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="90" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="90"/>
+      <c r="J10" s="89" t="s">
+        <v>102</v>
+      </c>
+      <c r="K10" s="89" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="M10" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="N10" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="89" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="81">
+        <v>1</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="80"/>
+      <c r="E11" s="88">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F11" s="75">
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G11" s="78"/>
+      <c r="H11" s="77">
+        <f>F11-G11</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="I11" s="77"/>
+      <c r="J11" s="76">
+        <f>H11*8.8%</f>
+        <v>4334.4385268800015</v>
+      </c>
+      <c r="K11" s="74">
+        <f>H11+J11</f>
+        <v>53589.421786880019</v>
+      </c>
+      <c r="L11" s="74">
+        <f>Edesur!M10</f>
+        <v>64195.248493199993</v>
+      </c>
+      <c r="M11" s="75">
+        <f>C7*E11/100</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="N11" s="75">
+        <f>C8*E11/100</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="74">
+        <f>K11+M11+N11+L11</f>
+        <v>167039.65354008003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="81">
+        <v>2</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="79">
+        <v>3.89</v>
+      </c>
+      <c r="F12" s="75">
+        <v>1561877.6363181532</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="77">
+        <f>F12-G12</f>
+        <v>1561877.6363181532</v>
+      </c>
+      <c r="I12" s="75">
+        <v>0</v>
+      </c>
+      <c r="J12" s="76">
+        <f>H12*8.8%</f>
+        <v>137445.23199599748</v>
+      </c>
+      <c r="K12" s="74">
+        <f>H12+I12+J12</f>
+        <v>1699322.8683141507</v>
+      </c>
+      <c r="L12" s="74">
+        <f>Edesur!M11</f>
+        <v>30798.89364052</v>
+      </c>
+      <c r="M12" s="75">
+        <f>C7*E12/100</f>
+        <v>39102.425486</v>
+      </c>
+      <c r="N12" s="75">
+        <f>C8*E12/100</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="74">
+        <f t="shared" ref="O12:O34" si="0">K12+M12+N12+L12</f>
+        <v>1769224.1874406708</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="81">
+        <v>3</v>
+      </c>
+      <c r="B13" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="84">
+        <v>4</v>
+      </c>
+      <c r="F13" s="75">
+        <v>40208.149600000004</v>
+      </c>
+      <c r="G13" s="82">
+        <f>F13</f>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="H13" s="77">
+        <f>F13-G13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="75">
+        <v>0</v>
+      </c>
+      <c r="J13" s="76">
+        <f>H13*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="74">
+        <f>H13+I13+J13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="74">
+        <f>Edesur!M12</f>
+        <v>32890.853872</v>
+      </c>
+      <c r="M13" s="75">
+        <f>C7*E13/100</f>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="N13" s="75">
+        <f>C8*E13/100</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="74">
+        <f t="shared" si="0"/>
+        <v>73099.003472000011</v>
+      </c>
+      <c r="Q13" s="87"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="81">
+        <v>4</v>
+      </c>
+      <c r="B14" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="84">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F14" s="75">
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G14" s="82">
+        <f>F14</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="H14" s="77">
+        <f>F14-G14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="77">
+        <v>0</v>
+      </c>
+      <c r="J14" s="76">
+        <f>H14*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="74">
+        <f>H14+J14+I14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="74">
+        <f>Edesur!M13</f>
+        <v>68901.004493199725</v>
+      </c>
+      <c r="M14" s="75">
+        <f>C7*E14/100</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="N14" s="75">
+        <f>C8*E14/100</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="74">
+        <f t="shared" si="0"/>
+        <v>118155.98775319973</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="81">
+        <v>5</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="80" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="79">
+        <v>3.89</v>
+      </c>
+      <c r="F15" s="75">
+        <v>39102.425486</v>
+      </c>
+      <c r="G15" s="82">
+        <f>F15</f>
+        <v>39102.425486</v>
+      </c>
+      <c r="H15" s="77">
+        <f>F15-G15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="77">
+        <v>0</v>
+      </c>
+      <c r="J15" s="76">
+        <f>H15*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="74">
+        <f>H15+J15+I15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="74">
+        <f>Edesur!M14</f>
+        <v>63490.601640520035</v>
+      </c>
+      <c r="M15" s="75">
+        <f>C7*E15/100</f>
+        <v>39102.425486</v>
+      </c>
+      <c r="N15" s="75">
+        <f>C8*E15/100</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="74">
+        <f t="shared" si="0"/>
+        <v>102593.02712652003</v>
+      </c>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="81">
+        <v>6</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="84">
+        <v>4</v>
+      </c>
+      <c r="F16" s="75">
+        <v>188420.71699511315</v>
+      </c>
+      <c r="G16" s="82">
+        <f>40208-10450</f>
+        <v>29758</v>
+      </c>
+      <c r="H16" s="77">
+        <f>F16-G16</f>
+        <v>158662.71699511315</v>
+      </c>
+      <c r="I16" s="75">
+        <v>0</v>
+      </c>
+      <c r="J16" s="76">
+        <f>H16*8.8%</f>
+        <v>13962.319095569959</v>
+      </c>
+      <c r="K16" s="74">
+        <f>H16+J16+I16</f>
+        <v>172625.0360906831</v>
+      </c>
+      <c r="L16" s="74">
+        <f>Edesur!M15</f>
+        <v>50240.153871999995</v>
+      </c>
+      <c r="M16" s="75">
+        <f>C7*E16/100</f>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="N16" s="75">
+        <f>C8*E16/100</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="74">
+        <f t="shared" si="0"/>
+        <v>263073.33956268313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="81">
+        <v>7</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="84">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F17" s="75">
+        <v>49254.983260000015</v>
+      </c>
+      <c r="G17" s="82">
+        <f>F17</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="H17" s="77">
+        <f>F17-G17</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="75">
+        <v>0</v>
+      </c>
+      <c r="J17" s="76">
+        <f>H17*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="74">
+        <f>H17+I17+J17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="74">
+        <f>Edesur!M16</f>
+        <v>69285.502493199936</v>
+      </c>
+      <c r="M17" s="75">
+        <f>C7*E17/100</f>
+        <v>49254.983260000015</v>
+      </c>
+      <c r="N17" s="75">
+        <f>C8*E17/100</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="74">
+        <f t="shared" si="0"/>
+        <v>118540.48575319996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="81">
+        <v>8</v>
+      </c>
+      <c r="B18" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="80" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="80"/>
+      <c r="E18" s="79">
+        <v>3.89</v>
+      </c>
+      <c r="F18" s="75">
+        <v>39102.425486</v>
+      </c>
+      <c r="G18" s="82">
+        <f>F18</f>
+        <v>39102.425486</v>
+      </c>
+      <c r="H18" s="77">
+        <f>F18-G18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="75">
+        <v>0</v>
+      </c>
+      <c r="J18" s="76">
+        <f>H18*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="74">
+        <f>H18+J18+I18</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="74">
+        <f>Edesur!M17</f>
+        <v>34911.146640520034</v>
+      </c>
+      <c r="M18" s="75">
+        <f>C7*E18/100</f>
+        <v>39102.425486</v>
+      </c>
+      <c r="N18" s="75">
+        <f>C8*E18/100</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="74">
+        <f t="shared" si="0"/>
+        <v>74013.572126520041</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="81">
+        <v>9</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="84">
+        <v>4</v>
+      </c>
+      <c r="F19" s="75">
+        <v>40208.149600000004</v>
+      </c>
+      <c r="G19" s="82">
+        <f>F19</f>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="H19" s="77">
+        <f>F19-G19</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="75">
+        <v>0</v>
+      </c>
+      <c r="J19" s="76">
+        <f>H19*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="74">
+        <f>H19+J19</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="74">
+        <f>Edesur!M18</f>
+        <v>44519.573871999994</v>
+      </c>
+      <c r="M19" s="75">
+        <f>C7*E19/100</f>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="N19" s="75">
+        <f>C8*E19/100</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="74">
+        <f t="shared" si="0"/>
+        <v>84727.723471999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="81">
+        <v>10</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="80"/>
+      <c r="E20" s="79">
+        <v>12.66</v>
+      </c>
+      <c r="F20" s="75">
+        <v>127258.79348400002</v>
+      </c>
+      <c r="G20" s="78"/>
+      <c r="H20" s="77">
+        <f>F20-G20</f>
+        <v>127258.79348400002</v>
+      </c>
+      <c r="I20" s="75">
+        <v>0</v>
+      </c>
+      <c r="J20" s="76">
+        <f>H20*8.8%</f>
+        <v>11198.773826592003</v>
+      </c>
+      <c r="K20" s="74">
+        <f>H20+J20+I20</f>
+        <v>138457.56731059201</v>
+      </c>
+      <c r="L20" s="74">
+        <f>Edesur!M19</f>
+        <v>153451.45700487995</v>
+      </c>
+      <c r="M20" s="75">
+        <f>C7*E20/100</f>
+        <v>127258.79348400002</v>
+      </c>
+      <c r="N20" s="75">
+        <f>C8*E20/100</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="74">
+        <f t="shared" si="0"/>
+        <v>419167.81779947202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="81">
+        <v>11</v>
+      </c>
+      <c r="B21" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="79">
+        <v>7.75</v>
+      </c>
+      <c r="F21" s="75">
+        <v>77903.289850000016</v>
+      </c>
+      <c r="G21" s="78"/>
+      <c r="H21" s="77">
+        <f>F21-G21</f>
+        <v>77903.289850000016</v>
+      </c>
+      <c r="I21" s="75">
+        <v>0</v>
+      </c>
+      <c r="J21" s="76">
+        <f>H21*8.8%</f>
+        <v>6855.4895068000023</v>
+      </c>
+      <c r="K21" s="74">
+        <f>H21+J21+I21</f>
+        <v>84758.77935680002</v>
+      </c>
+      <c r="L21" s="74">
+        <f>Edesur!M20</f>
+        <v>67036.698126999996</v>
+      </c>
+      <c r="M21" s="75">
+        <f>C7*E21/100</f>
+        <v>77903.289850000016</v>
+      </c>
+      <c r="N21" s="75">
+        <f>C8*E21/100</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="74">
+        <f t="shared" si="0"/>
+        <v>229698.76733380003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="81">
+        <v>12</v>
+      </c>
+      <c r="B22" s="81" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="80"/>
+      <c r="E22" s="79">
+        <v>7.51</v>
+      </c>
+      <c r="F22" s="75">
+        <v>75490.800874000008</v>
+      </c>
+      <c r="G22" s="78"/>
+      <c r="H22" s="77">
+        <f>F22-G22</f>
+        <v>75490.800874000008</v>
+      </c>
+      <c r="I22" s="75">
+        <v>0</v>
+      </c>
+      <c r="J22" s="76">
+        <f>H22*8.8%</f>
+        <v>6643.190476912001</v>
+      </c>
+      <c r="K22" s="74">
+        <f>H22+J22+I22</f>
+        <v>82133.991350912009</v>
+      </c>
+      <c r="L22" s="74">
+        <f>Edesur!M21</f>
+        <v>49720.898894680089</v>
+      </c>
+      <c r="M22" s="75">
+        <f>C7*E22/100</f>
+        <v>75490.800874000008</v>
+      </c>
+      <c r="N22" s="75">
+        <f>C8*E22/100</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="74">
+        <f t="shared" si="0"/>
+        <v>207345.69111959211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="81">
+        <v>13</v>
+      </c>
+      <c r="B23" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="80"/>
+      <c r="E23" s="79">
+        <v>4.45</v>
+      </c>
+      <c r="F23" s="75">
+        <v>421314.26687926141</v>
+      </c>
+      <c r="G23" s="78"/>
+      <c r="H23" s="77">
+        <f>F23-G23</f>
+        <v>421314.26687926141</v>
+      </c>
+      <c r="I23" s="75">
+        <v>0</v>
+      </c>
+      <c r="J23" s="76">
+        <f>H23*8.8%</f>
+        <v>37075.655485375006</v>
+      </c>
+      <c r="K23" s="74">
+        <f>H23+J23+I23</f>
+        <v>458389.92236463644</v>
+      </c>
+      <c r="L23" s="74">
+        <f>Edesur!M22</f>
+        <v>55856.891182599997</v>
+      </c>
+      <c r="M23" s="75">
+        <f>C7*E23/100</f>
+        <v>44731.566430000013</v>
+      </c>
+      <c r="N23" s="75">
+        <f>C8*E23/100</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="74">
+        <f t="shared" si="0"/>
+        <v>558978.3799772365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="81">
+        <v>14</v>
+      </c>
+      <c r="B24" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="80"/>
+      <c r="E24" s="79">
+        <v>6.17</v>
+      </c>
+      <c r="F24" s="75">
+        <v>62021.070758000009</v>
+      </c>
+      <c r="G24" s="78"/>
+      <c r="H24" s="77">
+        <f>F24-G24</f>
+        <v>62021.070758000009</v>
+      </c>
+      <c r="I24" s="75">
+        <v>0</v>
+      </c>
+      <c r="J24" s="76">
+        <f>H24*8.8%</f>
+        <v>5457.8542267040011</v>
+      </c>
+      <c r="K24" s="74">
+        <f>H24+J24+I24</f>
+        <v>67478.924984704005</v>
+      </c>
+      <c r="L24" s="74">
+        <f>Edesur!M23</f>
+        <v>71775.721547560155</v>
+      </c>
+      <c r="M24" s="75">
+        <f>C7*E24/100</f>
+        <v>62021.070758000009</v>
+      </c>
+      <c r="N24" s="75">
+        <f>C8*E24/100</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="74">
+        <f t="shared" si="0"/>
+        <v>201275.71729026418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="81">
+        <v>15</v>
+      </c>
+      <c r="B25" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="79">
+        <v>4.45</v>
+      </c>
+      <c r="F25" s="75">
+        <v>653459.26182407467</v>
+      </c>
+      <c r="G25" s="82">
+        <v>62301</v>
+      </c>
+      <c r="H25" s="77">
+        <f>F25-G25</f>
+        <v>591158.26182407467</v>
+      </c>
+      <c r="I25" s="75">
+        <v>0</v>
+      </c>
+      <c r="J25" s="76">
+        <f>H25*8.8%</f>
+        <v>52021.927040518574</v>
+      </c>
+      <c r="K25" s="74">
+        <f>H25+J25+I25</f>
+        <v>643180.18886459328</v>
+      </c>
+      <c r="L25" s="74">
+        <f>Edesur!M24</f>
+        <v>44603.291182600005</v>
+      </c>
+      <c r="M25" s="75">
+        <f>C7*E25/100+1</f>
+        <v>44732.566430000013</v>
+      </c>
+      <c r="N25" s="75">
+        <f>C8*E25/100</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="74">
+        <f t="shared" si="0"/>
+        <v>732516.04647719325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="81">
+        <v>16</v>
+      </c>
+      <c r="B26" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="79">
+        <v>9.19</v>
+      </c>
+      <c r="F26" s="75">
+        <v>1871236.8809173489</v>
+      </c>
+      <c r="G26" s="82">
+        <v>92379</v>
+      </c>
+      <c r="H26" s="77">
+        <f>F26-G26</f>
+        <v>1778857.8809173489</v>
+      </c>
+      <c r="I26" s="75">
+        <v>0</v>
+      </c>
+      <c r="J26" s="76">
+        <f>H26*8.8%</f>
+        <v>156539.49352072671</v>
+      </c>
+      <c r="K26" s="74">
+        <f>H26+J26+I26</f>
+        <v>1935397.3744380756</v>
+      </c>
+      <c r="L26" s="74">
+        <f>Edesur!M25</f>
+        <v>69808.519520920119</v>
+      </c>
+      <c r="M26" s="75">
+        <f>C7*E26/100+1</f>
+        <v>92379.223706000004</v>
+      </c>
+      <c r="N26" s="75">
+        <f>C8*E26/100</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="74">
+        <f t="shared" si="0"/>
+        <v>2097585.1176649956</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="81">
+        <v>17</v>
+      </c>
+      <c r="B27" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F27" s="75">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G27" s="78"/>
+      <c r="H27" s="77">
+        <f>F27-G27</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="I27" s="75">
+        <v>0</v>
+      </c>
+      <c r="J27" s="76">
+        <f>H27*8.8%</f>
+        <v>1043.8915636160002</v>
+      </c>
+      <c r="K27" s="74">
+        <f>H27+J27+I27</f>
+        <v>12906.295695616001</v>
+      </c>
+      <c r="L27" s="74">
+        <f>Edesur!M26</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M27" s="75">
+        <f>C7*E27/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N27" s="75">
+        <f>C8*E27/100</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="74">
+        <f t="shared" si="0"/>
+        <v>32119.673219855998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="81">
+        <v>18</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="80"/>
+      <c r="E28" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F28" s="75">
+        <v>251938.50798349921</v>
+      </c>
+      <c r="G28" s="78"/>
+      <c r="H28" s="77">
+        <f>F28-G28</f>
+        <v>251938.50798349921</v>
+      </c>
+      <c r="I28" s="75">
+        <v>0</v>
+      </c>
+      <c r="J28" s="76">
+        <f>H28*8.8%</f>
+        <v>22170.588702547931</v>
+      </c>
+      <c r="K28" s="74">
+        <f>H28+J28+I28</f>
+        <v>274109.09668604715</v>
+      </c>
+      <c r="L28" s="74">
+        <f>Edesur!M27</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M28" s="75">
+        <f>C7*E28/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N28" s="75">
+        <f>C8*E28/100</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="74">
+        <f t="shared" si="0"/>
+        <v>293322.47421028715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="81">
+        <v>19</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="80"/>
+      <c r="E29" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F29" s="75">
+        <v>251938.50798349921</v>
+      </c>
+      <c r="G29" s="78"/>
+      <c r="H29" s="77">
+        <f>F29-G29</f>
+        <v>251938.50798349921</v>
+      </c>
+      <c r="I29" s="75">
+        <v>0</v>
+      </c>
+      <c r="J29" s="76">
+        <f>H29*8.8%</f>
+        <v>22170.588702547931</v>
+      </c>
+      <c r="K29" s="74">
+        <f>H29+J29+I29</f>
+        <v>274109.09668604715</v>
+      </c>
+      <c r="L29" s="74">
+        <f>Edesur!M28</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M29" s="75">
+        <f>C7*E29/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N29" s="75">
+        <f>C8*E29/100</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="74">
+        <f t="shared" si="0"/>
+        <v>293322.47421028715</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="81">
+        <v>20</v>
+      </c>
+      <c r="B30" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="80"/>
+      <c r="E30" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F30" s="75">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G30" s="82">
+        <f>F30</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="H30" s="83">
+        <f>F30-G30</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="75">
+        <v>0</v>
+      </c>
+      <c r="J30" s="76">
+        <f>H30*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="74">
+        <f>H30+J30+I30</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="74">
+        <f>Edesur!M29</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M30" s="75">
+        <f>C7*E30/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N30" s="75">
+        <f>C8*E30/100</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="74">
+        <f t="shared" si="0"/>
+        <v>19213.377524240001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="81">
+        <v>21</v>
+      </c>
+      <c r="B31" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F31" s="75">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G31" s="78"/>
+      <c r="H31" s="77">
+        <f>F31-G31</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="I31" s="75">
+        <v>0</v>
+      </c>
+      <c r="J31" s="76">
+        <f>H31*8.8%</f>
+        <v>1043.8915636160002</v>
+      </c>
+      <c r="K31" s="74">
+        <f>H31+J31+I31</f>
+        <v>12906.295695616001</v>
+      </c>
+      <c r="L31" s="74">
+        <f>Edesur!M30</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M31" s="75">
+        <f>C7*E31/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N31" s="75">
+        <f>C8*E31/100</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="74">
+        <f t="shared" si="0"/>
+        <v>32119.673219855998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="81">
+        <v>22</v>
+      </c>
+      <c r="B32" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="80"/>
+      <c r="E32" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F32" s="75">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G32" s="82">
+        <f>F32</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="H32" s="77">
+        <f>F32-G32</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="75">
+        <v>0</v>
+      </c>
+      <c r="J32" s="76">
+        <f>H32*8.8%</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="74">
+        <f>H32+J32+I32</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="74">
+        <f>Edesur!M31</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M32" s="75">
+        <f>C7*E32/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N32" s="75">
+        <f>C8*E32/100</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="74">
+        <f t="shared" si="0"/>
+        <v>19213.377524240001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="81">
+        <v>23</v>
+      </c>
+      <c r="B33" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="80"/>
+      <c r="E33" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F33" s="75">
+        <v>49393.886756</v>
+      </c>
+      <c r="G33" s="78"/>
+      <c r="H33" s="77">
+        <f>F33-G33</f>
+        <v>49393.886756</v>
+      </c>
+      <c r="I33" s="75">
+        <v>0</v>
+      </c>
+      <c r="J33" s="76">
+        <f>H33*8.8%</f>
+        <v>4346.6620345280007</v>
+      </c>
+      <c r="K33" s="74">
+        <f>H33+J33+I33</f>
+        <v>53740.548790528002</v>
+      </c>
+      <c r="L33" s="74">
+        <f>Edesur!M32</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M33" s="75">
+        <f>C7*E33/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N33" s="75">
+        <f>C8*E33/100</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="74">
+        <f t="shared" si="0"/>
+        <v>72953.926314768003</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="81">
+        <v>24</v>
+      </c>
+      <c r="B34" s="81" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="80"/>
+      <c r="E34" s="79">
+        <v>1.18</v>
+      </c>
+      <c r="F34" s="75">
+        <v>11862.404132000001</v>
+      </c>
+      <c r="G34" s="78"/>
+      <c r="H34" s="77">
+        <f>F34-G34</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="I34" s="75">
+        <v>0</v>
+      </c>
+      <c r="J34" s="76">
+        <f>H34*8.8%</f>
+        <v>1043.8915636160002</v>
+      </c>
+      <c r="K34" s="74">
+        <f>H34+J34+I34</f>
+        <v>12906.295695616001</v>
+      </c>
+      <c r="L34" s="74">
+        <f>Edesur!M33</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M34" s="75">
+        <f>C7*E34/100+1</f>
+        <v>11862.404132000001</v>
+      </c>
+      <c r="N34" s="75">
+        <f>C8*E34/100</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="74">
+        <f t="shared" si="0"/>
+        <v>32119.673219855998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="64" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A35" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="71">
+        <f>SUM(E11:E34)</f>
+        <v>99.990000000000066</v>
+      </c>
+      <c r="F35" s="70">
+        <f>SUM(F11:F34)</f>
+        <v>5957951.7412349507</v>
+      </c>
+      <c r="G35" s="69">
+        <f>SUM(G11:G34)</f>
+        <v>465293.924956</v>
+      </c>
+      <c r="H35" s="67">
+        <f>SUM(H11:H34)</f>
+        <v>5492657.8162789503</v>
+      </c>
+      <c r="I35" s="67">
+        <f>SUM(I12:I34)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="68">
+        <f>SUM(J11:J34)</f>
+        <v>483353.88783254754</v>
+      </c>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="67">
+        <f>SUM(M11:M34)</f>
+        <v>1005113.2196260006</v>
+      </c>
+      <c r="N35" s="66">
+        <f>SUM(N11:N34)</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="65">
+        <f>SUM(O11:O34)</f>
+        <v>8011419.167352818</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{0B4047C6-F122-41A7-B942-75A3A964FC5E}"/>
+  </hyperlinks>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" orientation="landscape" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582AEC43-F93A-440E-999B-59B587C24298}">
+  <dimension ref="A1:Y1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.6640625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="19" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="0.33203125" hidden="1" customWidth="1"/>
+    <col min="19" max="24" width="10.6640625" customWidth="1"/>
+    <col min="25" max="25" width="21.88671875" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="176" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+    </row>
+    <row r="2" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="173"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+    </row>
+    <row r="3" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="129" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
+    </row>
+    <row r="4" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="169" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="169" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="129" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="172"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="116"/>
+    </row>
+    <row r="5" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="129"/>
+      <c r="L5" s="129"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="129"/>
+      <c r="O5" s="116"/>
+    </row>
+    <row r="6" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="169" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="169" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="129" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="129"/>
+      <c r="O6" s="116"/>
+    </row>
+    <row r="7" spans="1:25" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="170" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="170" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="171">
+        <v>78050</v>
+      </c>
+      <c r="E7" s="166"/>
+      <c r="F7" s="166"/>
+      <c r="G7" s="166"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="166"/>
+      <c r="J7" s="166"/>
+      <c r="K7" s="166"/>
+      <c r="L7" s="166"/>
+      <c r="M7" s="165"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="116"/>
+    </row>
+    <row r="8" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="170"/>
+      <c r="B8" s="169" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="168">
+        <v>1030338.54</v>
+      </c>
+      <c r="E8" s="166"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="166"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="166"/>
+      <c r="K8" s="166"/>
+      <c r="L8" s="166"/>
+      <c r="M8" s="165"/>
+      <c r="N8" s="129"/>
+      <c r="O8" s="116"/>
+      <c r="S8" s="157"/>
+    </row>
+    <row r="9" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="164" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="164" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="160" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="164" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="160" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="163" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="162" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="163" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="160" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" s="160" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="162">
+        <f>C8-J34</f>
+        <v>622963.84679999994</v>
+      </c>
+      <c r="M9" s="160" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="161"/>
+      <c r="O9" s="160" t="s">
+        <v>123</v>
+      </c>
+      <c r="P9" s="160" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="141">
+        <v>1</v>
+      </c>
+      <c r="B10" s="141">
+        <v>1</v>
+      </c>
+      <c r="C10" s="141" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="141" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="141">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F10" s="141">
+        <v>20263.599999999999</v>
+      </c>
+      <c r="G10" s="147">
+        <v>20622.599999999999</v>
+      </c>
+      <c r="H10" s="140">
+        <v>0</v>
+      </c>
+      <c r="I10" s="130">
+        <f>H10*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="130">
+        <f>(G10-F10)*93.78</f>
+        <v>33667.019999999997</v>
+      </c>
+      <c r="K10" s="151">
+        <f>G10-F10</f>
+        <v>359</v>
+      </c>
+      <c r="L10" s="140">
+        <f>L9*E10/100</f>
+        <v>30525.2284932</v>
+      </c>
+      <c r="M10" s="140">
+        <f>J10+L10+3</f>
+        <v>64195.248493199993</v>
+      </c>
+      <c r="N10" s="132">
+        <f>J10/C7*100</f>
+        <v>43.135195387572068</v>
+      </c>
+      <c r="O10" s="131">
+        <f>J10/L9*100</f>
+        <v>5.4043296690391509</v>
+      </c>
+      <c r="P10" s="130">
+        <f>C7*O10/100</f>
+        <v>4218.0793066850574</v>
+      </c>
+      <c r="Q10" s="158">
+        <v>0.31</v>
+      </c>
+      <c r="R10" s="157">
+        <f>4000*Q10</f>
+        <v>1240</v>
+      </c>
+      <c r="V10" s="81" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="141">
+        <v>2</v>
+      </c>
+      <c r="B11" s="146">
+        <v>2</v>
+      </c>
+      <c r="C11" s="146" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="146" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="146">
+        <v>3.89</v>
+      </c>
+      <c r="F11" s="146">
+        <v>17353.900000000001</v>
+      </c>
+      <c r="G11" s="145">
+        <f>F11+70</f>
+        <v>17423.900000000001</v>
+      </c>
+      <c r="H11" s="143">
+        <v>0</v>
+      </c>
+      <c r="I11" s="144">
+        <f>H11*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="144">
+        <f>(G11-F11)*93.78</f>
+        <v>6564.6</v>
+      </c>
+      <c r="K11" s="159">
+        <f>G11-F11</f>
+        <v>70</v>
+      </c>
+      <c r="L11" s="143">
+        <f>L9*E11/100</f>
+        <v>24233.293640520002</v>
+      </c>
+      <c r="M11" s="143">
+        <f>J11+L11+1</f>
+        <v>30798.89364052</v>
+      </c>
+      <c r="N11" s="132" t="e">
+        <f>J11/C9*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O11" s="131">
+        <f>L11/L9*100</f>
+        <v>3.8900000000000006</v>
+      </c>
+      <c r="P11" s="130">
+        <f>C7*O11/100</f>
+        <v>3036.1450000000004</v>
+      </c>
+      <c r="Q11" s="158">
+        <v>0.19</v>
+      </c>
+      <c r="R11" s="157">
+        <f>4000*Q11</f>
+        <v>760</v>
+      </c>
+      <c r="U11" s="120"/>
+      <c r="V11" s="81" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="135">
+        <v>3</v>
+      </c>
+      <c r="B12" s="135">
+        <v>3</v>
+      </c>
+      <c r="C12" s="135" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="135" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="135">
+        <v>4</v>
+      </c>
+      <c r="F12" s="135">
+        <v>11841.3</v>
+      </c>
+      <c r="G12" s="147">
+        <f>F12+85</f>
+        <v>11926.3</v>
+      </c>
+      <c r="H12" s="133">
+        <v>0</v>
+      </c>
+      <c r="I12" s="134">
+        <f>H12*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="134">
+        <f>(G12-F12)*93.78</f>
+        <v>7971.3</v>
+      </c>
+      <c r="K12" s="148">
+        <f>G12-F12</f>
+        <v>85</v>
+      </c>
+      <c r="L12" s="133">
+        <f>L9*E12/100</f>
+        <v>24918.553871999997</v>
+      </c>
+      <c r="M12" s="133">
+        <f>J12+L12+1</f>
+        <v>32890.853872</v>
+      </c>
+      <c r="N12" s="132" t="e">
+        <f>J12/C10*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O12" s="131">
+        <f>J12/L9*100</f>
+        <v>1.2795766625858713</v>
+      </c>
+      <c r="P12" s="130">
+        <f>C7*O12/100</f>
+        <v>998.70958514827259</v>
+      </c>
+      <c r="V12" s="81" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="141">
+        <v>4</v>
+      </c>
+      <c r="B13" s="135">
+        <v>4</v>
+      </c>
+      <c r="C13" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="135">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F13" s="135">
+        <v>30278.400000000001</v>
+      </c>
+      <c r="G13" s="147">
+        <v>30687.599999999999</v>
+      </c>
+      <c r="H13" s="149">
+        <v>0</v>
+      </c>
+      <c r="I13" s="134">
+        <f>H13*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="134">
+        <f>(G13-F13)*93.78</f>
+        <v>38374.775999999729</v>
+      </c>
+      <c r="K13" s="148">
+        <f>G13-F13</f>
+        <v>409.19999999999709</v>
+      </c>
+      <c r="L13" s="133">
+        <f>L9*E13/100</f>
+        <v>30525.2284932</v>
+      </c>
+      <c r="M13" s="133">
+        <f>J13+L13+1</f>
+        <v>68901.004493199725</v>
+      </c>
+      <c r="N13" s="132" t="e">
+        <f>J13/C11*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O13" s="131">
+        <f>J13/L9*100</f>
+        <v>6.1600325921192338</v>
+      </c>
+      <c r="P13" s="130">
+        <f>C7*O13/100</f>
+        <v>4807.9054381490623</v>
+      </c>
+      <c r="V13" s="81" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="141">
+        <v>5</v>
+      </c>
+      <c r="B14" s="135">
+        <v>5</v>
+      </c>
+      <c r="C14" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="135" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="135">
+        <v>3.89</v>
+      </c>
+      <c r="F14" s="135">
+        <v>7623.9</v>
+      </c>
+      <c r="G14" s="147">
+        <v>8042.5</v>
+      </c>
+      <c r="H14" s="149">
+        <v>0</v>
+      </c>
+      <c r="I14" s="134">
+        <f>H14*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="134">
+        <f>(G14-F14)*93.78</f>
+        <v>39256.308000000034</v>
+      </c>
+      <c r="K14" s="148">
+        <f>G14-F14</f>
+        <v>418.60000000000036</v>
+      </c>
+      <c r="L14" s="133">
+        <f>L9*E14/100</f>
+        <v>24233.293640520002</v>
+      </c>
+      <c r="M14" s="133">
+        <f>J14+L14+1</f>
+        <v>63490.601640520035</v>
+      </c>
+      <c r="N14" s="132" t="e">
+        <f>J14/C12*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O14" s="131">
+        <f>J14/L9*100</f>
+        <v>6.3015387171581905</v>
+      </c>
+      <c r="P14" s="130">
+        <f>C7*O14/100</f>
+        <v>4918.3509687419682</v>
+      </c>
+      <c r="R14">
+        <v>2540.8200000000002</v>
+      </c>
+      <c r="V14" s="86" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="135">
+        <v>6</v>
+      </c>
+      <c r="B15" s="137">
+        <v>6</v>
+      </c>
+      <c r="C15" s="137" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="137" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="137">
+        <v>4</v>
+      </c>
+      <c r="F15" s="137">
+        <v>14706.7</v>
+      </c>
+      <c r="G15" s="156">
+        <f>F15+270</f>
+        <v>14976.7</v>
+      </c>
+      <c r="H15" s="138">
+        <v>0</v>
+      </c>
+      <c r="I15" s="139">
+        <f>H15*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="139">
+        <f>(G15-F15)*93.78</f>
+        <v>25320.6</v>
+      </c>
+      <c r="K15" s="155">
+        <f>G15-F15</f>
+        <v>270</v>
+      </c>
+      <c r="L15" s="138">
+        <f>L9*E15/100</f>
+        <v>24918.553871999997</v>
+      </c>
+      <c r="M15" s="138">
+        <f>J15+L15+1</f>
+        <v>50240.153871999995</v>
+      </c>
+      <c r="N15" s="154" t="e">
+        <f>J15/C13*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O15" s="153">
+        <f>J15/L9*100</f>
+        <v>4.0645376340962969</v>
+      </c>
+      <c r="P15" s="134">
+        <f>C7*O15/100</f>
+        <v>3172.3716234121598</v>
+      </c>
+      <c r="V15" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y15" s="152"/>
+    </row>
+    <row r="16" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="141">
+        <v>7</v>
+      </c>
+      <c r="B16" s="141">
+        <v>7</v>
+      </c>
+      <c r="C16" s="141" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="141" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="141">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F16" s="141">
+        <v>20071.5</v>
+      </c>
+      <c r="G16" s="147">
+        <v>20484.8</v>
+      </c>
+      <c r="H16" s="140">
+        <v>0</v>
+      </c>
+      <c r="I16" s="130">
+        <f>H16*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="130">
+        <f>(G16-F16)*93.78</f>
+        <v>38759.273999999932</v>
+      </c>
+      <c r="K16" s="151">
+        <f>G16-F16</f>
+        <v>413.29999999999927</v>
+      </c>
+      <c r="L16" s="140">
+        <f>L9*E16/100</f>
+        <v>30525.2284932</v>
+      </c>
+      <c r="M16" s="140">
+        <f>J16+L16+1</f>
+        <v>69285.502493199936</v>
+      </c>
+      <c r="N16" s="132" t="e">
+        <f>J16/C14*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O16" s="131">
+        <f>J16/L9*100</f>
+        <v>6.2217533487851728</v>
+      </c>
+      <c r="P16" s="130">
+        <f>C7*O16/100</f>
+        <v>4856.0784887268273</v>
+      </c>
+      <c r="V16" s="81" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="141">
+        <v>8</v>
+      </c>
+      <c r="B17" s="141">
+        <v>8</v>
+      </c>
+      <c r="C17" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="141" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="141">
+        <v>3.89</v>
+      </c>
+      <c r="F17" s="141">
+        <v>6715.4</v>
+      </c>
+      <c r="G17" s="147">
+        <v>6829.25</v>
+      </c>
+      <c r="H17" s="149">
+        <v>0</v>
+      </c>
+      <c r="I17" s="130">
+        <f>H17*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="130">
+        <f>(G17-F17)*93.78</f>
+        <v>10676.853000000034</v>
+      </c>
+      <c r="K17" s="151">
+        <f>G17-F17</f>
+        <v>113.85000000000036</v>
+      </c>
+      <c r="L17" s="140">
+        <f>L9*E17/100</f>
+        <v>24233.293640520002</v>
+      </c>
+      <c r="M17" s="140">
+        <f>J17+L17+1</f>
+        <v>34911.146640520034</v>
+      </c>
+      <c r="N17" s="132" t="e">
+        <f>J17/C15*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O17" s="131">
+        <f>J17/L9*100</f>
+        <v>1.7138800357106108</v>
+      </c>
+      <c r="P17" s="130">
+        <f>C7*O17/100</f>
+        <v>1337.6833678721316</v>
+      </c>
+      <c r="V17" s="81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="141">
+        <v>9</v>
+      </c>
+      <c r="B18" s="135">
+        <v>9</v>
+      </c>
+      <c r="C18" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="135" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="135">
+        <v>4</v>
+      </c>
+      <c r="F18" s="135">
+        <v>22279.9</v>
+      </c>
+      <c r="G18" s="147">
+        <f>F18+209</f>
+        <v>22488.9</v>
+      </c>
+      <c r="H18" s="150">
+        <v>0</v>
+      </c>
+      <c r="I18" s="134">
+        <f>H18*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="134">
+        <f>(G18-F18)*93.78</f>
+        <v>19600.02</v>
+      </c>
+      <c r="K18" s="148">
+        <f>G18-F18</f>
+        <v>209</v>
+      </c>
+      <c r="L18" s="133">
+        <f>L9*E18/100</f>
+        <v>24918.553871999997</v>
+      </c>
+      <c r="M18" s="133">
+        <f>J18+L18+1</f>
+        <v>44519.573871999994</v>
+      </c>
+      <c r="N18" s="132" t="e">
+        <f>J18/C16*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O18" s="131">
+        <f>J18/L9*100</f>
+        <v>3.1462532056523189</v>
+      </c>
+      <c r="P18" s="130">
+        <f>C7*O18/100</f>
+        <v>2455.6506270116352</v>
+      </c>
+      <c r="V18" s="81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="141">
+        <v>10</v>
+      </c>
+      <c r="B19" s="135">
+        <v>10</v>
+      </c>
+      <c r="C19" s="135" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="135" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="135">
+        <v>12.66</v>
+      </c>
+      <c r="F19" s="135">
+        <v>24404.2</v>
+      </c>
+      <c r="G19" s="147">
+        <v>25199.5</v>
+      </c>
+      <c r="H19" s="133">
+        <v>0</v>
+      </c>
+      <c r="I19" s="134">
+        <f>H19*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="134">
+        <f>(G19-F19)*93.78</f>
+        <v>74583.233999999939</v>
+      </c>
+      <c r="K19" s="148">
+        <f>G19-F19</f>
+        <v>795.29999999999927</v>
+      </c>
+      <c r="L19" s="133">
+        <f>L9*E19/100</f>
+        <v>78867.223004879997</v>
+      </c>
+      <c r="M19" s="133">
+        <f>J19+L19+1</f>
+        <v>153451.45700487995</v>
+      </c>
+      <c r="N19" s="132" t="e">
+        <f>J19/C17*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O19" s="131">
+        <f>J19/L9*100</f>
+        <v>11.972321408876972</v>
+      </c>
+      <c r="P19" s="130">
+        <f>C7*O19/100</f>
+        <v>9344.3968596284758</v>
+      </c>
+      <c r="V19" s="81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="135">
+        <v>11</v>
+      </c>
+      <c r="B20" s="135">
+        <v>11</v>
+      </c>
+      <c r="C20" s="135" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="135">
+        <v>7.75</v>
+      </c>
+      <c r="F20" s="135">
+        <v>18945.099999999999</v>
+      </c>
+      <c r="G20" s="147">
+        <f>F20+200</f>
+        <v>19145.099999999999</v>
+      </c>
+      <c r="H20" s="149">
+        <v>0</v>
+      </c>
+      <c r="I20" s="134">
+        <f>H20*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="134">
+        <f>(G20-F20)*93.78</f>
+        <v>18756</v>
+      </c>
+      <c r="K20" s="148">
+        <f>G20-F20</f>
+        <v>200</v>
+      </c>
+      <c r="L20" s="133">
+        <f>L9*E20/100</f>
+        <v>48279.698126999996</v>
+      </c>
+      <c r="M20" s="133">
+        <f>J20+L20+1</f>
+        <v>67036.698126999996</v>
+      </c>
+      <c r="N20" s="132" t="e">
+        <f>J20/C18*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O20" s="131">
+        <f>J20/L9*100</f>
+        <v>3.0107686178491093</v>
+      </c>
+      <c r="P20" s="130">
+        <f>C7*O20/100</f>
+        <v>2349.9049062312297</v>
+      </c>
+      <c r="V20" s="81" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="137">
+        <v>12</v>
+      </c>
+      <c r="B21" s="135">
+        <v>12</v>
+      </c>
+      <c r="C21" s="135" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="136" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="135">
+        <v>7.51</v>
+      </c>
+      <c r="F21" s="135">
+        <v>15306.9</v>
+      </c>
+      <c r="G21" s="147">
+        <v>15338.2</v>
+      </c>
+      <c r="H21" s="149">
+        <v>0</v>
+      </c>
+      <c r="I21" s="134">
+        <f>H21*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="134">
+        <f>(G21-F21)*93.78</f>
+        <v>2935.3140000001022</v>
+      </c>
+      <c r="K21" s="148">
+        <f>G21-F21</f>
+        <v>31.300000000001091</v>
+      </c>
+      <c r="L21" s="133">
+        <f>L9*E21/100</f>
+        <v>46784.584894679989</v>
+      </c>
+      <c r="M21" s="133">
+        <f>J21+L21+1</f>
+        <v>49720.898894680089</v>
+      </c>
+      <c r="N21" s="132" t="e">
+        <f>J21/C19*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O21" s="131">
+        <f>J21/L9*100</f>
+        <v>0.47118528869340198</v>
+      </c>
+      <c r="P21" s="130">
+        <f>C7*O21/100</f>
+        <v>367.76011782520021</v>
+      </c>
+      <c r="S21">
+        <f>G21-F21</f>
+        <v>31.300000000001091</v>
+      </c>
+      <c r="V21" s="81" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="135">
+        <v>13</v>
+      </c>
+      <c r="B22" s="135">
+        <v>13</v>
+      </c>
+      <c r="C22" s="135" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="135" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="135">
+        <v>4.45</v>
+      </c>
+      <c r="F22" s="135">
+        <v>12050.2</v>
+      </c>
+      <c r="G22" s="147">
+        <f>F22+300</f>
+        <v>12350.2</v>
+      </c>
+      <c r="H22" s="149">
+        <v>0</v>
+      </c>
+      <c r="I22" s="134">
+        <f>H22*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="134">
+        <f>(G22-F22)*93.78</f>
+        <v>28134</v>
+      </c>
+      <c r="K22" s="148">
+        <f>G22-F22</f>
+        <v>300</v>
+      </c>
+      <c r="L22" s="133">
+        <f>L9*E22/100</f>
+        <v>27721.8911826</v>
+      </c>
+      <c r="M22" s="133">
+        <f>J22+L22+1</f>
+        <v>55856.891182599997</v>
+      </c>
+      <c r="N22" s="132" t="e">
+        <f>J22/C20*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O22" s="131">
+        <f>J22/L9*100</f>
+        <v>4.516152926773664</v>
+      </c>
+      <c r="P22" s="130">
+        <f>C7*O22/100</f>
+        <v>3524.8573593468445</v>
+      </c>
+      <c r="S22">
+        <f>G22-F22</f>
+        <v>300</v>
+      </c>
+      <c r="V22" s="81" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="141">
+        <v>14</v>
+      </c>
+      <c r="B23" s="135">
+        <v>14</v>
+      </c>
+      <c r="C23" s="135" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="135" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="135">
+        <v>6.17</v>
+      </c>
+      <c r="F23" s="135">
+        <v>20587.3</v>
+      </c>
+      <c r="G23" s="147">
+        <v>20942.79</v>
+      </c>
+      <c r="H23" s="133">
+        <v>0</v>
+      </c>
+      <c r="I23" s="134">
+        <f>H23*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="134">
+        <f>(G23-F23)*93.78</f>
+        <v>33337.852200000154</v>
+      </c>
+      <c r="K23" s="148">
+        <f>G23-F23</f>
+        <v>355.4900000000016</v>
+      </c>
+      <c r="L23" s="133">
+        <f>L9*E23/100</f>
+        <v>38436.869347559994</v>
+      </c>
+      <c r="M23" s="133">
+        <f>J23+L23+1</f>
+        <v>71775.721547560155</v>
+      </c>
+      <c r="N23" s="132" t="e">
+        <f>J23/C21*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O23" s="131">
+        <f>J23/L9*100</f>
+        <v>5.3514906797959236</v>
+      </c>
+      <c r="P23" s="130">
+        <f>C7*O23/100</f>
+        <v>4176.8384755807183</v>
+      </c>
+      <c r="V23" s="81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="135">
+        <v>15</v>
+      </c>
+      <c r="B24" s="135">
+        <v>15</v>
+      </c>
+      <c r="C24" s="135" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="135" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="135">
+        <v>4.45</v>
+      </c>
+      <c r="F24" s="135">
+        <v>31465.9</v>
+      </c>
+      <c r="G24" s="147">
+        <f>F24+180</f>
+        <v>31645.9</v>
+      </c>
+      <c r="H24" s="133">
+        <v>0</v>
+      </c>
+      <c r="I24" s="134">
+        <f>H24*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="134">
+        <f>(G24-F24)*93.78</f>
+        <v>16880.400000000001</v>
+      </c>
+      <c r="K24" s="148">
+        <f>G24-F24</f>
+        <v>180</v>
+      </c>
+      <c r="L24" s="133">
+        <f>L9*E24/100</f>
+        <v>27721.8911826</v>
+      </c>
+      <c r="M24" s="133">
+        <f>J24+L24+1</f>
+        <v>44603.291182600005</v>
+      </c>
+      <c r="N24" s="132" t="e">
+        <f>J24/C22*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O24" s="131">
+        <f>J24/L9*100</f>
+        <v>2.7096917560641987</v>
+      </c>
+      <c r="P24" s="130">
+        <f>C7*O24/100</f>
+        <v>2114.914415608107</v>
+      </c>
+      <c r="V24" s="81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="135">
+        <v>16</v>
+      </c>
+      <c r="B25" s="135">
+        <v>16</v>
+      </c>
+      <c r="C25" s="135" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="135" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="135">
+        <v>9.19</v>
+      </c>
+      <c r="F25" s="135">
+        <v>12201.8</v>
+      </c>
+      <c r="G25" s="147">
+        <v>12335.7</v>
+      </c>
+      <c r="H25" s="133">
+        <v>0</v>
+      </c>
+      <c r="I25" s="134">
+        <f>H25*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="134">
+        <f>(G25-F25)*93.78</f>
+        <v>12557.142000000136</v>
+      </c>
+      <c r="K25" s="148">
+        <f>G25-F25</f>
+        <v>133.90000000000146</v>
+      </c>
+      <c r="L25" s="133">
+        <f>L9*E25/100</f>
+        <v>57250.377520919988</v>
+      </c>
+      <c r="M25" s="133">
+        <f>J25+L25+1</f>
+        <v>69808.519520920119</v>
+      </c>
+      <c r="N25" s="132" t="e">
+        <f>J25/C23*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O25" s="131">
+        <f>J25/L9*100</f>
+        <v>2.0157095896500006</v>
+      </c>
+      <c r="P25" s="130">
+        <f>C7*O25/100</f>
+        <v>1573.2613347218255</v>
+      </c>
+      <c r="V25" s="81" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="137">
+        <v>17</v>
+      </c>
+      <c r="B26" s="135">
+        <v>17</v>
+      </c>
+      <c r="C26" s="135" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="135">
+        <v>1.18</v>
+      </c>
+      <c r="F26" s="135">
+        <v>0</v>
+      </c>
+      <c r="G26" s="147">
+        <v>0</v>
+      </c>
+      <c r="H26" s="133">
+        <v>0</v>
+      </c>
+      <c r="I26" s="134">
+        <f>H26*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="134">
+        <f>(G26-F26)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133">
+        <f>L9*E26/100</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M26" s="133">
+        <f>J26+L26</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N26" s="132" t="e">
+        <f>J26/C24*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O26" s="131">
+        <f>J26/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="130">
+        <f>C7*O26/100</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="141">
+        <v>18</v>
+      </c>
+      <c r="B27" s="146">
+        <v>18</v>
+      </c>
+      <c r="C27" s="146" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="146" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="146">
+        <v>1.18</v>
+      </c>
+      <c r="F27" s="146">
+        <v>0</v>
+      </c>
+      <c r="G27" s="145">
+        <v>0</v>
+      </c>
+      <c r="H27" s="143">
+        <v>0</v>
+      </c>
+      <c r="I27" s="144">
+        <f>H27*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="144">
+        <f>(G27-F27)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="143"/>
+      <c r="L27" s="143">
+        <f>L26</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M27" s="143">
+        <f>J27+L27</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N27" s="132" t="e">
+        <f>J27/C25*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O27" s="131">
+        <f>J27/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="130">
+        <f>C7*O27/100</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="81" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="141">
+        <v>19</v>
+      </c>
+      <c r="B28" s="146">
+        <v>19</v>
+      </c>
+      <c r="C28" s="146" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="146" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="146">
+        <v>1.18</v>
+      </c>
+      <c r="F28" s="146">
+        <v>0</v>
+      </c>
+      <c r="G28" s="145">
+        <v>0</v>
+      </c>
+      <c r="H28" s="143">
+        <v>0</v>
+      </c>
+      <c r="I28" s="144">
+        <f>H28*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="144">
+        <f>(G28-F28)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="143"/>
+      <c r="L28" s="143">
+        <f>L27</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M28" s="143">
+        <f>J28+L28</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N28" s="132" t="e">
+        <f>J28/C26*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O28" s="131">
+        <f>J28/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="130">
+        <f>C7*O28/100</f>
+        <v>0</v>
+      </c>
+      <c r="V28" s="81" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="135">
+        <v>20</v>
+      </c>
+      <c r="B29" s="135">
+        <v>20</v>
+      </c>
+      <c r="C29" s="135" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="135" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="135">
+        <v>1.18</v>
+      </c>
+      <c r="F29" s="135">
+        <v>0</v>
+      </c>
+      <c r="G29" s="135">
+        <v>0</v>
+      </c>
+      <c r="H29" s="133">
+        <v>0</v>
+      </c>
+      <c r="I29" s="134">
+        <f>H29*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="134">
+        <f>(G29-F29)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133">
+        <f>L28</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M29" s="133">
+        <f>J29+L29</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N29" s="132" t="e">
+        <f>J29/C27*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O29" s="131">
+        <f>J29/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="130">
+        <f>C7*O29/100</f>
+        <v>0</v>
+      </c>
+      <c r="V29" s="81" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="141">
+        <v>21</v>
+      </c>
+      <c r="B30" s="141">
+        <v>21</v>
+      </c>
+      <c r="C30" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="141">
+        <v>1.18</v>
+      </c>
+      <c r="F30" s="141">
+        <v>0</v>
+      </c>
+      <c r="G30" s="141">
+        <v>0</v>
+      </c>
+      <c r="H30" s="140">
+        <v>0</v>
+      </c>
+      <c r="I30" s="130">
+        <f>H30*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="130">
+        <f>(G30-F30)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="140"/>
+      <c r="L30" s="140">
+        <f>L29</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M30" s="140">
+        <f>J30+L30</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N30" s="132" t="e">
+        <f>J30/C28*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O30" s="131">
+        <f>J30/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="130">
+        <f>C7*O30/100</f>
+        <v>0</v>
+      </c>
+      <c r="V30" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="141">
+        <v>22</v>
+      </c>
+      <c r="B31" s="141">
+        <v>22</v>
+      </c>
+      <c r="C31" s="141" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="141" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="141">
+        <v>1.18</v>
+      </c>
+      <c r="F31" s="141">
+        <v>0</v>
+      </c>
+      <c r="G31" s="141">
+        <v>0</v>
+      </c>
+      <c r="H31" s="140">
+        <v>0</v>
+      </c>
+      <c r="I31" s="130">
+        <f>H31*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="130">
+        <f>(G31-F31)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="140"/>
+      <c r="L31" s="140">
+        <f>L30</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M31" s="140">
+        <f>J31+L31</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N31" s="132" t="e">
+        <f>J31/C29*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O31" s="131">
+        <f>J31/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="130">
+        <f>C7*O31/100</f>
+        <v>0</v>
+      </c>
+      <c r="V31" s="81" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="137">
+        <v>23</v>
+      </c>
+      <c r="B32" s="137">
+        <v>23</v>
+      </c>
+      <c r="C32" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="137" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="137">
+        <v>1.18</v>
+      </c>
+      <c r="F32" s="137">
+        <v>0</v>
+      </c>
+      <c r="G32" s="137">
+        <v>0</v>
+      </c>
+      <c r="H32" s="138">
+        <v>0</v>
+      </c>
+      <c r="I32" s="139">
+        <f>H32*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="139">
+        <f>(G32-F32)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138">
+        <f>L31</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M32" s="138">
+        <f>J32+L32</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N32" s="132" t="e">
+        <f>J32/C30*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O32" s="131">
+        <f>J32/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="130">
+        <f>C7*O32/100</f>
+        <v>0</v>
+      </c>
+      <c r="V32" s="81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="137">
+        <v>24</v>
+      </c>
+      <c r="B33" s="135">
+        <v>24</v>
+      </c>
+      <c r="C33" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="136" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="135">
+        <v>1.18</v>
+      </c>
+      <c r="F33" s="135">
+        <v>0</v>
+      </c>
+      <c r="G33" s="135">
+        <v>0</v>
+      </c>
+      <c r="H33" s="133">
+        <v>0</v>
+      </c>
+      <c r="I33" s="134">
+        <f>H33*7%</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="134">
+        <f>(G33-F33)*93.78</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133">
+        <f>L32</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="M33" s="133">
+        <f>J33+L33</f>
+        <v>7350.9733922399992</v>
+      </c>
+      <c r="N33" s="132" t="e">
+        <f>J33/C31*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O33" s="131">
+        <f>J33/L9*100</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="130">
+        <f>C7*O33/100</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="81" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="129"/>
+      <c r="C34" s="128"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="125">
+        <f>SUM(H10:H33)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="126">
+        <f>SUM(I10:I33)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="126">
+        <f>SUM(J10:J33)</f>
+        <v>407374.69320000004</v>
+      </c>
+      <c r="K34" s="125">
+        <f>SUM(K10:K33)</f>
+        <v>4343.9400000000005</v>
+      </c>
+      <c r="L34" s="125">
+        <f>SUM(L10:L33)</f>
+        <v>622901.55041531997</v>
+      </c>
+      <c r="M34" s="125">
+        <f>SUM(M10:M33)</f>
+        <v>1030294.24361532</v>
+      </c>
+      <c r="N34" s="117"/>
+      <c r="O34" s="116" t="e">
+        <f>J34/C32*100</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="122" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="124" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="123"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="123"/>
+      <c r="K35" s="123"/>
+      <c r="L35" s="123"/>
+      <c r="M35" s="123"/>
+      <c r="N35" s="122"/>
+      <c r="O35" s="116" t="e">
+        <f>J35/C33*100</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H36" s="117"/>
+      <c r="J36" s="121"/>
+      <c r="L36" s="121"/>
+      <c r="M36" s="120"/>
+      <c r="O36" s="116"/>
+    </row>
+    <row r="37" spans="1:22" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="117"/>
+      <c r="K37" s="19">
+        <f>J34+L34</f>
+        <v>1030276.24361532</v>
+      </c>
+      <c r="L37" s="19"/>
+      <c r="O37" s="116"/>
+    </row>
+    <row r="38" spans="1:22" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="119" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
+      <c r="M38" s="118"/>
+      <c r="O38" s="116"/>
+    </row>
+    <row r="39" spans="1:22" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="118"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="118"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
+      <c r="M39" s="118"/>
+      <c r="O39" s="116"/>
+    </row>
+    <row r="40" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="118"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="O40" s="116"/>
+    </row>
+    <row r="41" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="118"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="118"/>
+      <c r="O41" s="116"/>
+    </row>
+    <row r="42" spans="1:22" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="118"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
+      <c r="M42" s="118"/>
+      <c r="O42" s="116"/>
+    </row>
+    <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H43" s="117"/>
+      <c r="O43" s="116"/>
+    </row>
+    <row r="44" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="117"/>
+      <c r="O44" s="116"/>
+    </row>
+    <row r="45" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="117"/>
+      <c r="O45" s="116"/>
+    </row>
+    <row r="46" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="117"/>
+      <c r="O46" s="116"/>
+    </row>
+    <row r="47" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="117"/>
+      <c r="O47" s="116"/>
+    </row>
+    <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="117"/>
+      <c r="O48" s="116"/>
+    </row>
+    <row r="49" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="117"/>
+      <c r="O49" s="116"/>
+    </row>
+    <row r="50" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="117"/>
+      <c r="O50" s="116"/>
+    </row>
+    <row r="51" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="117"/>
+      <c r="O51" s="116"/>
+    </row>
+    <row r="52" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="117"/>
+      <c r="O52" s="116"/>
+    </row>
+    <row r="53" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="117"/>
+      <c r="O53" s="116"/>
+    </row>
+    <row r="54" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="117"/>
+      <c r="O54" s="116"/>
+    </row>
+    <row r="55" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="117"/>
+      <c r="O55" s="116"/>
+    </row>
+    <row r="56" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="117"/>
+      <c r="O56" s="116"/>
+    </row>
+    <row r="57" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="117"/>
+      <c r="O57" s="116"/>
+    </row>
+    <row r="58" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="117"/>
+      <c r="O58" s="116"/>
+    </row>
+    <row r="59" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="117"/>
+      <c r="O59" s="116"/>
+    </row>
+    <row r="60" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="117"/>
+      <c r="O60" s="116"/>
+    </row>
+    <row r="61" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="117"/>
+      <c r="O61" s="116"/>
+    </row>
+    <row r="62" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="117"/>
+      <c r="O62" s="116"/>
+    </row>
+    <row r="63" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="117"/>
+      <c r="O63" s="116"/>
+    </row>
+    <row r="64" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="117"/>
+      <c r="O64" s="116"/>
+    </row>
+    <row r="65" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="117"/>
+      <c r="O65" s="116"/>
+    </row>
+    <row r="66" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="117"/>
+      <c r="O66" s="116"/>
+    </row>
+    <row r="67" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H67" s="117"/>
+      <c r="O67" s="116"/>
+    </row>
+    <row r="68" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H68" s="117"/>
+      <c r="O68" s="116"/>
+    </row>
+    <row r="69" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="117"/>
+      <c r="O69" s="116"/>
+    </row>
+    <row r="70" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="117"/>
+      <c r="O70" s="116"/>
+    </row>
+    <row r="71" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="117"/>
+      <c r="O71" s="116"/>
+    </row>
+    <row r="72" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="117"/>
+      <c r="O72" s="116"/>
+    </row>
+    <row r="73" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="117"/>
+      <c r="O73" s="116"/>
+    </row>
+    <row r="74" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H74" s="117"/>
+      <c r="O74" s="116"/>
+    </row>
+    <row r="75" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="117"/>
+      <c r="O75" s="116"/>
+    </row>
+    <row r="76" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H76" s="117"/>
+      <c r="O76" s="116"/>
+    </row>
+    <row r="77" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="117"/>
+      <c r="O77" s="116"/>
+    </row>
+    <row r="78" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="117"/>
+      <c r="O78" s="116"/>
+    </row>
+    <row r="79" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="117"/>
+      <c r="O79" s="116"/>
+    </row>
+    <row r="80" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H80" s="117"/>
+      <c r="O80" s="116"/>
+    </row>
+    <row r="81" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="117"/>
+      <c r="O81" s="116"/>
+    </row>
+    <row r="82" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H82" s="117"/>
+      <c r="O82" s="116"/>
+    </row>
+    <row r="83" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="117"/>
+      <c r="O83" s="116"/>
+    </row>
+    <row r="84" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="117"/>
+      <c r="O84" s="116"/>
+    </row>
+    <row r="85" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="117"/>
+      <c r="O85" s="116"/>
+    </row>
+    <row r="86" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="117"/>
+      <c r="O86" s="116"/>
+    </row>
+    <row r="87" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="117"/>
+      <c r="O87" s="116"/>
+    </row>
+    <row r="88" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H88" s="117"/>
+      <c r="O88" s="116"/>
+    </row>
+    <row r="89" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="117"/>
+      <c r="O89" s="116"/>
+    </row>
+    <row r="90" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="117"/>
+      <c r="O90" s="116"/>
+    </row>
+    <row r="91" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="117"/>
+      <c r="O91" s="116"/>
+    </row>
+    <row r="92" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="117"/>
+      <c r="O92" s="116"/>
+    </row>
+    <row r="93" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="117"/>
+      <c r="O93" s="116"/>
+    </row>
+    <row r="94" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H94" s="117"/>
+      <c r="O94" s="116"/>
+    </row>
+    <row r="95" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H95" s="117"/>
+      <c r="O95" s="116"/>
+    </row>
+    <row r="96" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="117"/>
+      <c r="O96" s="116"/>
+    </row>
+    <row r="97" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="117"/>
+      <c r="O97" s="116"/>
+    </row>
+    <row r="98" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="117"/>
+      <c r="O98" s="116"/>
+    </row>
+    <row r="99" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H99" s="117"/>
+      <c r="O99" s="116"/>
+    </row>
+    <row r="100" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H100" s="117"/>
+      <c r="O100" s="116"/>
+    </row>
+    <row r="101" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H101" s="117"/>
+      <c r="O101" s="116"/>
+    </row>
+    <row r="102" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H102" s="117"/>
+      <c r="O102" s="116"/>
+    </row>
+    <row r="103" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H103" s="117"/>
+      <c r="O103" s="116"/>
+    </row>
+    <row r="104" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H104" s="117"/>
+      <c r="O104" s="116"/>
+    </row>
+    <row r="105" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H105" s="117"/>
+      <c r="O105" s="116"/>
+    </row>
+    <row r="106" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H106" s="117"/>
+      <c r="O106" s="116"/>
+    </row>
+    <row r="107" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H107" s="117"/>
+      <c r="O107" s="116"/>
+    </row>
+    <row r="108" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H108" s="117"/>
+      <c r="O108" s="116"/>
+    </row>
+    <row r="109" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H109" s="117"/>
+      <c r="O109" s="116"/>
+    </row>
+    <row r="110" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="117"/>
+      <c r="O110" s="116"/>
+    </row>
+    <row r="111" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H111" s="117"/>
+      <c r="O111" s="116"/>
+    </row>
+    <row r="112" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H112" s="117"/>
+      <c r="O112" s="116"/>
+    </row>
+    <row r="113" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H113" s="117"/>
+      <c r="O113" s="116"/>
+    </row>
+    <row r="114" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H114" s="117"/>
+      <c r="O114" s="116"/>
+    </row>
+    <row r="115" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H115" s="117"/>
+      <c r="O115" s="116"/>
+    </row>
+    <row r="116" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H116" s="117"/>
+      <c r="O116" s="116"/>
+    </row>
+    <row r="117" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H117" s="117"/>
+      <c r="O117" s="116"/>
+    </row>
+    <row r="118" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H118" s="117"/>
+      <c r="O118" s="116"/>
+    </row>
+    <row r="119" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H119" s="117"/>
+      <c r="O119" s="116"/>
+    </row>
+    <row r="120" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H120" s="117"/>
+      <c r="O120" s="116"/>
+    </row>
+    <row r="121" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H121" s="117"/>
+      <c r="O121" s="116"/>
+    </row>
+    <row r="122" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H122" s="117"/>
+      <c r="O122" s="116"/>
+    </row>
+    <row r="123" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H123" s="117"/>
+      <c r="O123" s="116"/>
+    </row>
+    <row r="124" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H124" s="117"/>
+      <c r="O124" s="116"/>
+    </row>
+    <row r="125" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H125" s="117"/>
+      <c r="O125" s="116"/>
+    </row>
+    <row r="126" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H126" s="117"/>
+      <c r="O126" s="116"/>
+    </row>
+    <row r="127" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H127" s="117"/>
+      <c r="O127" s="116"/>
+    </row>
+    <row r="128" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H128" s="117"/>
+      <c r="O128" s="116"/>
+    </row>
+    <row r="129" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H129" s="117"/>
+      <c r="O129" s="116"/>
+    </row>
+    <row r="130" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H130" s="117"/>
+      <c r="O130" s="116"/>
+    </row>
+    <row r="131" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H131" s="117"/>
+      <c r="O131" s="116"/>
+    </row>
+    <row r="132" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H132" s="117"/>
+      <c r="O132" s="116"/>
+    </row>
+    <row r="133" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H133" s="117"/>
+      <c r="O133" s="116"/>
+    </row>
+    <row r="134" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="117"/>
+      <c r="O134" s="116"/>
+    </row>
+    <row r="135" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="117"/>
+      <c r="O135" s="116"/>
+    </row>
+    <row r="136" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H136" s="117"/>
+      <c r="O136" s="116"/>
+    </row>
+    <row r="137" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H137" s="117"/>
+      <c r="O137" s="116"/>
+    </row>
+    <row r="138" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H138" s="117"/>
+      <c r="O138" s="116"/>
+    </row>
+    <row r="139" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H139" s="117"/>
+      <c r="O139" s="116"/>
+    </row>
+    <row r="140" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H140" s="117"/>
+      <c r="O140" s="116"/>
+    </row>
+    <row r="141" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H141" s="117"/>
+      <c r="O141" s="116"/>
+    </row>
+    <row r="142" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H142" s="117"/>
+      <c r="O142" s="116"/>
+    </row>
+    <row r="143" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H143" s="117"/>
+      <c r="O143" s="116"/>
+    </row>
+    <row r="144" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H144" s="117"/>
+      <c r="O144" s="116"/>
+    </row>
+    <row r="145" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H145" s="117"/>
+      <c r="O145" s="116"/>
+    </row>
+    <row r="146" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H146" s="117"/>
+      <c r="O146" s="116"/>
+    </row>
+    <row r="147" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H147" s="117"/>
+      <c r="O147" s="116"/>
+    </row>
+    <row r="148" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H148" s="117"/>
+      <c r="O148" s="116"/>
+    </row>
+    <row r="149" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H149" s="117"/>
+      <c r="O149" s="116"/>
+    </row>
+    <row r="150" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H150" s="117"/>
+      <c r="O150" s="116"/>
+    </row>
+    <row r="151" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="117"/>
+      <c r="O151" s="116"/>
+    </row>
+    <row r="152" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H152" s="117"/>
+      <c r="O152" s="116"/>
+    </row>
+    <row r="153" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H153" s="117"/>
+      <c r="O153" s="116"/>
+    </row>
+    <row r="154" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H154" s="117"/>
+      <c r="O154" s="116"/>
+    </row>
+    <row r="155" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H155" s="117"/>
+      <c r="O155" s="116"/>
+    </row>
+    <row r="156" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H156" s="117"/>
+      <c r="O156" s="116"/>
+    </row>
+    <row r="157" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H157" s="117"/>
+      <c r="O157" s="116"/>
+    </row>
+    <row r="158" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H158" s="117"/>
+      <c r="O158" s="116"/>
+    </row>
+    <row r="159" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H159" s="117"/>
+      <c r="O159" s="116"/>
+    </row>
+    <row r="160" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H160" s="117"/>
+      <c r="O160" s="116"/>
+    </row>
+    <row r="161" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H161" s="117"/>
+      <c r="O161" s="116"/>
+    </row>
+    <row r="162" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H162" s="117"/>
+      <c r="O162" s="116"/>
+    </row>
+    <row r="163" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H163" s="117"/>
+      <c r="O163" s="116"/>
+    </row>
+    <row r="164" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H164" s="117"/>
+      <c r="O164" s="116"/>
+    </row>
+    <row r="165" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H165" s="117"/>
+      <c r="O165" s="116"/>
+    </row>
+    <row r="166" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H166" s="117"/>
+      <c r="O166" s="116"/>
+    </row>
+    <row r="167" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H167" s="117"/>
+      <c r="O167" s="116"/>
+    </row>
+    <row r="168" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H168" s="117"/>
+      <c r="O168" s="116"/>
+    </row>
+    <row r="169" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H169" s="117"/>
+      <c r="O169" s="116"/>
+    </row>
+    <row r="170" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H170" s="117"/>
+      <c r="O170" s="116"/>
+    </row>
+    <row r="171" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H171" s="117"/>
+      <c r="O171" s="116"/>
+    </row>
+    <row r="172" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H172" s="117"/>
+      <c r="O172" s="116"/>
+    </row>
+    <row r="173" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H173" s="117"/>
+      <c r="O173" s="116"/>
+    </row>
+    <row r="174" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H174" s="117"/>
+      <c r="O174" s="116"/>
+    </row>
+    <row r="175" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H175" s="117"/>
+      <c r="O175" s="116"/>
+    </row>
+    <row r="176" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H176" s="117"/>
+      <c r="O176" s="116"/>
+    </row>
+    <row r="177" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H177" s="117"/>
+      <c r="O177" s="116"/>
+    </row>
+    <row r="178" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H178" s="117"/>
+      <c r="O178" s="116"/>
+    </row>
+    <row r="179" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H179" s="117"/>
+      <c r="O179" s="116"/>
+    </row>
+    <row r="180" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H180" s="117"/>
+      <c r="O180" s="116"/>
+    </row>
+    <row r="181" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H181" s="117"/>
+      <c r="O181" s="116"/>
+    </row>
+    <row r="182" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H182" s="117"/>
+      <c r="O182" s="116"/>
+    </row>
+    <row r="183" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H183" s="117"/>
+      <c r="O183" s="116"/>
+    </row>
+    <row r="184" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H184" s="117"/>
+      <c r="O184" s="116"/>
+    </row>
+    <row r="185" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H185" s="117"/>
+      <c r="O185" s="116"/>
+    </row>
+    <row r="186" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H186" s="117"/>
+      <c r="O186" s="116"/>
+    </row>
+    <row r="187" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H187" s="117"/>
+      <c r="O187" s="116"/>
+    </row>
+    <row r="188" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H188" s="117"/>
+      <c r="O188" s="116"/>
+    </row>
+    <row r="189" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H189" s="117"/>
+      <c r="O189" s="116"/>
+    </row>
+    <row r="190" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H190" s="117"/>
+      <c r="O190" s="116"/>
+    </row>
+    <row r="191" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H191" s="117"/>
+      <c r="O191" s="116"/>
+    </row>
+    <row r="192" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H192" s="117"/>
+      <c r="O192" s="116"/>
+    </row>
+    <row r="193" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H193" s="117"/>
+      <c r="O193" s="116"/>
+    </row>
+    <row r="194" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H194" s="117"/>
+      <c r="O194" s="116"/>
+    </row>
+    <row r="195" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H195" s="117"/>
+      <c r="O195" s="116"/>
+    </row>
+    <row r="196" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H196" s="117"/>
+      <c r="O196" s="116"/>
+    </row>
+    <row r="197" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H197" s="117"/>
+      <c r="O197" s="116"/>
+    </row>
+    <row r="198" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H198" s="117"/>
+      <c r="O198" s="116"/>
+    </row>
+    <row r="199" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H199" s="117"/>
+      <c r="O199" s="116"/>
+    </row>
+    <row r="200" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H200" s="117"/>
+      <c r="O200" s="116"/>
+    </row>
+    <row r="201" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H201" s="117"/>
+      <c r="O201" s="116"/>
+    </row>
+    <row r="202" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H202" s="117"/>
+      <c r="O202" s="116"/>
+    </row>
+    <row r="203" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H203" s="117"/>
+      <c r="O203" s="116"/>
+    </row>
+    <row r="204" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H204" s="117"/>
+      <c r="O204" s="116"/>
+    </row>
+    <row r="205" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H205" s="117"/>
+      <c r="O205" s="116"/>
+    </row>
+    <row r="206" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H206" s="117"/>
+      <c r="O206" s="116"/>
+    </row>
+    <row r="207" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H207" s="117"/>
+      <c r="O207" s="116"/>
+    </row>
+    <row r="208" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H208" s="117"/>
+      <c r="O208" s="116"/>
+    </row>
+    <row r="209" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H209" s="117"/>
+      <c r="O209" s="116"/>
+    </row>
+    <row r="210" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H210" s="117"/>
+      <c r="O210" s="116"/>
+    </row>
+    <row r="211" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H211" s="117"/>
+      <c r="O211" s="116"/>
+    </row>
+    <row r="212" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H212" s="117"/>
+      <c r="O212" s="116"/>
+    </row>
+    <row r="213" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H213" s="117"/>
+      <c r="O213" s="116"/>
+    </row>
+    <row r="214" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H214" s="117"/>
+      <c r="O214" s="116"/>
+    </row>
+    <row r="215" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H215" s="117"/>
+      <c r="O215" s="116"/>
+    </row>
+    <row r="216" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H216" s="117"/>
+      <c r="O216" s="116"/>
+    </row>
+    <row r="217" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H217" s="117"/>
+      <c r="O217" s="116"/>
+    </row>
+    <row r="218" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H218" s="117"/>
+      <c r="O218" s="116"/>
+    </row>
+    <row r="219" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H219" s="117"/>
+      <c r="O219" s="116"/>
+    </row>
+    <row r="220" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H220" s="117"/>
+      <c r="O220" s="116"/>
+    </row>
+    <row r="221" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H221" s="117"/>
+      <c r="O221" s="116"/>
+    </row>
+    <row r="222" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H222" s="117"/>
+      <c r="O222" s="116"/>
+    </row>
+    <row r="223" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H223" s="117"/>
+      <c r="O223" s="116"/>
+    </row>
+    <row r="224" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H224" s="117"/>
+      <c r="O224" s="116"/>
+    </row>
+    <row r="225" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H225" s="117"/>
+      <c r="O225" s="116"/>
+    </row>
+    <row r="226" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H226" s="117"/>
+      <c r="O226" s="116"/>
+    </row>
+    <row r="227" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H227" s="117"/>
+      <c r="O227" s="116"/>
+    </row>
+    <row r="228" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H228" s="117"/>
+      <c r="O228" s="116"/>
+    </row>
+    <row r="229" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H229" s="117"/>
+      <c r="O229" s="116"/>
+    </row>
+    <row r="230" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H230" s="117"/>
+      <c r="O230" s="116"/>
+    </row>
+    <row r="231" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H231" s="117"/>
+      <c r="O231" s="116"/>
+    </row>
+    <row r="232" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H232" s="117"/>
+      <c r="O232" s="116"/>
+    </row>
+    <row r="233" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H233" s="117"/>
+      <c r="O233" s="116"/>
+    </row>
+    <row r="234" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H234" s="117"/>
+      <c r="O234" s="116"/>
+    </row>
+    <row r="235" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H235" s="117"/>
+      <c r="O235" s="116"/>
+    </row>
+    <row r="236" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H236" s="117"/>
+      <c r="O236" s="116"/>
+    </row>
+    <row r="237" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H237" s="117"/>
+      <c r="O237" s="116"/>
+    </row>
+    <row r="238" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H238" s="117"/>
+      <c r="O238" s="116"/>
+    </row>
+    <row r="239" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H239" s="117"/>
+      <c r="O239" s="116"/>
+    </row>
+    <row r="240" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H240" s="117"/>
+      <c r="O240" s="116"/>
+    </row>
+    <row r="241" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H241" s="117"/>
+      <c r="O241" s="116"/>
+    </row>
+    <row r="242" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H242" s="117"/>
+      <c r="O242" s="116"/>
+    </row>
+    <row r="243" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H243" s="117"/>
+      <c r="O243" s="116"/>
+    </row>
+    <row r="244" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H244" s="117"/>
+      <c r="O244" s="116"/>
+    </row>
+    <row r="245" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H245" s="117"/>
+      <c r="O245" s="116"/>
+    </row>
+    <row r="246" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H246" s="117"/>
+      <c r="O246" s="116"/>
+    </row>
+    <row r="247" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H247" s="117"/>
+      <c r="O247" s="116"/>
+    </row>
+    <row r="248" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H248" s="117"/>
+      <c r="O248" s="116"/>
+    </row>
+    <row r="249" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H249" s="117"/>
+      <c r="O249" s="116"/>
+    </row>
+    <row r="250" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H250" s="117"/>
+      <c r="O250" s="116"/>
+    </row>
+    <row r="251" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H251" s="117"/>
+      <c r="O251" s="116"/>
+    </row>
+    <row r="252" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H252" s="117"/>
+      <c r="O252" s="116"/>
+    </row>
+    <row r="253" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H253" s="117"/>
+      <c r="O253" s="116"/>
+    </row>
+    <row r="254" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H254" s="117"/>
+      <c r="O254" s="116"/>
+    </row>
+    <row r="255" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H255" s="117"/>
+      <c r="O255" s="116"/>
+    </row>
+    <row r="256" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H256" s="117"/>
+      <c r="O256" s="116"/>
+    </row>
+    <row r="257" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H257" s="117"/>
+      <c r="O257" s="116"/>
+    </row>
+    <row r="258" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H258" s="117"/>
+      <c r="O258" s="116"/>
+    </row>
+    <row r="259" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H259" s="117"/>
+      <c r="O259" s="116"/>
+    </row>
+    <row r="260" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H260" s="117"/>
+      <c r="O260" s="116"/>
+    </row>
+    <row r="261" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H261" s="117"/>
+      <c r="O261" s="116"/>
+    </row>
+    <row r="262" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H262" s="117"/>
+      <c r="O262" s="116"/>
+    </row>
+    <row r="263" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H263" s="117"/>
+      <c r="O263" s="116"/>
+    </row>
+    <row r="264" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H264" s="117"/>
+      <c r="O264" s="116"/>
+    </row>
+    <row r="265" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H265" s="117"/>
+      <c r="O265" s="116"/>
+    </row>
+    <row r="266" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H266" s="117"/>
+      <c r="O266" s="116"/>
+    </row>
+    <row r="267" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H267" s="117"/>
+      <c r="O267" s="116"/>
+    </row>
+    <row r="268" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H268" s="117"/>
+      <c r="O268" s="116"/>
+    </row>
+    <row r="269" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H269" s="117"/>
+      <c r="O269" s="116"/>
+    </row>
+    <row r="270" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H270" s="117"/>
+      <c r="O270" s="116"/>
+    </row>
+    <row r="271" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H271" s="117"/>
+      <c r="O271" s="116"/>
+    </row>
+    <row r="272" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H272" s="117"/>
+      <c r="O272" s="116"/>
+    </row>
+    <row r="273" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H273" s="117"/>
+      <c r="O273" s="116"/>
+    </row>
+    <row r="274" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H274" s="117"/>
+      <c r="O274" s="116"/>
+    </row>
+    <row r="275" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H275" s="117"/>
+      <c r="O275" s="116"/>
+    </row>
+    <row r="276" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H276" s="117"/>
+      <c r="O276" s="116"/>
+    </row>
+    <row r="277" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H277" s="117"/>
+      <c r="O277" s="116"/>
+    </row>
+    <row r="278" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H278" s="117"/>
+      <c r="O278" s="116"/>
+    </row>
+    <row r="279" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H279" s="117"/>
+      <c r="O279" s="116"/>
+    </row>
+    <row r="280" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H280" s="117"/>
+      <c r="O280" s="116"/>
+    </row>
+    <row r="281" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H281" s="117"/>
+      <c r="O281" s="116"/>
+    </row>
+    <row r="282" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H282" s="117"/>
+      <c r="O282" s="116"/>
+    </row>
+    <row r="283" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H283" s="117"/>
+      <c r="O283" s="116"/>
+    </row>
+    <row r="284" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H284" s="117"/>
+      <c r="O284" s="116"/>
+    </row>
+    <row r="285" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H285" s="117"/>
+      <c r="O285" s="116"/>
+    </row>
+    <row r="286" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H286" s="117"/>
+      <c r="O286" s="116"/>
+    </row>
+    <row r="287" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H287" s="117"/>
+      <c r="O287" s="116"/>
+    </row>
+    <row r="288" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H288" s="117"/>
+      <c r="O288" s="116"/>
+    </row>
+    <row r="289" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H289" s="117"/>
+      <c r="O289" s="116"/>
+    </row>
+    <row r="290" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H290" s="117"/>
+      <c r="O290" s="116"/>
+    </row>
+    <row r="291" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H291" s="117"/>
+      <c r="O291" s="116"/>
+    </row>
+    <row r="292" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H292" s="117"/>
+      <c r="O292" s="116"/>
+    </row>
+    <row r="293" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H293" s="117"/>
+      <c r="O293" s="116"/>
+    </row>
+    <row r="294" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H294" s="117"/>
+      <c r="O294" s="116"/>
+    </row>
+    <row r="295" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H295" s="117"/>
+      <c r="O295" s="116"/>
+    </row>
+    <row r="296" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H296" s="117"/>
+      <c r="O296" s="116"/>
+    </row>
+    <row r="297" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H297" s="117"/>
+      <c r="O297" s="116"/>
+    </row>
+    <row r="298" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H298" s="117"/>
+      <c r="O298" s="116"/>
+    </row>
+    <row r="299" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H299" s="117"/>
+      <c r="O299" s="116"/>
+    </row>
+    <row r="300" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H300" s="117"/>
+      <c r="O300" s="116"/>
+    </row>
+    <row r="301" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H301" s="117"/>
+      <c r="O301" s="116"/>
+    </row>
+    <row r="302" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H302" s="117"/>
+      <c r="O302" s="116"/>
+    </row>
+    <row r="303" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H303" s="117"/>
+      <c r="O303" s="116"/>
+    </row>
+    <row r="304" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H304" s="117"/>
+      <c r="O304" s="116"/>
+    </row>
+    <row r="305" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H305" s="117"/>
+      <c r="O305" s="116"/>
+    </row>
+    <row r="306" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H306" s="117"/>
+      <c r="O306" s="116"/>
+    </row>
+    <row r="307" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H307" s="117"/>
+      <c r="O307" s="116"/>
+    </row>
+    <row r="308" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H308" s="117"/>
+      <c r="O308" s="116"/>
+    </row>
+    <row r="309" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H309" s="117"/>
+      <c r="O309" s="116"/>
+    </row>
+    <row r="310" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H310" s="117"/>
+      <c r="O310" s="116"/>
+    </row>
+    <row r="311" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H311" s="117"/>
+      <c r="O311" s="116"/>
+    </row>
+    <row r="312" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H312" s="117"/>
+      <c r="O312" s="116"/>
+    </row>
+    <row r="313" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H313" s="117"/>
+      <c r="O313" s="116"/>
+    </row>
+    <row r="314" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H314" s="117"/>
+      <c r="O314" s="116"/>
+    </row>
+    <row r="315" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H315" s="117"/>
+      <c r="O315" s="116"/>
+    </row>
+    <row r="316" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H316" s="117"/>
+      <c r="O316" s="116"/>
+    </row>
+    <row r="317" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H317" s="117"/>
+      <c r="O317" s="116"/>
+    </row>
+    <row r="318" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H318" s="117"/>
+      <c r="O318" s="116"/>
+    </row>
+    <row r="319" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H319" s="117"/>
+      <c r="O319" s="116"/>
+    </row>
+    <row r="320" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H320" s="117"/>
+      <c r="O320" s="116"/>
+    </row>
+    <row r="321" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H321" s="117"/>
+      <c r="O321" s="116"/>
+    </row>
+    <row r="322" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H322" s="117"/>
+      <c r="O322" s="116"/>
+    </row>
+    <row r="323" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H323" s="117"/>
+      <c r="O323" s="116"/>
+    </row>
+    <row r="324" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H324" s="117"/>
+      <c r="O324" s="116"/>
+    </row>
+    <row r="325" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H325" s="117"/>
+      <c r="O325" s="116"/>
+    </row>
+    <row r="326" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H326" s="117"/>
+      <c r="O326" s="116"/>
+    </row>
+    <row r="327" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H327" s="117"/>
+      <c r="O327" s="116"/>
+    </row>
+    <row r="328" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H328" s="117"/>
+      <c r="O328" s="116"/>
+    </row>
+    <row r="329" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H329" s="117"/>
+      <c r="O329" s="116"/>
+    </row>
+    <row r="330" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H330" s="117"/>
+      <c r="O330" s="116"/>
+    </row>
+    <row r="331" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H331" s="117"/>
+      <c r="O331" s="116"/>
+    </row>
+    <row r="332" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H332" s="117"/>
+      <c r="O332" s="116"/>
+    </row>
+    <row r="333" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H333" s="117"/>
+      <c r="O333" s="116"/>
+    </row>
+    <row r="334" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H334" s="117"/>
+      <c r="O334" s="116"/>
+    </row>
+    <row r="335" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H335" s="117"/>
+      <c r="O335" s="116"/>
+    </row>
+    <row r="336" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H336" s="117"/>
+      <c r="O336" s="116"/>
+    </row>
+    <row r="337" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H337" s="117"/>
+      <c r="O337" s="116"/>
+    </row>
+    <row r="338" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H338" s="117"/>
+      <c r="O338" s="116"/>
+    </row>
+    <row r="339" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H339" s="117"/>
+      <c r="O339" s="116"/>
+    </row>
+    <row r="340" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H340" s="117"/>
+      <c r="O340" s="116"/>
+    </row>
+    <row r="341" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H341" s="117"/>
+      <c r="O341" s="116"/>
+    </row>
+    <row r="342" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H342" s="117"/>
+      <c r="O342" s="116"/>
+    </row>
+    <row r="343" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H343" s="117"/>
+      <c r="O343" s="116"/>
+    </row>
+    <row r="344" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H344" s="117"/>
+      <c r="O344" s="116"/>
+    </row>
+    <row r="345" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H345" s="117"/>
+      <c r="O345" s="116"/>
+    </row>
+    <row r="346" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H346" s="117"/>
+      <c r="O346" s="116"/>
+    </row>
+    <row r="347" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H347" s="117"/>
+      <c r="O347" s="116"/>
+    </row>
+    <row r="348" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H348" s="117"/>
+      <c r="O348" s="116"/>
+    </row>
+    <row r="349" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H349" s="117"/>
+      <c r="O349" s="116"/>
+    </row>
+    <row r="350" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H350" s="117"/>
+      <c r="O350" s="116"/>
+    </row>
+    <row r="351" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H351" s="117"/>
+      <c r="O351" s="116"/>
+    </row>
+    <row r="352" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H352" s="117"/>
+      <c r="O352" s="116"/>
+    </row>
+    <row r="353" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H353" s="117"/>
+      <c r="O353" s="116"/>
+    </row>
+    <row r="354" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H354" s="117"/>
+      <c r="O354" s="116"/>
+    </row>
+    <row r="355" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H355" s="117"/>
+      <c r="O355" s="116"/>
+    </row>
+    <row r="356" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H356" s="117"/>
+      <c r="O356" s="116"/>
+    </row>
+    <row r="357" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H357" s="117"/>
+      <c r="O357" s="116"/>
+    </row>
+    <row r="358" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H358" s="117"/>
+      <c r="O358" s="116"/>
+    </row>
+    <row r="359" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H359" s="117"/>
+      <c r="O359" s="116"/>
+    </row>
+    <row r="360" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H360" s="117"/>
+      <c r="O360" s="116"/>
+    </row>
+    <row r="361" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H361" s="117"/>
+      <c r="O361" s="116"/>
+    </row>
+    <row r="362" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H362" s="117"/>
+      <c r="O362" s="116"/>
+    </row>
+    <row r="363" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H363" s="117"/>
+      <c r="O363" s="116"/>
+    </row>
+    <row r="364" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H364" s="117"/>
+      <c r="O364" s="116"/>
+    </row>
+    <row r="365" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H365" s="117"/>
+      <c r="O365" s="116"/>
+    </row>
+    <row r="366" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H366" s="117"/>
+      <c r="O366" s="116"/>
+    </row>
+    <row r="367" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H367" s="117"/>
+      <c r="O367" s="116"/>
+    </row>
+    <row r="368" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H368" s="117"/>
+      <c r="O368" s="116"/>
+    </row>
+    <row r="369" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H369" s="117"/>
+      <c r="O369" s="116"/>
+    </row>
+    <row r="370" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H370" s="117"/>
+      <c r="O370" s="116"/>
+    </row>
+    <row r="371" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H371" s="117"/>
+      <c r="O371" s="116"/>
+    </row>
+    <row r="372" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H372" s="117"/>
+      <c r="O372" s="116"/>
+    </row>
+    <row r="373" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H373" s="117"/>
+      <c r="O373" s="116"/>
+    </row>
+    <row r="374" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H374" s="117"/>
+      <c r="O374" s="116"/>
+    </row>
+    <row r="375" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H375" s="117"/>
+      <c r="O375" s="116"/>
+    </row>
+    <row r="376" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H376" s="117"/>
+      <c r="O376" s="116"/>
+    </row>
+    <row r="377" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H377" s="117"/>
+      <c r="O377" s="116"/>
+    </row>
+    <row r="378" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H378" s="117"/>
+      <c r="O378" s="116"/>
+    </row>
+    <row r="379" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H379" s="117"/>
+      <c r="O379" s="116"/>
+    </row>
+    <row r="380" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H380" s="117"/>
+      <c r="O380" s="116"/>
+    </row>
+    <row r="381" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H381" s="117"/>
+      <c r="O381" s="116"/>
+    </row>
+    <row r="382" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H382" s="117"/>
+      <c r="O382" s="116"/>
+    </row>
+    <row r="383" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H383" s="117"/>
+      <c r="O383" s="116"/>
+    </row>
+    <row r="384" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H384" s="117"/>
+      <c r="O384" s="116"/>
+    </row>
+    <row r="385" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H385" s="117"/>
+      <c r="O385" s="116"/>
+    </row>
+    <row r="386" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H386" s="117"/>
+      <c r="O386" s="116"/>
+    </row>
+    <row r="387" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H387" s="117"/>
+      <c r="O387" s="116"/>
+    </row>
+    <row r="388" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H388" s="117"/>
+      <c r="O388" s="116"/>
+    </row>
+    <row r="389" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H389" s="117"/>
+      <c r="O389" s="116"/>
+    </row>
+    <row r="390" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H390" s="117"/>
+      <c r="O390" s="116"/>
+    </row>
+    <row r="391" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H391" s="117"/>
+      <c r="O391" s="116"/>
+    </row>
+    <row r="392" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H392" s="117"/>
+      <c r="O392" s="116"/>
+    </row>
+    <row r="393" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H393" s="117"/>
+      <c r="O393" s="116"/>
+    </row>
+    <row r="394" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H394" s="117"/>
+      <c r="O394" s="116"/>
+    </row>
+    <row r="395" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H395" s="117"/>
+      <c r="O395" s="116"/>
+    </row>
+    <row r="396" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H396" s="117"/>
+      <c r="O396" s="116"/>
+    </row>
+    <row r="397" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H397" s="117"/>
+      <c r="O397" s="116"/>
+    </row>
+    <row r="398" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H398" s="117"/>
+      <c r="O398" s="116"/>
+    </row>
+    <row r="399" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H399" s="117"/>
+      <c r="O399" s="116"/>
+    </row>
+    <row r="400" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H400" s="117"/>
+      <c r="O400" s="116"/>
+    </row>
+    <row r="401" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H401" s="117"/>
+      <c r="O401" s="116"/>
+    </row>
+    <row r="402" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H402" s="117"/>
+      <c r="O402" s="116"/>
+    </row>
+    <row r="403" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H403" s="117"/>
+      <c r="O403" s="116"/>
+    </row>
+    <row r="404" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H404" s="117"/>
+      <c r="O404" s="116"/>
+    </row>
+    <row r="405" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H405" s="117"/>
+      <c r="O405" s="116"/>
+    </row>
+    <row r="406" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H406" s="117"/>
+      <c r="O406" s="116"/>
+    </row>
+    <row r="407" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H407" s="117"/>
+      <c r="O407" s="116"/>
+    </row>
+    <row r="408" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H408" s="117"/>
+      <c r="O408" s="116"/>
+    </row>
+    <row r="409" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H409" s="117"/>
+      <c r="O409" s="116"/>
+    </row>
+    <row r="410" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H410" s="117"/>
+      <c r="O410" s="116"/>
+    </row>
+    <row r="411" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H411" s="117"/>
+      <c r="O411" s="116"/>
+    </row>
+    <row r="412" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H412" s="117"/>
+      <c r="O412" s="116"/>
+    </row>
+    <row r="413" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H413" s="117"/>
+      <c r="O413" s="116"/>
+    </row>
+    <row r="414" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H414" s="117"/>
+      <c r="O414" s="116"/>
+    </row>
+    <row r="415" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H415" s="117"/>
+      <c r="O415" s="116"/>
+    </row>
+    <row r="416" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H416" s="117"/>
+      <c r="O416" s="116"/>
+    </row>
+    <row r="417" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H417" s="117"/>
+      <c r="O417" s="116"/>
+    </row>
+    <row r="418" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H418" s="117"/>
+      <c r="O418" s="116"/>
+    </row>
+    <row r="419" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H419" s="117"/>
+      <c r="O419" s="116"/>
+    </row>
+    <row r="420" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H420" s="117"/>
+      <c r="O420" s="116"/>
+    </row>
+    <row r="421" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H421" s="117"/>
+      <c r="O421" s="116"/>
+    </row>
+    <row r="422" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H422" s="117"/>
+      <c r="O422" s="116"/>
+    </row>
+    <row r="423" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H423" s="117"/>
+      <c r="O423" s="116"/>
+    </row>
+    <row r="424" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H424" s="117"/>
+      <c r="O424" s="116"/>
+    </row>
+    <row r="425" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H425" s="117"/>
+      <c r="O425" s="116"/>
+    </row>
+    <row r="426" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H426" s="117"/>
+      <c r="O426" s="116"/>
+    </row>
+    <row r="427" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H427" s="117"/>
+      <c r="O427" s="116"/>
+    </row>
+    <row r="428" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H428" s="117"/>
+      <c r="O428" s="116"/>
+    </row>
+    <row r="429" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H429" s="117"/>
+      <c r="O429" s="116"/>
+    </row>
+    <row r="430" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H430" s="117"/>
+      <c r="O430" s="116"/>
+    </row>
+    <row r="431" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H431" s="117"/>
+      <c r="O431" s="116"/>
+    </row>
+    <row r="432" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H432" s="117"/>
+      <c r="O432" s="116"/>
+    </row>
+    <row r="433" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H433" s="117"/>
+      <c r="O433" s="116"/>
+    </row>
+    <row r="434" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H434" s="117"/>
+      <c r="O434" s="116"/>
+    </row>
+    <row r="435" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H435" s="117"/>
+      <c r="O435" s="116"/>
+    </row>
+    <row r="436" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H436" s="117"/>
+      <c r="O436" s="116"/>
+    </row>
+    <row r="437" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H437" s="117"/>
+      <c r="O437" s="116"/>
+    </row>
+    <row r="438" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H438" s="117"/>
+      <c r="O438" s="116"/>
+    </row>
+    <row r="439" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H439" s="117"/>
+      <c r="O439" s="116"/>
+    </row>
+    <row r="440" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H440" s="117"/>
+      <c r="O440" s="116"/>
+    </row>
+    <row r="441" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H441" s="117"/>
+      <c r="O441" s="116"/>
+    </row>
+    <row r="442" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H442" s="117"/>
+      <c r="O442" s="116"/>
+    </row>
+    <row r="443" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H443" s="117"/>
+      <c r="O443" s="116"/>
+    </row>
+    <row r="444" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H444" s="117"/>
+      <c r="O444" s="116"/>
+    </row>
+    <row r="445" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H445" s="117"/>
+      <c r="O445" s="116"/>
+    </row>
+    <row r="446" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H446" s="117"/>
+      <c r="O446" s="116"/>
+    </row>
+    <row r="447" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H447" s="117"/>
+      <c r="O447" s="116"/>
+    </row>
+    <row r="448" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H448" s="117"/>
+      <c r="O448" s="116"/>
+    </row>
+    <row r="449" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H449" s="117"/>
+      <c r="O449" s="116"/>
+    </row>
+    <row r="450" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H450" s="117"/>
+      <c r="O450" s="116"/>
+    </row>
+    <row r="451" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H451" s="117"/>
+      <c r="O451" s="116"/>
+    </row>
+    <row r="452" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H452" s="117"/>
+      <c r="O452" s="116"/>
+    </row>
+    <row r="453" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H453" s="117"/>
+      <c r="O453" s="116"/>
+    </row>
+    <row r="454" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H454" s="117"/>
+      <c r="O454" s="116"/>
+    </row>
+    <row r="455" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H455" s="117"/>
+      <c r="O455" s="116"/>
+    </row>
+    <row r="456" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H456" s="117"/>
+      <c r="O456" s="116"/>
+    </row>
+    <row r="457" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H457" s="117"/>
+      <c r="O457" s="116"/>
+    </row>
+    <row r="458" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H458" s="117"/>
+      <c r="O458" s="116"/>
+    </row>
+    <row r="459" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H459" s="117"/>
+      <c r="O459" s="116"/>
+    </row>
+    <row r="460" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H460" s="117"/>
+      <c r="O460" s="116"/>
+    </row>
+    <row r="461" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H461" s="117"/>
+      <c r="O461" s="116"/>
+    </row>
+    <row r="462" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H462" s="117"/>
+      <c r="O462" s="116"/>
+    </row>
+    <row r="463" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H463" s="117"/>
+      <c r="O463" s="116"/>
+    </row>
+    <row r="464" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H464" s="117"/>
+      <c r="O464" s="116"/>
+    </row>
+    <row r="465" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H465" s="117"/>
+      <c r="O465" s="116"/>
+    </row>
+    <row r="466" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H466" s="117"/>
+      <c r="O466" s="116"/>
+    </row>
+    <row r="467" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H467" s="117"/>
+      <c r="O467" s="116"/>
+    </row>
+    <row r="468" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H468" s="117"/>
+      <c r="O468" s="116"/>
+    </row>
+    <row r="469" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H469" s="117"/>
+      <c r="O469" s="116"/>
+    </row>
+    <row r="470" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H470" s="117"/>
+      <c r="O470" s="116"/>
+    </row>
+    <row r="471" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H471" s="117"/>
+      <c r="O471" s="116"/>
+    </row>
+    <row r="472" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H472" s="117"/>
+      <c r="O472" s="116"/>
+    </row>
+    <row r="473" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H473" s="117"/>
+      <c r="O473" s="116"/>
+    </row>
+    <row r="474" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H474" s="117"/>
+      <c r="O474" s="116"/>
+    </row>
+    <row r="475" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H475" s="117"/>
+      <c r="O475" s="116"/>
+    </row>
+    <row r="476" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H476" s="117"/>
+      <c r="O476" s="116"/>
+    </row>
+    <row r="477" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H477" s="117"/>
+      <c r="O477" s="116"/>
+    </row>
+    <row r="478" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H478" s="117"/>
+      <c r="O478" s="116"/>
+    </row>
+    <row r="479" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H479" s="117"/>
+      <c r="O479" s="116"/>
+    </row>
+    <row r="480" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H480" s="117"/>
+      <c r="O480" s="116"/>
+    </row>
+    <row r="481" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H481" s="117"/>
+      <c r="O481" s="116"/>
+    </row>
+    <row r="482" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H482" s="117"/>
+      <c r="O482" s="116"/>
+    </row>
+    <row r="483" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H483" s="117"/>
+      <c r="O483" s="116"/>
+    </row>
+    <row r="484" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H484" s="117"/>
+      <c r="O484" s="116"/>
+    </row>
+    <row r="485" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H485" s="117"/>
+      <c r="O485" s="116"/>
+    </row>
+    <row r="486" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H486" s="117"/>
+      <c r="O486" s="116"/>
+    </row>
+    <row r="487" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H487" s="117"/>
+      <c r="O487" s="116"/>
+    </row>
+    <row r="488" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H488" s="117"/>
+      <c r="O488" s="116"/>
+    </row>
+    <row r="489" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H489" s="117"/>
+      <c r="O489" s="116"/>
+    </row>
+    <row r="490" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H490" s="117"/>
+      <c r="O490" s="116"/>
+    </row>
+    <row r="491" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H491" s="117"/>
+      <c r="O491" s="116"/>
+    </row>
+    <row r="492" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H492" s="117"/>
+      <c r="O492" s="116"/>
+    </row>
+    <row r="493" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H493" s="117"/>
+      <c r="O493" s="116"/>
+    </row>
+    <row r="494" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H494" s="117"/>
+      <c r="O494" s="116"/>
+    </row>
+    <row r="495" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H495" s="117"/>
+      <c r="O495" s="116"/>
+    </row>
+    <row r="496" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H496" s="117"/>
+      <c r="O496" s="116"/>
+    </row>
+    <row r="497" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H497" s="117"/>
+      <c r="O497" s="116"/>
+    </row>
+    <row r="498" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H498" s="117"/>
+      <c r="O498" s="116"/>
+    </row>
+    <row r="499" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H499" s="117"/>
+      <c r="O499" s="116"/>
+    </row>
+    <row r="500" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H500" s="117"/>
+      <c r="O500" s="116"/>
+    </row>
+    <row r="501" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H501" s="117"/>
+      <c r="O501" s="116"/>
+    </row>
+    <row r="502" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H502" s="117"/>
+      <c r="O502" s="116"/>
+    </row>
+    <row r="503" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H503" s="117"/>
+      <c r="O503" s="116"/>
+    </row>
+    <row r="504" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H504" s="117"/>
+      <c r="O504" s="116"/>
+    </row>
+    <row r="505" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H505" s="117"/>
+      <c r="O505" s="116"/>
+    </row>
+    <row r="506" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H506" s="117"/>
+      <c r="O506" s="116"/>
+    </row>
+    <row r="507" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H507" s="117"/>
+      <c r="O507" s="116"/>
+    </row>
+    <row r="508" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H508" s="117"/>
+      <c r="O508" s="116"/>
+    </row>
+    <row r="509" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H509" s="117"/>
+      <c r="O509" s="116"/>
+    </row>
+    <row r="510" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H510" s="117"/>
+      <c r="O510" s="116"/>
+    </row>
+    <row r="511" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H511" s="117"/>
+      <c r="O511" s="116"/>
+    </row>
+    <row r="512" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H512" s="117"/>
+      <c r="O512" s="116"/>
+    </row>
+    <row r="513" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H513" s="117"/>
+      <c r="O513" s="116"/>
+    </row>
+    <row r="514" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H514" s="117"/>
+      <c r="O514" s="116"/>
+    </row>
+    <row r="515" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H515" s="117"/>
+      <c r="O515" s="116"/>
+    </row>
+    <row r="516" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H516" s="117"/>
+      <c r="O516" s="116"/>
+    </row>
+    <row r="517" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H517" s="117"/>
+      <c r="O517" s="116"/>
+    </row>
+    <row r="518" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H518" s="117"/>
+      <c r="O518" s="116"/>
+    </row>
+    <row r="519" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H519" s="117"/>
+      <c r="O519" s="116"/>
+    </row>
+    <row r="520" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H520" s="117"/>
+      <c r="O520" s="116"/>
+    </row>
+    <row r="521" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H521" s="117"/>
+      <c r="O521" s="116"/>
+    </row>
+    <row r="522" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H522" s="117"/>
+      <c r="O522" s="116"/>
+    </row>
+    <row r="523" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H523" s="117"/>
+      <c r="O523" s="116"/>
+    </row>
+    <row r="524" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H524" s="117"/>
+      <c r="O524" s="116"/>
+    </row>
+    <row r="525" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H525" s="117"/>
+      <c r="O525" s="116"/>
+    </row>
+    <row r="526" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H526" s="117"/>
+      <c r="O526" s="116"/>
+    </row>
+    <row r="527" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H527" s="117"/>
+      <c r="O527" s="116"/>
+    </row>
+    <row r="528" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H528" s="117"/>
+      <c r="O528" s="116"/>
+    </row>
+    <row r="529" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H529" s="117"/>
+      <c r="O529" s="116"/>
+    </row>
+    <row r="530" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H530" s="117"/>
+      <c r="O530" s="116"/>
+    </row>
+    <row r="531" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H531" s="117"/>
+      <c r="O531" s="116"/>
+    </row>
+    <row r="532" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H532" s="117"/>
+      <c r="O532" s="116"/>
+    </row>
+    <row r="533" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H533" s="117"/>
+      <c r="O533" s="116"/>
+    </row>
+    <row r="534" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H534" s="117"/>
+      <c r="O534" s="116"/>
+    </row>
+    <row r="535" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H535" s="117"/>
+      <c r="O535" s="116"/>
+    </row>
+    <row r="536" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H536" s="117"/>
+      <c r="O536" s="116"/>
+    </row>
+    <row r="537" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H537" s="117"/>
+      <c r="O537" s="116"/>
+    </row>
+    <row r="538" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H538" s="117"/>
+      <c r="O538" s="116"/>
+    </row>
+    <row r="539" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H539" s="117"/>
+      <c r="O539" s="116"/>
+    </row>
+    <row r="540" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H540" s="117"/>
+      <c r="O540" s="116"/>
+    </row>
+    <row r="541" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H541" s="117"/>
+      <c r="O541" s="116"/>
+    </row>
+    <row r="542" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H542" s="117"/>
+      <c r="O542" s="116"/>
+    </row>
+    <row r="543" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H543" s="117"/>
+      <c r="O543" s="116"/>
+    </row>
+    <row r="544" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H544" s="117"/>
+      <c r="O544" s="116"/>
+    </row>
+    <row r="545" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H545" s="117"/>
+      <c r="O545" s="116"/>
+    </row>
+    <row r="546" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H546" s="117"/>
+      <c r="O546" s="116"/>
+    </row>
+    <row r="547" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H547" s="117"/>
+      <c r="O547" s="116"/>
+    </row>
+    <row r="548" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H548" s="117"/>
+      <c r="O548" s="116"/>
+    </row>
+    <row r="549" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H549" s="117"/>
+      <c r="O549" s="116"/>
+    </row>
+    <row r="550" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H550" s="117"/>
+      <c r="O550" s="116"/>
+    </row>
+    <row r="551" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H551" s="117"/>
+      <c r="O551" s="116"/>
+    </row>
+    <row r="552" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H552" s="117"/>
+      <c r="O552" s="116"/>
+    </row>
+    <row r="553" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H553" s="117"/>
+      <c r="O553" s="116"/>
+    </row>
+    <row r="554" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H554" s="117"/>
+      <c r="O554" s="116"/>
+    </row>
+    <row r="555" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H555" s="117"/>
+      <c r="O555" s="116"/>
+    </row>
+    <row r="556" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H556" s="117"/>
+      <c r="O556" s="116"/>
+    </row>
+    <row r="557" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H557" s="117"/>
+      <c r="O557" s="116"/>
+    </row>
+    <row r="558" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H558" s="117"/>
+      <c r="O558" s="116"/>
+    </row>
+    <row r="559" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H559" s="117"/>
+      <c r="O559" s="116"/>
+    </row>
+    <row r="560" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H560" s="117"/>
+      <c r="O560" s="116"/>
+    </row>
+    <row r="561" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H561" s="117"/>
+      <c r="O561" s="116"/>
+    </row>
+    <row r="562" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H562" s="117"/>
+      <c r="O562" s="116"/>
+    </row>
+    <row r="563" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H563" s="117"/>
+      <c r="O563" s="116"/>
+    </row>
+    <row r="564" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H564" s="117"/>
+      <c r="O564" s="116"/>
+    </row>
+    <row r="565" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H565" s="117"/>
+      <c r="O565" s="116"/>
+    </row>
+    <row r="566" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H566" s="117"/>
+      <c r="O566" s="116"/>
+    </row>
+    <row r="567" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H567" s="117"/>
+      <c r="O567" s="116"/>
+    </row>
+    <row r="568" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H568" s="117"/>
+      <c r="O568" s="116"/>
+    </row>
+    <row r="569" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H569" s="117"/>
+      <c r="O569" s="116"/>
+    </row>
+    <row r="570" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H570" s="117"/>
+      <c r="O570" s="116"/>
+    </row>
+    <row r="571" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H571" s="117"/>
+      <c r="O571" s="116"/>
+    </row>
+    <row r="572" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H572" s="117"/>
+      <c r="O572" s="116"/>
+    </row>
+    <row r="573" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H573" s="117"/>
+      <c r="O573" s="116"/>
+    </row>
+    <row r="574" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H574" s="117"/>
+      <c r="O574" s="116"/>
+    </row>
+    <row r="575" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H575" s="117"/>
+      <c r="O575" s="116"/>
+    </row>
+    <row r="576" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H576" s="117"/>
+      <c r="O576" s="116"/>
+    </row>
+    <row r="577" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H577" s="117"/>
+      <c r="O577" s="116"/>
+    </row>
+    <row r="578" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H578" s="117"/>
+      <c r="O578" s="116"/>
+    </row>
+    <row r="579" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H579" s="117"/>
+      <c r="O579" s="116"/>
+    </row>
+    <row r="580" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H580" s="117"/>
+      <c r="O580" s="116"/>
+    </row>
+    <row r="581" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H581" s="117"/>
+      <c r="O581" s="116"/>
+    </row>
+    <row r="582" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H582" s="117"/>
+      <c r="O582" s="116"/>
+    </row>
+    <row r="583" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H583" s="117"/>
+      <c r="O583" s="116"/>
+    </row>
+    <row r="584" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H584" s="117"/>
+      <c r="O584" s="116"/>
+    </row>
+    <row r="585" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H585" s="117"/>
+      <c r="O585" s="116"/>
+    </row>
+    <row r="586" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H586" s="117"/>
+      <c r="O586" s="116"/>
+    </row>
+    <row r="587" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H587" s="117"/>
+      <c r="O587" s="116"/>
+    </row>
+    <row r="588" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H588" s="117"/>
+      <c r="O588" s="116"/>
+    </row>
+    <row r="589" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H589" s="117"/>
+      <c r="O589" s="116"/>
+    </row>
+    <row r="590" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H590" s="117"/>
+      <c r="O590" s="116"/>
+    </row>
+    <row r="591" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H591" s="117"/>
+      <c r="O591" s="116"/>
+    </row>
+    <row r="592" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H592" s="117"/>
+      <c r="O592" s="116"/>
+    </row>
+    <row r="593" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H593" s="117"/>
+      <c r="O593" s="116"/>
+    </row>
+    <row r="594" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H594" s="117"/>
+      <c r="O594" s="116"/>
+    </row>
+    <row r="595" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H595" s="117"/>
+      <c r="O595" s="116"/>
+    </row>
+    <row r="596" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H596" s="117"/>
+      <c r="O596" s="116"/>
+    </row>
+    <row r="597" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H597" s="117"/>
+      <c r="O597" s="116"/>
+    </row>
+    <row r="598" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H598" s="117"/>
+      <c r="O598" s="116"/>
+    </row>
+    <row r="599" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H599" s="117"/>
+      <c r="O599" s="116"/>
+    </row>
+    <row r="600" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H600" s="117"/>
+      <c r="O600" s="116"/>
+    </row>
+    <row r="601" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H601" s="117"/>
+      <c r="O601" s="116"/>
+    </row>
+    <row r="602" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H602" s="117"/>
+      <c r="O602" s="116"/>
+    </row>
+    <row r="603" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H603" s="117"/>
+      <c r="O603" s="116"/>
+    </row>
+    <row r="604" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H604" s="117"/>
+      <c r="O604" s="116"/>
+    </row>
+    <row r="605" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H605" s="117"/>
+      <c r="O605" s="116"/>
+    </row>
+    <row r="606" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H606" s="117"/>
+      <c r="O606" s="116"/>
+    </row>
+    <row r="607" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H607" s="117"/>
+      <c r="O607" s="116"/>
+    </row>
+    <row r="608" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H608" s="117"/>
+      <c r="O608" s="116"/>
+    </row>
+    <row r="609" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H609" s="117"/>
+      <c r="O609" s="116"/>
+    </row>
+    <row r="610" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H610" s="117"/>
+      <c r="O610" s="116"/>
+    </row>
+    <row r="611" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H611" s="117"/>
+      <c r="O611" s="116"/>
+    </row>
+    <row r="612" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H612" s="117"/>
+      <c r="O612" s="116"/>
+    </row>
+    <row r="613" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H613" s="117"/>
+      <c r="O613" s="116"/>
+    </row>
+    <row r="614" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H614" s="117"/>
+      <c r="O614" s="116"/>
+    </row>
+    <row r="615" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H615" s="117"/>
+      <c r="O615" s="116"/>
+    </row>
+    <row r="616" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H616" s="117"/>
+      <c r="O616" s="116"/>
+    </row>
+    <row r="617" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H617" s="117"/>
+      <c r="O617" s="116"/>
+    </row>
+    <row r="618" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H618" s="117"/>
+      <c r="O618" s="116"/>
+    </row>
+    <row r="619" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H619" s="117"/>
+      <c r="O619" s="116"/>
+    </row>
+    <row r="620" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H620" s="117"/>
+      <c r="O620" s="116"/>
+    </row>
+    <row r="621" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H621" s="117"/>
+      <c r="O621" s="116"/>
+    </row>
+    <row r="622" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H622" s="117"/>
+      <c r="O622" s="116"/>
+    </row>
+    <row r="623" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H623" s="117"/>
+      <c r="O623" s="116"/>
+    </row>
+    <row r="624" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H624" s="117"/>
+      <c r="O624" s="116"/>
+    </row>
+    <row r="625" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H625" s="117"/>
+      <c r="O625" s="116"/>
+    </row>
+    <row r="626" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H626" s="117"/>
+      <c r="O626" s="116"/>
+    </row>
+    <row r="627" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H627" s="117"/>
+      <c r="O627" s="116"/>
+    </row>
+    <row r="628" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H628" s="117"/>
+      <c r="O628" s="116"/>
+    </row>
+    <row r="629" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H629" s="117"/>
+      <c r="O629" s="116"/>
+    </row>
+    <row r="630" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H630" s="117"/>
+      <c r="O630" s="116"/>
+    </row>
+    <row r="631" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H631" s="117"/>
+      <c r="O631" s="116"/>
+    </row>
+    <row r="632" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H632" s="117"/>
+      <c r="O632" s="116"/>
+    </row>
+    <row r="633" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H633" s="117"/>
+      <c r="O633" s="116"/>
+    </row>
+    <row r="634" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H634" s="117"/>
+      <c r="O634" s="116"/>
+    </row>
+    <row r="635" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H635" s="117"/>
+      <c r="O635" s="116"/>
+    </row>
+    <row r="636" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H636" s="117"/>
+      <c r="O636" s="116"/>
+    </row>
+    <row r="637" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H637" s="117"/>
+      <c r="O637" s="116"/>
+    </row>
+    <row r="638" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H638" s="117"/>
+      <c r="O638" s="116"/>
+    </row>
+    <row r="639" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H639" s="117"/>
+      <c r="O639" s="116"/>
+    </row>
+    <row r="640" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H640" s="117"/>
+      <c r="O640" s="116"/>
+    </row>
+    <row r="641" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H641" s="117"/>
+      <c r="O641" s="116"/>
+    </row>
+    <row r="642" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H642" s="117"/>
+      <c r="O642" s="116"/>
+    </row>
+    <row r="643" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H643" s="117"/>
+      <c r="O643" s="116"/>
+    </row>
+    <row r="644" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H644" s="117"/>
+      <c r="O644" s="116"/>
+    </row>
+    <row r="645" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H645" s="117"/>
+      <c r="O645" s="116"/>
+    </row>
+    <row r="646" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H646" s="117"/>
+      <c r="O646" s="116"/>
+    </row>
+    <row r="647" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H647" s="117"/>
+      <c r="O647" s="116"/>
+    </row>
+    <row r="648" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H648" s="117"/>
+      <c r="O648" s="116"/>
+    </row>
+    <row r="649" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H649" s="117"/>
+      <c r="O649" s="116"/>
+    </row>
+    <row r="650" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H650" s="117"/>
+      <c r="O650" s="116"/>
+    </row>
+    <row r="651" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H651" s="117"/>
+      <c r="O651" s="116"/>
+    </row>
+    <row r="652" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H652" s="117"/>
+      <c r="O652" s="116"/>
+    </row>
+    <row r="653" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H653" s="117"/>
+      <c r="O653" s="116"/>
+    </row>
+    <row r="654" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H654" s="117"/>
+      <c r="O654" s="116"/>
+    </row>
+    <row r="655" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H655" s="117"/>
+      <c r="O655" s="116"/>
+    </row>
+    <row r="656" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H656" s="117"/>
+      <c r="O656" s="116"/>
+    </row>
+    <row r="657" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H657" s="117"/>
+      <c r="O657" s="116"/>
+    </row>
+    <row r="658" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H658" s="117"/>
+      <c r="O658" s="116"/>
+    </row>
+    <row r="659" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H659" s="117"/>
+      <c r="O659" s="116"/>
+    </row>
+    <row r="660" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H660" s="117"/>
+      <c r="O660" s="116"/>
+    </row>
+    <row r="661" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H661" s="117"/>
+      <c r="O661" s="116"/>
+    </row>
+    <row r="662" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H662" s="117"/>
+      <c r="O662" s="116"/>
+    </row>
+    <row r="663" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H663" s="117"/>
+      <c r="O663" s="116"/>
+    </row>
+    <row r="664" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H664" s="117"/>
+      <c r="O664" s="116"/>
+    </row>
+    <row r="665" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H665" s="117"/>
+      <c r="O665" s="116"/>
+    </row>
+    <row r="666" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H666" s="117"/>
+      <c r="O666" s="116"/>
+    </row>
+    <row r="667" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H667" s="117"/>
+      <c r="O667" s="116"/>
+    </row>
+    <row r="668" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H668" s="117"/>
+      <c r="O668" s="116"/>
+    </row>
+    <row r="669" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H669" s="117"/>
+      <c r="O669" s="116"/>
+    </row>
+    <row r="670" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H670" s="117"/>
+      <c r="O670" s="116"/>
+    </row>
+    <row r="671" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H671" s="117"/>
+      <c r="O671" s="116"/>
+    </row>
+    <row r="672" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H672" s="117"/>
+      <c r="O672" s="116"/>
+    </row>
+    <row r="673" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H673" s="117"/>
+      <c r="O673" s="116"/>
+    </row>
+    <row r="674" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H674" s="117"/>
+      <c r="O674" s="116"/>
+    </row>
+    <row r="675" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H675" s="117"/>
+      <c r="O675" s="116"/>
+    </row>
+    <row r="676" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H676" s="117"/>
+      <c r="O676" s="116"/>
+    </row>
+    <row r="677" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H677" s="117"/>
+      <c r="O677" s="116"/>
+    </row>
+    <row r="678" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H678" s="117"/>
+      <c r="O678" s="116"/>
+    </row>
+    <row r="679" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H679" s="117"/>
+      <c r="O679" s="116"/>
+    </row>
+    <row r="680" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H680" s="117"/>
+      <c r="O680" s="116"/>
+    </row>
+    <row r="681" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H681" s="117"/>
+      <c r="O681" s="116"/>
+    </row>
+    <row r="682" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H682" s="117"/>
+      <c r="O682" s="116"/>
+    </row>
+    <row r="683" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H683" s="117"/>
+      <c r="O683" s="116"/>
+    </row>
+    <row r="684" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H684" s="117"/>
+      <c r="O684" s="116"/>
+    </row>
+    <row r="685" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H685" s="117"/>
+      <c r="O685" s="116"/>
+    </row>
+    <row r="686" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H686" s="117"/>
+      <c r="O686" s="116"/>
+    </row>
+    <row r="687" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H687" s="117"/>
+      <c r="O687" s="116"/>
+    </row>
+    <row r="688" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H688" s="117"/>
+      <c r="O688" s="116"/>
+    </row>
+    <row r="689" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H689" s="117"/>
+      <c r="O689" s="116"/>
+    </row>
+    <row r="690" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H690" s="117"/>
+      <c r="O690" s="116"/>
+    </row>
+    <row r="691" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H691" s="117"/>
+      <c r="O691" s="116"/>
+    </row>
+    <row r="692" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H692" s="117"/>
+      <c r="O692" s="116"/>
+    </row>
+    <row r="693" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H693" s="117"/>
+      <c r="O693" s="116"/>
+    </row>
+    <row r="694" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H694" s="117"/>
+      <c r="O694" s="116"/>
+    </row>
+    <row r="695" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H695" s="117"/>
+      <c r="O695" s="116"/>
+    </row>
+    <row r="696" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H696" s="117"/>
+      <c r="O696" s="116"/>
+    </row>
+    <row r="697" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H697" s="117"/>
+      <c r="O697" s="116"/>
+    </row>
+    <row r="698" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H698" s="117"/>
+      <c r="O698" s="116"/>
+    </row>
+    <row r="699" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H699" s="117"/>
+      <c r="O699" s="116"/>
+    </row>
+    <row r="700" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H700" s="117"/>
+      <c r="O700" s="116"/>
+    </row>
+    <row r="701" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H701" s="117"/>
+      <c r="O701" s="116"/>
+    </row>
+    <row r="702" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H702" s="117"/>
+      <c r="O702" s="116"/>
+    </row>
+    <row r="703" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H703" s="117"/>
+      <c r="O703" s="116"/>
+    </row>
+    <row r="704" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H704" s="117"/>
+      <c r="O704" s="116"/>
+    </row>
+    <row r="705" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H705" s="117"/>
+      <c r="O705" s="116"/>
+    </row>
+    <row r="706" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H706" s="117"/>
+      <c r="O706" s="116"/>
+    </row>
+    <row r="707" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H707" s="117"/>
+      <c r="O707" s="116"/>
+    </row>
+    <row r="708" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H708" s="117"/>
+      <c r="O708" s="116"/>
+    </row>
+    <row r="709" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H709" s="117"/>
+      <c r="O709" s="116"/>
+    </row>
+    <row r="710" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H710" s="117"/>
+      <c r="O710" s="116"/>
+    </row>
+    <row r="711" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H711" s="117"/>
+      <c r="O711" s="116"/>
+    </row>
+    <row r="712" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H712" s="117"/>
+      <c r="O712" s="116"/>
+    </row>
+    <row r="713" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H713" s="117"/>
+      <c r="O713" s="116"/>
+    </row>
+    <row r="714" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H714" s="117"/>
+      <c r="O714" s="116"/>
+    </row>
+    <row r="715" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H715" s="117"/>
+      <c r="O715" s="116"/>
+    </row>
+    <row r="716" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H716" s="117"/>
+      <c r="O716" s="116"/>
+    </row>
+    <row r="717" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H717" s="117"/>
+      <c r="O717" s="116"/>
+    </row>
+    <row r="718" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H718" s="117"/>
+      <c r="O718" s="116"/>
+    </row>
+    <row r="719" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H719" s="117"/>
+      <c r="O719" s="116"/>
+    </row>
+    <row r="720" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H720" s="117"/>
+      <c r="O720" s="116"/>
+    </row>
+    <row r="721" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H721" s="117"/>
+      <c r="O721" s="116"/>
+    </row>
+    <row r="722" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H722" s="117"/>
+      <c r="O722" s="116"/>
+    </row>
+    <row r="723" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H723" s="117"/>
+      <c r="O723" s="116"/>
+    </row>
+    <row r="724" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H724" s="117"/>
+      <c r="O724" s="116"/>
+    </row>
+    <row r="725" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H725" s="117"/>
+      <c r="O725" s="116"/>
+    </row>
+    <row r="726" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H726" s="117"/>
+      <c r="O726" s="116"/>
+    </row>
+    <row r="727" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H727" s="117"/>
+      <c r="O727" s="116"/>
+    </row>
+    <row r="728" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H728" s="117"/>
+      <c r="O728" s="116"/>
+    </row>
+    <row r="729" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H729" s="117"/>
+      <c r="O729" s="116"/>
+    </row>
+    <row r="730" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H730" s="117"/>
+      <c r="O730" s="116"/>
+    </row>
+    <row r="731" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H731" s="117"/>
+      <c r="O731" s="116"/>
+    </row>
+    <row r="732" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H732" s="117"/>
+      <c r="O732" s="116"/>
+    </row>
+    <row r="733" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H733" s="117"/>
+      <c r="O733" s="116"/>
+    </row>
+    <row r="734" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H734" s="117"/>
+      <c r="O734" s="116"/>
+    </row>
+    <row r="735" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H735" s="117"/>
+      <c r="O735" s="116"/>
+    </row>
+    <row r="736" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H736" s="117"/>
+      <c r="O736" s="116"/>
+    </row>
+    <row r="737" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H737" s="117"/>
+      <c r="O737" s="116"/>
+    </row>
+    <row r="738" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H738" s="117"/>
+      <c r="O738" s="116"/>
+    </row>
+    <row r="739" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H739" s="117"/>
+      <c r="O739" s="116"/>
+    </row>
+    <row r="740" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H740" s="117"/>
+      <c r="O740" s="116"/>
+    </row>
+    <row r="741" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H741" s="117"/>
+      <c r="O741" s="116"/>
+    </row>
+    <row r="742" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H742" s="117"/>
+      <c r="O742" s="116"/>
+    </row>
+    <row r="743" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H743" s="117"/>
+      <c r="O743" s="116"/>
+    </row>
+    <row r="744" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H744" s="117"/>
+      <c r="O744" s="116"/>
+    </row>
+    <row r="745" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H745" s="117"/>
+      <c r="O745" s="116"/>
+    </row>
+    <row r="746" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H746" s="117"/>
+      <c r="O746" s="116"/>
+    </row>
+    <row r="747" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H747" s="117"/>
+      <c r="O747" s="116"/>
+    </row>
+    <row r="748" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H748" s="117"/>
+      <c r="O748" s="116"/>
+    </row>
+    <row r="749" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H749" s="117"/>
+      <c r="O749" s="116"/>
+    </row>
+    <row r="750" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H750" s="117"/>
+      <c r="O750" s="116"/>
+    </row>
+    <row r="751" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H751" s="117"/>
+      <c r="O751" s="116"/>
+    </row>
+    <row r="752" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H752" s="117"/>
+      <c r="O752" s="116"/>
+    </row>
+    <row r="753" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H753" s="117"/>
+      <c r="O753" s="116"/>
+    </row>
+    <row r="754" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H754" s="117"/>
+      <c r="O754" s="116"/>
+    </row>
+    <row r="755" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H755" s="117"/>
+      <c r="O755" s="116"/>
+    </row>
+    <row r="756" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H756" s="117"/>
+      <c r="O756" s="116"/>
+    </row>
+    <row r="757" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H757" s="117"/>
+      <c r="O757" s="116"/>
+    </row>
+    <row r="758" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H758" s="117"/>
+      <c r="O758" s="116"/>
+    </row>
+    <row r="759" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H759" s="117"/>
+      <c r="O759" s="116"/>
+    </row>
+    <row r="760" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H760" s="117"/>
+      <c r="O760" s="116"/>
+    </row>
+    <row r="761" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H761" s="117"/>
+      <c r="O761" s="116"/>
+    </row>
+    <row r="762" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H762" s="117"/>
+      <c r="O762" s="116"/>
+    </row>
+    <row r="763" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H763" s="117"/>
+      <c r="O763" s="116"/>
+    </row>
+    <row r="764" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H764" s="117"/>
+      <c r="O764" s="116"/>
+    </row>
+    <row r="765" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H765" s="117"/>
+      <c r="O765" s="116"/>
+    </row>
+    <row r="766" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H766" s="117"/>
+      <c r="O766" s="116"/>
+    </row>
+    <row r="767" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H767" s="117"/>
+      <c r="O767" s="116"/>
+    </row>
+    <row r="768" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H768" s="117"/>
+      <c r="O768" s="116"/>
+    </row>
+    <row r="769" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H769" s="117"/>
+      <c r="O769" s="116"/>
+    </row>
+    <row r="770" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H770" s="117"/>
+      <c r="O770" s="116"/>
+    </row>
+    <row r="771" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H771" s="117"/>
+      <c r="O771" s="116"/>
+    </row>
+    <row r="772" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H772" s="117"/>
+      <c r="O772" s="116"/>
+    </row>
+    <row r="773" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H773" s="117"/>
+      <c r="O773" s="116"/>
+    </row>
+    <row r="774" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H774" s="117"/>
+      <c r="O774" s="116"/>
+    </row>
+    <row r="775" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H775" s="117"/>
+      <c r="O775" s="116"/>
+    </row>
+    <row r="776" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H776" s="117"/>
+      <c r="O776" s="116"/>
+    </row>
+    <row r="777" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H777" s="117"/>
+      <c r="O777" s="116"/>
+    </row>
+    <row r="778" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H778" s="117"/>
+      <c r="O778" s="116"/>
+    </row>
+    <row r="779" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H779" s="117"/>
+      <c r="O779" s="116"/>
+    </row>
+    <row r="780" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H780" s="117"/>
+      <c r="O780" s="116"/>
+    </row>
+    <row r="781" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H781" s="117"/>
+      <c r="O781" s="116"/>
+    </row>
+    <row r="782" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H782" s="117"/>
+      <c r="O782" s="116"/>
+    </row>
+    <row r="783" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H783" s="117"/>
+      <c r="O783" s="116"/>
+    </row>
+    <row r="784" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H784" s="117"/>
+      <c r="O784" s="116"/>
+    </row>
+    <row r="785" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H785" s="117"/>
+      <c r="O785" s="116"/>
+    </row>
+    <row r="786" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H786" s="117"/>
+      <c r="O786" s="116"/>
+    </row>
+    <row r="787" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H787" s="117"/>
+      <c r="O787" s="116"/>
+    </row>
+    <row r="788" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H788" s="117"/>
+      <c r="O788" s="116"/>
+    </row>
+    <row r="789" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H789" s="117"/>
+      <c r="O789" s="116"/>
+    </row>
+    <row r="790" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H790" s="117"/>
+      <c r="O790" s="116"/>
+    </row>
+    <row r="791" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H791" s="117"/>
+      <c r="O791" s="116"/>
+    </row>
+    <row r="792" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H792" s="117"/>
+      <c r="O792" s="116"/>
+    </row>
+    <row r="793" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H793" s="117"/>
+      <c r="O793" s="116"/>
+    </row>
+    <row r="794" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H794" s="117"/>
+      <c r="O794" s="116"/>
+    </row>
+    <row r="795" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H795" s="117"/>
+      <c r="O795" s="116"/>
+    </row>
+    <row r="796" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H796" s="117"/>
+      <c r="O796" s="116"/>
+    </row>
+    <row r="797" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H797" s="117"/>
+      <c r="O797" s="116"/>
+    </row>
+    <row r="798" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H798" s="117"/>
+      <c r="O798" s="116"/>
+    </row>
+    <row r="799" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H799" s="117"/>
+      <c r="O799" s="116"/>
+    </row>
+    <row r="800" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H800" s="117"/>
+      <c r="O800" s="116"/>
+    </row>
+    <row r="801" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H801" s="117"/>
+      <c r="O801" s="116"/>
+    </row>
+    <row r="802" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H802" s="117"/>
+      <c r="O802" s="116"/>
+    </row>
+    <row r="803" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H803" s="117"/>
+      <c r="O803" s="116"/>
+    </row>
+    <row r="804" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H804" s="117"/>
+      <c r="O804" s="116"/>
+    </row>
+    <row r="805" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H805" s="117"/>
+      <c r="O805" s="116"/>
+    </row>
+    <row r="806" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H806" s="117"/>
+      <c r="O806" s="116"/>
+    </row>
+    <row r="807" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H807" s="117"/>
+      <c r="O807" s="116"/>
+    </row>
+    <row r="808" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H808" s="117"/>
+      <c r="O808" s="116"/>
+    </row>
+    <row r="809" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H809" s="117"/>
+      <c r="O809" s="116"/>
+    </row>
+    <row r="810" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H810" s="117"/>
+      <c r="O810" s="116"/>
+    </row>
+    <row r="811" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H811" s="117"/>
+      <c r="O811" s="116"/>
+    </row>
+    <row r="812" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H812" s="117"/>
+      <c r="O812" s="116"/>
+    </row>
+    <row r="813" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H813" s="117"/>
+      <c r="O813" s="116"/>
+    </row>
+    <row r="814" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H814" s="117"/>
+      <c r="O814" s="116"/>
+    </row>
+    <row r="815" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H815" s="117"/>
+      <c r="O815" s="116"/>
+    </row>
+    <row r="816" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H816" s="117"/>
+      <c r="O816" s="116"/>
+    </row>
+    <row r="817" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H817" s="117"/>
+      <c r="O817" s="116"/>
+    </row>
+    <row r="818" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H818" s="117"/>
+      <c r="O818" s="116"/>
+    </row>
+    <row r="819" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H819" s="117"/>
+      <c r="O819" s="116"/>
+    </row>
+    <row r="820" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H820" s="117"/>
+      <c r="O820" s="116"/>
+    </row>
+    <row r="821" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H821" s="117"/>
+      <c r="O821" s="116"/>
+    </row>
+    <row r="822" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H822" s="117"/>
+      <c r="O822" s="116"/>
+    </row>
+    <row r="823" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H823" s="117"/>
+      <c r="O823" s="116"/>
+    </row>
+    <row r="824" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H824" s="117"/>
+      <c r="O824" s="116"/>
+    </row>
+    <row r="825" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H825" s="117"/>
+      <c r="O825" s="116"/>
+    </row>
+    <row r="826" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H826" s="117"/>
+      <c r="O826" s="116"/>
+    </row>
+    <row r="827" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H827" s="117"/>
+      <c r="O827" s="116"/>
+    </row>
+    <row r="828" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H828" s="117"/>
+      <c r="O828" s="116"/>
+    </row>
+    <row r="829" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H829" s="117"/>
+      <c r="O829" s="116"/>
+    </row>
+    <row r="830" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H830" s="117"/>
+      <c r="O830" s="116"/>
+    </row>
+    <row r="831" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H831" s="117"/>
+      <c r="O831" s="116"/>
+    </row>
+    <row r="832" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H832" s="117"/>
+      <c r="O832" s="116"/>
+    </row>
+    <row r="833" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H833" s="117"/>
+      <c r="O833" s="116"/>
+    </row>
+    <row r="834" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H834" s="117"/>
+      <c r="O834" s="116"/>
+    </row>
+    <row r="835" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H835" s="117"/>
+      <c r="O835" s="116"/>
+    </row>
+    <row r="836" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H836" s="117"/>
+      <c r="O836" s="116"/>
+    </row>
+    <row r="837" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H837" s="117"/>
+      <c r="O837" s="116"/>
+    </row>
+    <row r="838" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H838" s="117"/>
+      <c r="O838" s="116"/>
+    </row>
+    <row r="839" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H839" s="117"/>
+      <c r="O839" s="116"/>
+    </row>
+    <row r="840" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H840" s="117"/>
+      <c r="O840" s="116"/>
+    </row>
+    <row r="841" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H841" s="117"/>
+      <c r="O841" s="116"/>
+    </row>
+    <row r="842" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H842" s="117"/>
+      <c r="O842" s="116"/>
+    </row>
+    <row r="843" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H843" s="117"/>
+      <c r="O843" s="116"/>
+    </row>
+    <row r="844" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H844" s="117"/>
+      <c r="O844" s="116"/>
+    </row>
+    <row r="845" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H845" s="117"/>
+      <c r="O845" s="116"/>
+    </row>
+    <row r="846" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H846" s="117"/>
+      <c r="O846" s="116"/>
+    </row>
+    <row r="847" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H847" s="117"/>
+      <c r="O847" s="116"/>
+    </row>
+    <row r="848" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H848" s="117"/>
+      <c r="O848" s="116"/>
+    </row>
+    <row r="849" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H849" s="117"/>
+      <c r="O849" s="116"/>
+    </row>
+    <row r="850" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H850" s="117"/>
+      <c r="O850" s="116"/>
+    </row>
+    <row r="851" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H851" s="117"/>
+      <c r="O851" s="116"/>
+    </row>
+    <row r="852" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H852" s="117"/>
+      <c r="O852" s="116"/>
+    </row>
+    <row r="853" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H853" s="117"/>
+      <c r="O853" s="116"/>
+    </row>
+    <row r="854" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H854" s="117"/>
+      <c r="O854" s="116"/>
+    </row>
+    <row r="855" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H855" s="117"/>
+      <c r="O855" s="116"/>
+    </row>
+    <row r="856" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H856" s="117"/>
+      <c r="O856" s="116"/>
+    </row>
+    <row r="857" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H857" s="117"/>
+      <c r="O857" s="116"/>
+    </row>
+    <row r="858" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H858" s="117"/>
+      <c r="O858" s="116"/>
+    </row>
+    <row r="859" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H859" s="117"/>
+      <c r="O859" s="116"/>
+    </row>
+    <row r="860" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H860" s="117"/>
+      <c r="O860" s="116"/>
+    </row>
+    <row r="861" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H861" s="117"/>
+      <c r="O861" s="116"/>
+    </row>
+    <row r="862" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H862" s="117"/>
+      <c r="O862" s="116"/>
+    </row>
+    <row r="863" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H863" s="117"/>
+      <c r="O863" s="116"/>
+    </row>
+    <row r="864" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H864" s="117"/>
+      <c r="O864" s="116"/>
+    </row>
+    <row r="865" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H865" s="117"/>
+      <c r="O865" s="116"/>
+    </row>
+    <row r="866" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H866" s="117"/>
+      <c r="O866" s="116"/>
+    </row>
+    <row r="867" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H867" s="117"/>
+      <c r="O867" s="116"/>
+    </row>
+    <row r="868" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H868" s="117"/>
+      <c r="O868" s="116"/>
+    </row>
+    <row r="869" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H869" s="117"/>
+      <c r="O869" s="116"/>
+    </row>
+    <row r="870" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H870" s="117"/>
+      <c r="O870" s="116"/>
+    </row>
+    <row r="871" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H871" s="117"/>
+      <c r="O871" s="116"/>
+    </row>
+    <row r="872" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H872" s="117"/>
+      <c r="O872" s="116"/>
+    </row>
+    <row r="873" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H873" s="117"/>
+      <c r="O873" s="116"/>
+    </row>
+    <row r="874" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H874" s="117"/>
+      <c r="O874" s="116"/>
+    </row>
+    <row r="875" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H875" s="117"/>
+      <c r="O875" s="116"/>
+    </row>
+    <row r="876" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H876" s="117"/>
+      <c r="O876" s="116"/>
+    </row>
+    <row r="877" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H877" s="117"/>
+      <c r="O877" s="116"/>
+    </row>
+    <row r="878" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H878" s="117"/>
+      <c r="O878" s="116"/>
+    </row>
+    <row r="879" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H879" s="117"/>
+      <c r="O879" s="116"/>
+    </row>
+    <row r="880" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H880" s="117"/>
+      <c r="O880" s="116"/>
+    </row>
+    <row r="881" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H881" s="117"/>
+      <c r="O881" s="116"/>
+    </row>
+    <row r="882" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H882" s="117"/>
+      <c r="O882" s="116"/>
+    </row>
+    <row r="883" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H883" s="117"/>
+      <c r="O883" s="116"/>
+    </row>
+    <row r="884" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H884" s="117"/>
+      <c r="O884" s="116"/>
+    </row>
+    <row r="885" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H885" s="117"/>
+      <c r="O885" s="116"/>
+    </row>
+    <row r="886" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H886" s="117"/>
+      <c r="O886" s="116"/>
+    </row>
+    <row r="887" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H887" s="117"/>
+      <c r="O887" s="116"/>
+    </row>
+    <row r="888" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H888" s="117"/>
+      <c r="O888" s="116"/>
+    </row>
+    <row r="889" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H889" s="117"/>
+      <c r="O889" s="116"/>
+    </row>
+    <row r="890" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H890" s="117"/>
+      <c r="O890" s="116"/>
+    </row>
+    <row r="891" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H891" s="117"/>
+      <c r="O891" s="116"/>
+    </row>
+    <row r="892" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H892" s="117"/>
+      <c r="O892" s="116"/>
+    </row>
+    <row r="893" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H893" s="117"/>
+      <c r="O893" s="116"/>
+    </row>
+    <row r="894" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H894" s="117"/>
+      <c r="O894" s="116"/>
+    </row>
+    <row r="895" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H895" s="117"/>
+      <c r="O895" s="116"/>
+    </row>
+    <row r="896" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H896" s="117"/>
+      <c r="O896" s="116"/>
+    </row>
+    <row r="897" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H897" s="117"/>
+      <c r="O897" s="116"/>
+    </row>
+    <row r="898" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H898" s="117"/>
+      <c r="O898" s="116"/>
+    </row>
+    <row r="899" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H899" s="117"/>
+      <c r="O899" s="116"/>
+    </row>
+    <row r="900" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H900" s="117"/>
+      <c r="O900" s="116"/>
+    </row>
+    <row r="901" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H901" s="117"/>
+      <c r="O901" s="116"/>
+    </row>
+    <row r="902" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H902" s="117"/>
+      <c r="O902" s="116"/>
+    </row>
+    <row r="903" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H903" s="117"/>
+      <c r="O903" s="116"/>
+    </row>
+    <row r="904" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H904" s="117"/>
+      <c r="O904" s="116"/>
+    </row>
+    <row r="905" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H905" s="117"/>
+      <c r="O905" s="116"/>
+    </row>
+    <row r="906" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H906" s="117"/>
+      <c r="O906" s="116"/>
+    </row>
+    <row r="907" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H907" s="117"/>
+      <c r="O907" s="116"/>
+    </row>
+    <row r="908" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H908" s="117"/>
+      <c r="O908" s="116"/>
+    </row>
+    <row r="909" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H909" s="117"/>
+      <c r="O909" s="116"/>
+    </row>
+    <row r="910" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H910" s="117"/>
+      <c r="O910" s="116"/>
+    </row>
+    <row r="911" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H911" s="117"/>
+      <c r="O911" s="116"/>
+    </row>
+    <row r="912" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H912" s="117"/>
+      <c r="O912" s="116"/>
+    </row>
+    <row r="913" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H913" s="117"/>
+      <c r="O913" s="116"/>
+    </row>
+    <row r="914" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H914" s="117"/>
+      <c r="O914" s="116"/>
+    </row>
+    <row r="915" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H915" s="117"/>
+      <c r="O915" s="116"/>
+    </row>
+    <row r="916" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H916" s="117"/>
+      <c r="O916" s="116"/>
+    </row>
+    <row r="917" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H917" s="117"/>
+      <c r="O917" s="116"/>
+    </row>
+    <row r="918" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H918" s="117"/>
+      <c r="O918" s="116"/>
+    </row>
+    <row r="919" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H919" s="117"/>
+      <c r="O919" s="116"/>
+    </row>
+    <row r="920" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H920" s="117"/>
+      <c r="O920" s="116"/>
+    </row>
+    <row r="921" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H921" s="117"/>
+      <c r="O921" s="116"/>
+    </row>
+    <row r="922" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H922" s="117"/>
+      <c r="O922" s="116"/>
+    </row>
+    <row r="923" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H923" s="117"/>
+      <c r="O923" s="116"/>
+    </row>
+    <row r="924" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H924" s="117"/>
+      <c r="O924" s="116"/>
+    </row>
+    <row r="925" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H925" s="117"/>
+      <c r="O925" s="116"/>
+    </row>
+    <row r="926" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H926" s="117"/>
+      <c r="O926" s="116"/>
+    </row>
+    <row r="927" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H927" s="117"/>
+      <c r="O927" s="116"/>
+    </row>
+    <row r="928" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H928" s="117"/>
+      <c r="O928" s="116"/>
+    </row>
+    <row r="929" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H929" s="117"/>
+      <c r="O929" s="116"/>
+    </row>
+    <row r="930" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H930" s="117"/>
+      <c r="O930" s="116"/>
+    </row>
+    <row r="931" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H931" s="117"/>
+      <c r="O931" s="116"/>
+    </row>
+    <row r="932" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H932" s="117"/>
+      <c r="O932" s="116"/>
+    </row>
+    <row r="933" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H933" s="117"/>
+      <c r="O933" s="116"/>
+    </row>
+    <row r="934" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H934" s="117"/>
+      <c r="O934" s="116"/>
+    </row>
+    <row r="935" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H935" s="117"/>
+      <c r="O935" s="116"/>
+    </row>
+    <row r="936" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H936" s="117"/>
+      <c r="O936" s="116"/>
+    </row>
+    <row r="937" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H937" s="117"/>
+      <c r="O937" s="116"/>
+    </row>
+    <row r="938" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H938" s="117"/>
+      <c r="O938" s="116"/>
+    </row>
+    <row r="939" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H939" s="117"/>
+      <c r="O939" s="116"/>
+    </row>
+    <row r="940" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H940" s="117"/>
+      <c r="O940" s="116"/>
+    </row>
+    <row r="941" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H941" s="117"/>
+      <c r="O941" s="116"/>
+    </row>
+    <row r="942" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H942" s="117"/>
+      <c r="O942" s="116"/>
+    </row>
+    <row r="943" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H943" s="117"/>
+      <c r="O943" s="116"/>
+    </row>
+    <row r="944" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H944" s="117"/>
+      <c r="O944" s="116"/>
+    </row>
+    <row r="945" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H945" s="117"/>
+      <c r="O945" s="116"/>
+    </row>
+    <row r="946" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H946" s="117"/>
+      <c r="O946" s="116"/>
+    </row>
+    <row r="947" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H947" s="117"/>
+      <c r="O947" s="116"/>
+    </row>
+    <row r="948" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H948" s="117"/>
+      <c r="O948" s="116"/>
+    </row>
+    <row r="949" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H949" s="117"/>
+      <c r="O949" s="116"/>
+    </row>
+    <row r="950" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H950" s="117"/>
+      <c r="O950" s="116"/>
+    </row>
+    <row r="951" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H951" s="117"/>
+      <c r="O951" s="116"/>
+    </row>
+    <row r="952" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H952" s="117"/>
+      <c r="O952" s="116"/>
+    </row>
+    <row r="953" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H953" s="117"/>
+      <c r="O953" s="116"/>
+    </row>
+    <row r="954" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H954" s="117"/>
+      <c r="O954" s="116"/>
+    </row>
+    <row r="955" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H955" s="117"/>
+      <c r="O955" s="116"/>
+    </row>
+    <row r="956" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H956" s="117"/>
+      <c r="O956" s="116"/>
+    </row>
+    <row r="957" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H957" s="117"/>
+      <c r="O957" s="116"/>
+    </row>
+    <row r="958" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H958" s="117"/>
+      <c r="O958" s="116"/>
+    </row>
+    <row r="959" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H959" s="117"/>
+      <c r="O959" s="116"/>
+    </row>
+    <row r="960" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H960" s="117"/>
+      <c r="O960" s="116"/>
+    </row>
+    <row r="961" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H961" s="117"/>
+      <c r="O961" s="116"/>
+    </row>
+    <row r="962" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H962" s="117"/>
+      <c r="O962" s="116"/>
+    </row>
+    <row r="963" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H963" s="117"/>
+      <c r="O963" s="116"/>
+    </row>
+    <row r="964" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H964" s="117"/>
+      <c r="O964" s="116"/>
+    </row>
+    <row r="965" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H965" s="117"/>
+      <c r="O965" s="116"/>
+    </row>
+    <row r="966" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H966" s="117"/>
+      <c r="O966" s="116"/>
+    </row>
+    <row r="967" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H967" s="117"/>
+      <c r="O967" s="116"/>
+    </row>
+    <row r="968" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H968" s="117"/>
+      <c r="O968" s="116"/>
+    </row>
+    <row r="969" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H969" s="117"/>
+      <c r="O969" s="116"/>
+    </row>
+    <row r="970" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H970" s="117"/>
+      <c r="O970" s="116"/>
+    </row>
+    <row r="971" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H971" s="117"/>
+      <c r="O971" s="116"/>
+    </row>
+    <row r="972" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H972" s="117"/>
+      <c r="O972" s="116"/>
+    </row>
+    <row r="973" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H973" s="117"/>
+      <c r="O973" s="116"/>
+    </row>
+    <row r="974" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H974" s="117"/>
+      <c r="O974" s="116"/>
+    </row>
+    <row r="975" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H975" s="117"/>
+      <c r="O975" s="116"/>
+    </row>
+    <row r="976" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H976" s="117"/>
+      <c r="O976" s="116"/>
+    </row>
+    <row r="977" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H977" s="117"/>
+      <c r="O977" s="116"/>
+    </row>
+    <row r="978" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H978" s="117"/>
+      <c r="O978" s="116"/>
+    </row>
+    <row r="979" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H979" s="117"/>
+      <c r="O979" s="116"/>
+    </row>
+    <row r="980" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H980" s="117"/>
+      <c r="O980" s="116"/>
+    </row>
+    <row r="981" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H981" s="117"/>
+      <c r="O981" s="116"/>
+    </row>
+    <row r="982" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H982" s="117"/>
+      <c r="O982" s="116"/>
+    </row>
+    <row r="983" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H983" s="117"/>
+      <c r="O983" s="116"/>
+    </row>
+    <row r="984" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H984" s="117"/>
+      <c r="O984" s="116"/>
+    </row>
+    <row r="985" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H985" s="117"/>
+      <c r="O985" s="116"/>
+    </row>
+    <row r="986" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H986" s="117"/>
+      <c r="O986" s="116"/>
+    </row>
+    <row r="987" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H987" s="117"/>
+      <c r="O987" s="116"/>
+    </row>
+    <row r="988" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H988" s="117"/>
+      <c r="O988" s="116"/>
+    </row>
+    <row r="989" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H989" s="117"/>
+      <c r="O989" s="116"/>
+    </row>
+    <row r="990" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H990" s="117"/>
+      <c r="O990" s="116"/>
+    </row>
+    <row r="991" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H991" s="117"/>
+      <c r="O991" s="116"/>
+    </row>
+    <row r="992" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H992" s="117"/>
+      <c r="O992" s="116"/>
+    </row>
+    <row r="993" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H993" s="117"/>
+      <c r="O993" s="116"/>
+    </row>
+    <row r="994" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H994" s="117"/>
+      <c r="O994" s="116"/>
+    </row>
+    <row r="995" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H995" s="117"/>
+      <c r="O995" s="116"/>
+    </row>
+    <row r="996" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H996" s="117"/>
+      <c r="O996" s="116"/>
+    </row>
+    <row r="997" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H997" s="117"/>
+      <c r="O997" s="116"/>
+    </row>
+    <row r="998" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H998" s="117"/>
+      <c r="O998" s="116"/>
+    </row>
+    <row r="999" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H999" s="117"/>
+      <c r="O999" s="116"/>
+    </row>
+    <row r="1000" spans="8:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1000" s="117"/>
+      <c r="O1000" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="C35:M35"/>
+    <mergeCell ref="B38:M42"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8988AF9C-C230-4988-B181-0C772662D251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFB0E0E-C06E-4B63-84EF-5A1CCE89736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -129,9 +129,6 @@
     <t xml:space="preserve">Ingreso pago por expensas </t>
   </si>
   <si>
-    <t xml:space="preserve">PREVISION ORDINARIA </t>
-  </si>
-  <si>
     <t>SUELDO SRA. FERNANDA</t>
   </si>
   <si>
@@ -456,6 +453,9 @@
   </si>
   <si>
     <t>EDESUR</t>
+  </si>
+  <si>
+    <t>PREVISION EDESUR ORDINARIA - DEBIDO A LA NUEVA FORMA DE FACTURAR DE EDESUR</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1023,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1299,6 +1299,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1780,7 +1789,7 @@
       <c r="C7" s="29"/>
       <c r="D7" s="29"/>
       <c r="E7" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="29"/>
       <c r="G7" s="30"/>
@@ -1848,7 +1857,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="38"/>
       <c r="C13" s="38"/>
@@ -1863,7 +1872,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="160"/>
       <c r="C14" s="160"/>
@@ -1905,7 +1914,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="38"/>
       <c r="C17" s="38"/>
@@ -1999,7 +2008,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="161"/>
       <c r="C24" s="161"/>
@@ -2013,7 +2022,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
@@ -2035,7 +2044,7 @@
       <c r="G26" s="47"/>
       <c r="H26" s="42"/>
       <c r="K26" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2094,7 +2103,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="40"/>
@@ -2107,7 +2116,7 @@
       </c>
       <c r="I31" s="19"/>
       <c r="K31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2138,7 +2147,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="38"/>
       <c r="C34" s="38"/>
@@ -2165,17 +2174,19 @@
         <v>816407.78</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="34"/>
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="176" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="177"/>
+      <c r="C36" s="177"/>
+      <c r="D36" s="177"/>
+      <c r="E36" s="177"/>
+      <c r="F36" s="177"/>
+      <c r="G36" s="178"/>
+      <c r="H36" s="34">
+        <v>1938740</v>
+      </c>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
     </row>
@@ -2191,7 +2202,7 @@
       <c r="G37" s="33"/>
       <c r="H37" s="34">
         <f>H35+H36</f>
-        <v>816407.78</v>
+        <v>2755147.7800000003</v>
       </c>
       <c r="I37" s="22"/>
     </row>
@@ -2252,7 +2263,7 @@
     </row>
     <row r="43" spans="1:10" ht="199.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="163" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="163"/>
       <c r="C43" s="163"/>
@@ -2407,7 +2418,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -2422,7 +2433,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -2438,7 +2449,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -2453,7 +2464,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -2489,7 +2500,7 @@
       <c r="H62" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A39:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A12:H12"/>
@@ -2502,6 +2513,7 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A43:H50"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2559,7 +2571,7 @@
       <c r="G2" s="52"/>
       <c r="H2" s="52"/>
       <c r="I2" s="96" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O2" s="86"/>
     </row>
@@ -2570,19 +2582,19 @@
       <c r="F3" s="52"/>
       <c r="G3" s="52"/>
       <c r="I3" s="95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J3" s="94"/>
       <c r="O3" s="86"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F4" s="52"/>
       <c r="G4" s="52"/>
       <c r="I4" s="92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J4" s="165">
         <v>1153202676</v>
@@ -2595,7 +2607,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="93"/>
       <c r="F5" s="52"/>
@@ -2619,10 +2631,10 @@
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="88"/>
       <c r="B7" s="87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="90">
-        <v>816407.78</v>
+        <v>2755147.7800000003</v>
       </c>
       <c r="D7" s="89"/>
       <c r="F7" s="52"/>
@@ -2634,7 +2646,7 @@
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="88"/>
       <c r="B8" s="87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="87"/>
       <c r="D8" s="87"/>
@@ -2663,47 +2675,47 @@
     </row>
     <row r="10" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E10" s="77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G10" s="77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10" s="77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="77"/>
       <c r="J10" s="76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10" s="76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L10" s="76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M10" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N10" s="76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O10" s="76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2711,10 +2723,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="68"/>
       <c r="E11" s="75">
@@ -2743,7 +2755,7 @@
       </c>
       <c r="M11" s="63">
         <f>C7*E11/100</f>
-        <v>40003.981220000001</v>
+        <v>135002.24122000003</v>
       </c>
       <c r="N11" s="63">
         <f>C8*E11/100</f>
@@ -2751,7 +2763,7 @@
       </c>
       <c r="O11" s="62">
         <f>K11+M11+N11+L11</f>
-        <v>157788.65150008001</v>
+        <v>252786.91150008002</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2759,13 +2771,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="67">
         <v>3.89</v>
@@ -2795,7 +2807,7 @@
       </c>
       <c r="M12" s="63">
         <f>C7*E12/100</f>
-        <v>31758.262642000002</v>
+        <v>107175.24864200002</v>
       </c>
       <c r="N12" s="63">
         <f>C8*E12/100</f>
@@ -2803,7 +2815,7 @@
       </c>
       <c r="O12" s="62">
         <f t="shared" ref="O12:O34" si="2">K12+M12+N12+L12</f>
-        <v>1761880.0245966709</v>
+        <v>1837297.0105966707</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2811,13 +2823,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" s="71">
         <v>4</v>
@@ -2850,7 +2862,7 @@
       </c>
       <c r="M13" s="63">
         <f>C7*E13/100</f>
-        <v>32656.3112</v>
+        <v>110205.91120000002</v>
       </c>
       <c r="N13" s="63">
         <f>C8*E13/100</f>
@@ -2858,7 +2870,7 @@
       </c>
       <c r="O13" s="62">
         <f t="shared" si="2"/>
-        <v>65547.165072000003</v>
+        <v>143096.76507200001</v>
       </c>
       <c r="Q13" s="74"/>
     </row>
@@ -2867,13 +2879,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="71">
         <v>4.9000000000000004</v>
@@ -2906,7 +2918,7 @@
       </c>
       <c r="M14" s="63">
         <f>C7*E14/100</f>
-        <v>40003.981220000001</v>
+        <v>135002.24122000003</v>
       </c>
       <c r="N14" s="63">
         <f>C8*E14/100</f>
@@ -2914,7 +2926,7 @@
       </c>
       <c r="O14" s="62">
         <f t="shared" si="2"/>
-        <v>108904.98571319973</v>
+        <v>203903.24571319975</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -2922,13 +2934,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" s="67">
         <v>3.89</v>
@@ -2961,7 +2973,7 @@
       </c>
       <c r="M15" s="63">
         <f>C7*E15/100</f>
-        <v>31758.262642000002</v>
+        <v>107175.24864200002</v>
       </c>
       <c r="N15" s="63">
         <f>C8*E15/100</f>
@@ -2969,7 +2981,7 @@
       </c>
       <c r="O15" s="62">
         <f t="shared" si="2"/>
-        <v>95248.864282520037</v>
+        <v>170665.85028252006</v>
       </c>
       <c r="Q15" s="1"/>
     </row>
@@ -2978,13 +2990,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="71">
         <v>4</v>
@@ -3017,7 +3029,7 @@
       </c>
       <c r="M16" s="63">
         <f>C7*E16/100</f>
-        <v>32656.3112</v>
+        <v>110205.91120000002</v>
       </c>
       <c r="N16" s="63">
         <f>C8*E16/100</f>
@@ -3025,7 +3037,7 @@
       </c>
       <c r="O16" s="62">
         <f t="shared" si="2"/>
-        <v>255521.5011626831</v>
+        <v>333071.1011626831</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3033,13 +3045,13 @@
         <v>7</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="71">
         <v>4.9000000000000004</v>
@@ -3072,7 +3084,7 @@
       </c>
       <c r="M17" s="63">
         <f>C7*E17/100</f>
-        <v>40003.981220000001</v>
+        <v>135002.24122000003</v>
       </c>
       <c r="N17" s="63">
         <f>C8*E17/100</f>
@@ -3080,7 +3092,7 @@
       </c>
       <c r="O17" s="62">
         <f t="shared" si="2"/>
-        <v>109289.48371319994</v>
+        <v>204287.74371319998</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -3088,10 +3100,10 @@
         <v>8</v>
       </c>
       <c r="B18" s="69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D18" s="68"/>
       <c r="E18" s="67">
@@ -3125,7 +3137,7 @@
       </c>
       <c r="M18" s="63">
         <f>C7*E18/100</f>
-        <v>31758.262642000002</v>
+        <v>107175.24864200002</v>
       </c>
       <c r="N18" s="63">
         <f>C8*E18/100</f>
@@ -3133,7 +3145,7 @@
       </c>
       <c r="O18" s="62">
         <f t="shared" si="2"/>
-        <v>66669.409282520035</v>
+        <v>142086.39528252004</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3141,13 +3153,13 @@
         <v>9</v>
       </c>
       <c r="B19" s="69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="71">
         <v>4</v>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="M19" s="63">
         <f>C7*E19/100</f>
-        <v>32656.3112</v>
+        <v>110205.91120000002</v>
       </c>
       <c r="N19" s="63">
         <f>C8*E19/100</f>
@@ -3188,7 +3200,7 @@
       </c>
       <c r="O19" s="62">
         <f t="shared" si="2"/>
-        <v>77175.88507199999</v>
+        <v>154725.48507200001</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -3196,10 +3208,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="68"/>
       <c r="E20" s="67">
@@ -3230,7 +3242,7 @@
       </c>
       <c r="M20" s="63">
         <f>C7*E20/100</f>
-        <v>103357.22494800002</v>
+        <v>348801.7089480001</v>
       </c>
       <c r="N20" s="63">
         <f>C8*E20/100</f>
@@ -3238,7 +3250,7 @@
       </c>
       <c r="O20" s="62">
         <f t="shared" si="2"/>
-        <v>395266.24926347198</v>
+        <v>640710.7332634721</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3246,13 +3258,13 @@
         <v>11</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="67">
         <v>7.75</v>
@@ -3282,7 +3294,7 @@
       </c>
       <c r="M21" s="63">
         <f>C7*E21/100</f>
-        <v>63271.60295</v>
+        <v>213523.95295000001</v>
       </c>
       <c r="N21" s="63">
         <f>C8*E21/100</f>
@@ -3290,7 +3302,7 @@
       </c>
       <c r="O21" s="62">
         <f t="shared" si="2"/>
-        <v>215067.0804338</v>
+        <v>365319.43043380004</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3298,10 +3310,10 @@
         <v>12</v>
       </c>
       <c r="B22" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="68"/>
       <c r="E22" s="67">
@@ -3332,7 +3344,7 @@
       </c>
       <c r="M22" s="63">
         <f>C7*E22/100</f>
-        <v>61312.224277999994</v>
+        <v>206911.59827800002</v>
       </c>
       <c r="N22" s="63">
         <f>C8*E22/100</f>
@@ -3340,7 +3352,7 @@
       </c>
       <c r="O22" s="62">
         <f t="shared" si="2"/>
-        <v>193167.11452359208</v>
+        <v>338766.48852359212</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3348,10 +3360,10 @@
         <v>13</v>
       </c>
       <c r="B23" s="69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D23" s="68"/>
       <c r="E23" s="67">
@@ -3382,7 +3394,7 @@
       </c>
       <c r="M23" s="63">
         <f>C7*E23/100</f>
-        <v>36330.146210000006</v>
+        <v>122604.07621000001</v>
       </c>
       <c r="N23" s="63">
         <f>C8*E23/100</f>
@@ -3390,7 +3402,7 @@
       </c>
       <c r="O23" s="62">
         <f t="shared" si="2"/>
-        <v>550576.95975723653</v>
+        <v>636850.88975723647</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3398,10 +3410,10 @@
         <v>14</v>
       </c>
       <c r="B24" s="69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" s="68"/>
       <c r="E24" s="67">
@@ -3432,7 +3444,7 @@
       </c>
       <c r="M24" s="63">
         <f>C7*E24/100</f>
-        <v>50372.360026000002</v>
+        <v>169992.61802600001</v>
       </c>
       <c r="N24" s="63">
         <f>C8*E24/100</f>
@@ -3440,7 +3452,7 @@
       </c>
       <c r="O24" s="62">
         <f t="shared" si="2"/>
-        <v>189627.00655826417</v>
+        <v>309247.26455826417</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3448,13 +3460,13 @@
         <v>15</v>
       </c>
       <c r="B25" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="67">
         <v>4.45</v>
@@ -3486,7 +3498,7 @@
       </c>
       <c r="M25" s="63">
         <f>C7*E25/100+1</f>
-        <v>36331.146210000006</v>
+        <v>122605.07621000001</v>
       </c>
       <c r="N25" s="63">
         <f>C8*E25/100</f>
@@ -3494,7 +3506,7 @@
       </c>
       <c r="O25" s="62">
         <f t="shared" si="2"/>
-        <v>724114.62625719327</v>
+        <v>810388.55625719321</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3502,13 +3514,13 @@
         <v>16</v>
       </c>
       <c r="B26" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" s="67">
         <v>9.19</v>
@@ -3540,7 +3552,7 @@
       </c>
       <c r="M26" s="63">
         <f>C7*E26/100+1</f>
-        <v>75028.874982000008</v>
+        <v>253199.08098200001</v>
       </c>
       <c r="N26" s="63">
         <f>C8*E26/100</f>
@@ -3548,7 +3560,7 @@
       </c>
       <c r="O26" s="62">
         <f t="shared" si="2"/>
-        <v>2080234.7689409959</v>
+        <v>2258404.9749409957</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3556,13 +3568,13 @@
         <v>17</v>
       </c>
       <c r="B27" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" s="67">
         <v>1.18</v>
@@ -3592,7 +3604,7 @@
       </c>
       <c r="M27" s="63">
         <f>C7*E27/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N27" s="63">
         <f>C8*E27/100</f>
@@ -3600,7 +3612,7 @@
       </c>
       <c r="O27" s="62">
         <f t="shared" si="2"/>
-        <v>29891.880891856003</v>
+        <v>52769.012891856</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3608,10 +3620,10 @@
         <v>18</v>
       </c>
       <c r="B28" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="68"/>
       <c r="E28" s="67">
@@ -3642,7 +3654,7 @@
       </c>
       <c r="M28" s="63">
         <f>C7*E28/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N28" s="63">
         <f>C8*E28/100</f>
@@ -3650,7 +3662,7 @@
       </c>
       <c r="O28" s="62">
         <f t="shared" si="2"/>
-        <v>291094.68188228714</v>
+        <v>313971.81388228718</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3658,10 +3670,10 @@
         <v>19</v>
       </c>
       <c r="B29" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="68"/>
       <c r="E29" s="67">
@@ -3692,7 +3704,7 @@
       </c>
       <c r="M29" s="63">
         <f>C7*E29/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N29" s="63">
         <f>C8*E29/100</f>
@@ -3700,7 +3712,7 @@
       </c>
       <c r="O29" s="62">
         <f t="shared" si="2"/>
-        <v>291094.68188228714</v>
+        <v>313971.81388228718</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3708,10 +3720,10 @@
         <v>20</v>
       </c>
       <c r="B30" s="69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="68"/>
       <c r="E30" s="67">
@@ -3745,7 +3757,7 @@
       </c>
       <c r="M30" s="63">
         <f>C7*E30/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N30" s="63">
         <f>C8*E30/100</f>
@@ -3753,7 +3765,7 @@
       </c>
       <c r="O30" s="62">
         <f t="shared" si="2"/>
-        <v>16985.585196239997</v>
+        <v>39862.717196240003</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3761,10 +3773,10 @@
         <v>21</v>
       </c>
       <c r="B31" s="69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="68"/>
       <c r="E31" s="67">
@@ -3795,7 +3807,7 @@
       </c>
       <c r="M31" s="63">
         <f>C7*E31/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N31" s="63">
         <f>C8*E31/100</f>
@@ -3803,7 +3815,7 @@
       </c>
       <c r="O31" s="62">
         <f t="shared" si="2"/>
-        <v>29891.880891856003</v>
+        <v>52769.012891856</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3811,10 +3823,10 @@
         <v>22</v>
       </c>
       <c r="B32" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="68"/>
       <c r="E32" s="67">
@@ -3848,7 +3860,7 @@
       </c>
       <c r="M32" s="63">
         <f>C7*E32/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N32" s="63">
         <f>C8*E32/100</f>
@@ -3856,7 +3868,7 @@
       </c>
       <c r="O32" s="62">
         <f t="shared" si="2"/>
-        <v>16985.585196239997</v>
+        <v>39862.717196240003</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -3864,10 +3876,10 @@
         <v>23</v>
       </c>
       <c r="B33" s="69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="68"/>
       <c r="E33" s="67">
@@ -3898,7 +3910,7 @@
       </c>
       <c r="M33" s="63">
         <f>C7*E33/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N33" s="63">
         <f>C8*E33/100</f>
@@ -3906,7 +3918,7 @@
       </c>
       <c r="O33" s="62">
         <f t="shared" si="2"/>
-        <v>70726.133986768007</v>
+        <v>93603.265986768005</v>
       </c>
       <c r="P33" s="1"/>
     </row>
@@ -3915,10 +3927,10 @@
         <v>24</v>
       </c>
       <c r="B34" s="69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" s="68"/>
       <c r="E34" s="67">
@@ -3949,7 +3961,7 @@
       </c>
       <c r="M34" s="63">
         <f>C7*E34/100+1</f>
-        <v>9634.6118040000001</v>
+        <v>32511.743804000002</v>
       </c>
       <c r="N34" s="63">
         <f>C8*E34/100</f>
@@ -3957,12 +3969,12 @@
       </c>
       <c r="O34" s="62">
         <f t="shared" si="2"/>
-        <v>29891.880891856003</v>
+        <v>52769.012891856</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="53" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A35" s="164" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B35" s="164"/>
       <c r="C35" s="164"/>
@@ -3995,7 +4007,7 @@
       <c r="L35" s="57"/>
       <c r="M35" s="56">
         <f>SUM(M11:M34)</f>
-        <v>816336.13922199979</v>
+        <v>2754882.2652219995</v>
       </c>
       <c r="N35" s="55">
         <f>SUM(N11:N34)</f>
@@ -4003,7 +4015,7 @@
       </c>
       <c r="O35" s="54">
         <f>SUM(O11:O34)</f>
-        <v>7822642.0869488185</v>
+        <v>9761188.2129488159</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -4063,7 +4075,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="170" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="171"/>
       <c r="C1" s="171"/>
@@ -4109,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="107" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" s="107"/>
       <c r="F3" s="107"/>
@@ -4127,13 +4139,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="147" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="147" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="107" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="107"/>
       <c r="F4" s="107"/>
@@ -4149,13 +4161,13 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="147" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="147" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E5" s="107"/>
       <c r="F5" s="107"/>
@@ -4171,13 +4183,13 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" s="147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="107"/>
       <c r="F6" s="107"/>
@@ -4193,10 +4205,10 @@
     </row>
     <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="148" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="148" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C7" s="149">
         <v>78050</v>
@@ -4216,7 +4228,7 @@
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="148"/>
       <c r="B8" s="147" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="146">
         <v>1030338.54</v>
@@ -4236,51 +4248,51 @@
     </row>
     <row r="9" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B9" s="142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="138" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="142" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G9" s="141" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H9" s="140" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I9" s="141" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J9" s="138" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K9" s="138" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L9" s="140">
         <f>C8-J34</f>
         <v>622963.84679999994</v>
       </c>
       <c r="M9" s="138" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N9" s="139"/>
       <c r="O9" s="138" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P9" s="138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -4291,10 +4303,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" s="119">
         <v>4.9000000000000004</v>
@@ -4348,7 +4360,7 @@
         <v>1240</v>
       </c>
       <c r="V10" s="69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -4359,10 +4371,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="124" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="124" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="124">
         <v>3.89</v>
@@ -4418,7 +4430,7 @@
       </c>
       <c r="U11" s="100"/>
       <c r="V11" s="69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -4429,10 +4441,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="113">
         <v>4</v>
@@ -4480,7 +4492,7 @@
         <v>998.70958514827259</v>
       </c>
       <c r="V12" s="69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -4491,10 +4503,10 @@
         <v>4</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" s="113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="113">
         <v>4.9000000000000004</v>
@@ -4541,7 +4553,7 @@
         <v>4807.9054381490623</v>
       </c>
       <c r="V13" s="69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -4552,10 +4564,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E14" s="113">
         <v>3.89</v>
@@ -4605,7 +4617,7 @@
         <v>2540.8200000000002</v>
       </c>
       <c r="V14" s="73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4616,10 +4628,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" s="115" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="115">
         <v>4</v>
@@ -4667,7 +4679,7 @@
         <v>3172.3716234121598</v>
       </c>
       <c r="V15" s="69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Y15" s="130"/>
     </row>
@@ -4679,10 +4691,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="119" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" s="119">
         <v>4.9000000000000004</v>
@@ -4729,7 +4741,7 @@
         <v>4856.0784887268273</v>
       </c>
       <c r="V16" s="69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -4740,10 +4752,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="119" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="119">
         <v>3.89</v>
@@ -4790,7 +4802,7 @@
         <v>1337.6833678721316</v>
       </c>
       <c r="V17" s="69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -4801,10 +4813,10 @@
         <v>9</v>
       </c>
       <c r="C18" s="113" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="113" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="113">
         <v>4</v>
@@ -4852,7 +4864,7 @@
         <v>2455.6506270116352</v>
       </c>
       <c r="V18" s="69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -4863,10 +4875,10 @@
         <v>10</v>
       </c>
       <c r="C19" s="113" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="113" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="113">
         <v>12.66</v>
@@ -4913,7 +4925,7 @@
         <v>9344.3968596284758</v>
       </c>
       <c r="V19" s="69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -4924,10 +4936,10 @@
         <v>11</v>
       </c>
       <c r="C20" s="113" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="113">
         <v>7.75</v>
@@ -4975,7 +4987,7 @@
         <v>2349.9049062312297</v>
       </c>
       <c r="V20" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4986,10 +4998,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="113" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="113">
         <v>7.51</v>
@@ -5040,7 +5052,7 @@
         <v>31.300000000001091</v>
       </c>
       <c r="V21" s="69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5051,10 +5063,10 @@
         <v>13</v>
       </c>
       <c r="C22" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D22" s="113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" s="113">
         <v>4.45</v>
@@ -5106,7 +5118,7 @@
         <v>300</v>
       </c>
       <c r="V22" s="69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5117,10 +5129,10 @@
         <v>14</v>
       </c>
       <c r="C23" s="113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="113" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="113">
         <v>6.17</v>
@@ -5167,7 +5179,7 @@
         <v>4176.8384755807183</v>
       </c>
       <c r="V23" s="69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5178,10 +5190,10 @@
         <v>15</v>
       </c>
       <c r="C24" s="113" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D24" s="113" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" s="113">
         <v>4.45</v>
@@ -5229,7 +5241,7 @@
         <v>2114.914415608107</v>
       </c>
       <c r="V24" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5240,10 +5252,10 @@
         <v>16</v>
       </c>
       <c r="C25" s="113" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" s="113" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" s="113">
         <v>9.19</v>
@@ -5290,7 +5302,7 @@
         <v>1573.2613347218255</v>
       </c>
       <c r="V25" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5301,10 +5313,10 @@
         <v>17</v>
       </c>
       <c r="C26" s="113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="113">
         <v>1.18</v>
@@ -5348,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5359,10 +5371,10 @@
         <v>18</v>
       </c>
       <c r="C27" s="124" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="124" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" s="124">
         <v>1.18</v>
@@ -5406,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5417,10 +5429,10 @@
         <v>19</v>
       </c>
       <c r="C28" s="124" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="124" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" s="124">
         <v>1.18</v>
@@ -5464,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5475,10 +5487,10 @@
         <v>20</v>
       </c>
       <c r="C29" s="113" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="113">
         <v>1.18</v>
@@ -5522,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5533,10 +5545,10 @@
         <v>21</v>
       </c>
       <c r="C30" s="119" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="120" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" s="119">
         <v>1.18</v>
@@ -5580,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5591,10 +5603,10 @@
         <v>22</v>
       </c>
       <c r="C31" s="119" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="119" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" s="119">
         <v>1.18</v>
@@ -5638,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5649,10 +5661,10 @@
         <v>23</v>
       </c>
       <c r="C32" s="115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="115">
         <v>1.18</v>
@@ -5696,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -5707,10 +5719,10 @@
         <v>24</v>
       </c>
       <c r="C33" s="113" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" s="114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" s="113">
         <v>1.18</v>
@@ -5754,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
@@ -5796,10 +5808,10 @@
     </row>
     <row r="35" spans="1:22" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C35" s="173" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D35" s="171"/>
       <c r="E35" s="171"/>
@@ -5835,7 +5847,7 @@
     </row>
     <row r="38" spans="1:22" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" s="175"/>
       <c r="D38" s="175"/>

--- a/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
+++ b/2026/FLORES DE ESTRADA/ENERO/RESUMEN-Enero-ESTRADA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\FLORES DE ESTRADA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\FLORES DE ESTRADA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFB0E0E-C06E-4B63-84EF-5A1CCE89736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318F392C-D8EC-4310-90CD-2C0A5A8594AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1268,6 +1271,15 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1299,15 +1311,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2175,15 +2178,15 @@
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="176" t="s">
+      <c r="A36" s="164" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="177"/>
-      <c r="C36" s="177"/>
-      <c r="D36" s="177"/>
-      <c r="E36" s="177"/>
-      <c r="F36" s="177"/>
-      <c r="G36" s="178"/>
+      <c r="B36" s="165"/>
+      <c r="C36" s="165"/>
+      <c r="D36" s="165"/>
+      <c r="E36" s="165"/>
+      <c r="F36" s="165"/>
+      <c r="G36" s="166"/>
       <c r="H36" s="34">
         <v>1938740</v>
       </c>
@@ -2400,7 +2403,7 @@
       <c r="G55" s="12"/>
       <c r="H55" s="42">
         <f>Planilla!G35</f>
-        <v>465293.924956</v>
+        <v>617080.68969600019</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2427,7 +2430,8 @@
       <c r="F57" s="12"/>
       <c r="G57" s="12"/>
       <c r="H57" s="36">
-        <v>-2892581.23</v>
+        <f>-(27043+5588+28371+29512+24306+191627+128319+383427)</f>
+        <v>-818193</v>
       </c>
       <c r="I57" s="18"/>
     </row>
@@ -2486,7 +2490,7 @@
       <c r="G61" s="15"/>
       <c r="H61" s="17">
         <f>SUM(H54:H60)</f>
-        <v>516455.98903652071</v>
+        <v>2742630.98377652</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2546,24 +2550,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="167" t="str">
+      <c r="A1" s="170" t="str">
         <f>RESUMEN!E7</f>
         <v>PERIODO: ENERO - Vto. 28/02</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
-      <c r="J1" s="168"/>
-      <c r="K1" s="168"/>
-      <c r="L1" s="168"/>
-      <c r="M1" s="168"/>
-      <c r="N1" s="168"/>
-      <c r="O1" s="169"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="172"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="97"/>
@@ -2596,14 +2600,14 @@
       <c r="I4" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="165">
+      <c r="J4" s="168">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="165"/>
-      <c r="L4" s="165"/>
-      <c r="M4" s="165"/>
-      <c r="N4" s="165"/>
-      <c r="O4" s="166"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="168"/>
+      <c r="M4" s="168"/>
+      <c r="N4" s="168"/>
+      <c r="O4" s="169"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="88" t="s">
@@ -3040,7 +3044,7 @@
         <v>333071.1011626831</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="69">
         <v>7</v>
       </c>
@@ -3095,7 +3099,7 @@
         <v>204287.74371319998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="69">
         <v>8</v>
       </c>
@@ -3148,7 +3152,7 @@
         <v>142086.39528252004</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <v>9</v>
       </c>
@@ -3203,7 +3207,7 @@
         <v>154725.48507200001</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>10</v>
       </c>
@@ -3253,7 +3257,7 @@
         <v>640710.7332634721</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <v>11</v>
       </c>
@@ -3272,21 +3276,24 @@
       <c r="F21" s="63">
         <v>77903.289850000016</v>
       </c>
-      <c r="G21" s="66"/>
+      <c r="G21" s="66">
+        <f>F21</f>
+        <v>77903.289850000016</v>
+      </c>
       <c r="H21" s="65">
         <f t="shared" si="0"/>
-        <v>77903.289850000016</v>
+        <v>0</v>
       </c>
       <c r="I21" s="63">
         <v>0</v>
       </c>
       <c r="J21" s="64">
         <f t="shared" si="1"/>
-        <v>6855.4895068000023</v>
+        <v>0</v>
       </c>
       <c r="K21" s="62">
         <f t="shared" si="3"/>
-        <v>84758.77935680002</v>
+        <v>0</v>
       </c>
       <c r="L21" s="62">
         <f>Edesur!M20</f>
@@ -3302,10 +3309,10 @@
       </c>
       <c r="O21" s="62">
         <f t="shared" si="2"/>
-        <v>365319.43043380004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>280560.65107700002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="69">
         <v>12</v>
       </c>
@@ -3355,7 +3362,7 @@
         <v>338766.48852359212</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="69">
         <v>13</v>
       </c>
@@ -3401,11 +3408,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="62">
-        <f t="shared" si="2"/>
+        <f>K23+M23+N23+L23</f>
         <v>636850.88975723647</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="69">
         <v>14</v>
       </c>
@@ -3422,21 +3429,24 @@
       <c r="F24" s="63">
         <v>62021.070758000009</v>
       </c>
-      <c r="G24" s="66"/>
+      <c r="G24" s="66">
+        <f>F24</f>
+        <v>62021.070758000009</v>
+      </c>
       <c r="H24" s="65">
         <f t="shared" si="0"/>
-        <v>62021.070758000009</v>
+        <v>0</v>
       </c>
       <c r="I24" s="63">
         <v>0</v>
       </c>
       <c r="J24" s="64">
         <f t="shared" si="1"/>
-        <v>5457.8542267040011</v>
+        <v>0</v>
       </c>
       <c r="K24" s="62">
         <f t="shared" si="3"/>
-        <v>67478.924984704005</v>
+        <v>0</v>
       </c>
       <c r="L24" s="62">
         <f>Edesur!M23</f>
@@ -3452,10 +3462,10 @@
       </c>
       <c r="O24" s="62">
         <f t="shared" si="2"/>
-        <v>309247.26455826417</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>241768.33957356017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="69">
         <v>15</v>
       </c>
@@ -3509,7 +3519,7 @@
         <v>810388.55625719321</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="69">
         <v>16</v>
       </c>
@@ -3562,8 +3572,12 @@
         <f t="shared" si="2"/>
         <v>2258404.9749409957</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="74">
+        <f>L26+M26</f>
+        <v>323007.6005029201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="69">
         <v>17</v>
       </c>
@@ -3582,21 +3596,24 @@
       <c r="F27" s="63">
         <v>11862.404132000001</v>
       </c>
-      <c r="G27" s="66"/>
+      <c r="G27" s="66">
+        <f>F27</f>
+        <v>11862.404132000001</v>
+      </c>
       <c r="H27" s="65">
         <f t="shared" si="0"/>
-        <v>11862.404132000001</v>
+        <v>0</v>
       </c>
       <c r="I27" s="63">
         <v>0</v>
       </c>
       <c r="J27" s="64">
         <f t="shared" si="1"/>
-        <v>1043.8915636160002</v>
+        <v>0</v>
       </c>
       <c r="K27" s="62">
         <f t="shared" si="3"/>
-        <v>12906.295695616001</v>
+        <v>0</v>
       </c>
       <c r="L27" s="62">
         <f>Edesur!M26</f>
@@ -3612,10 +3629,10 @@
       </c>
       <c r="O27" s="62">
         <f t="shared" si="2"/>
-        <v>52769.012891856</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>39862.717196240003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="69">
         <v>18</v>
       </c>
@@ -3665,7 +3682,7 @@
         <v>313971.81388228718</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="69">
         <v>19</v>
       </c>
@@ -3715,7 +3732,7 @@
         <v>313971.81388228718</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="69">
         <v>20</v>
       </c>
@@ -3768,7 +3785,7 @@
         <v>39862.717196240003</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="69">
         <v>21</v>
       </c>
@@ -3818,7 +3835,7 @@
         <v>52769.012891856</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="69">
         <v>22</v>
       </c>
@@ -3973,11 +3990,11 @@
       </c>
     </row>
     <row r="35" spans="1:16" s="53" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="164" t="s">
+      <c r="A35" s="167" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="164"/>
-      <c r="C35" s="164"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="167"/>
       <c r="D35" s="61"/>
       <c r="E35" s="60">
         <f>SUM(E11:E34)</f>
@@ -3989,11 +4006,11 @@
       </c>
       <c r="G35" s="58">
         <f>SUM(G11:G34)</f>
-        <v>465293.924956</v>
+        <v>617080.68969600019</v>
       </c>
       <c r="H35" s="56">
         <f>SUM(H11:H34)</f>
-        <v>5492657.8162789503</v>
+        <v>5340871.0515389508</v>
       </c>
       <c r="I35" s="56">
         <f>SUM(I12:I34)</f>
@@ -4001,7 +4018,7 @@
       </c>
       <c r="J35" s="57">
         <f>SUM(J11:J34)</f>
-        <v>483353.88783254754</v>
+        <v>469996.65253542759</v>
       </c>
       <c r="K35" s="57"/>
       <c r="L35" s="57"/>
@@ -4015,7 +4032,7 @@
       </c>
       <c r="O35" s="54">
         <f>SUM(O11:O34)</f>
-        <v>9761188.2129488159</v>
+        <v>9596044.2129116952</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -4074,21 +4091,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="173" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="172"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="152"/>
       <c r="O1" s="98"/>
       <c r="P1" s="107"/>
@@ -5810,19 +5827,19 @@
       <c r="A35" s="102" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="173" t="s">
+      <c r="C35" s="176" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="171"/>
-      <c r="I35" s="171"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="171"/>
-      <c r="M35" s="171"/>
+      <c r="D35" s="174"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="174"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="174"/>
+      <c r="M35" s="174"/>
       <c r="N35" s="102"/>
       <c r="O35" s="98" t="e">
         <f>J35/C33*100</f>
@@ -5846,80 +5863,80 @@
       <c r="O37" s="98"/>
     </row>
     <row r="38" spans="1:22" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="174" t="s">
+      <c r="B38" s="177" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="175"/>
-      <c r="D38" s="175"/>
-      <c r="E38" s="175"/>
-      <c r="F38" s="175"/>
-      <c r="G38" s="175"/>
-      <c r="H38" s="175"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
-      <c r="K38" s="175"/>
-      <c r="L38" s="175"/>
-      <c r="M38" s="175"/>
+      <c r="C38" s="178"/>
+      <c r="D38" s="178"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="178"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178"/>
       <c r="O38" s="98"/>
     </row>
     <row r="39" spans="1:22" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="175"/>
-      <c r="C39" s="175"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="175"/>
-      <c r="F39" s="175"/>
-      <c r="G39" s="175"/>
-      <c r="H39" s="175"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="175"/>
-      <c r="L39" s="175"/>
-      <c r="M39" s="175"/>
+      <c r="B39" s="178"/>
+      <c r="C39" s="178"/>
+      <c r="D39" s="178"/>
+      <c r="E39" s="178"/>
+      <c r="F39" s="178"/>
+      <c r="G39" s="178"/>
+      <c r="H39" s="178"/>
+      <c r="I39" s="178"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="178"/>
+      <c r="L39" s="178"/>
+      <c r="M39" s="178"/>
       <c r="O39" s="98"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="175"/>
-      <c r="C40" s="175"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="175"/>
-      <c r="F40" s="175"/>
-      <c r="G40" s="175"/>
-      <c r="H40" s="175"/>
-      <c r="I40" s="175"/>
-      <c r="J40" s="175"/>
-      <c r="K40" s="175"/>
-      <c r="L40" s="175"/>
-      <c r="M40" s="175"/>
+      <c r="B40" s="178"/>
+      <c r="C40" s="178"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="178"/>
+      <c r="F40" s="178"/>
+      <c r="G40" s="178"/>
+      <c r="H40" s="178"/>
+      <c r="I40" s="178"/>
+      <c r="J40" s="178"/>
+      <c r="K40" s="178"/>
+      <c r="L40" s="178"/>
+      <c r="M40" s="178"/>
       <c r="O40" s="98"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="175"/>
-      <c r="C41" s="175"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="175"/>
-      <c r="F41" s="175"/>
-      <c r="G41" s="175"/>
-      <c r="H41" s="175"/>
-      <c r="I41" s="175"/>
-      <c r="J41" s="175"/>
-      <c r="K41" s="175"/>
-      <c r="L41" s="175"/>
-      <c r="M41" s="175"/>
+      <c r="B41" s="178"/>
+      <c r="C41" s="178"/>
+      <c r="D41" s="178"/>
+      <c r="E41" s="178"/>
+      <c r="F41" s="178"/>
+      <c r="G41" s="178"/>
+      <c r="H41" s="178"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="178"/>
+      <c r="M41" s="178"/>
       <c r="O41" s="98"/>
     </row>
     <row r="42" spans="1:22" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="175"/>
-      <c r="C42" s="175"/>
-      <c r="D42" s="175"/>
-      <c r="E42" s="175"/>
-      <c r="F42" s="175"/>
-      <c r="G42" s="175"/>
-      <c r="H42" s="175"/>
-      <c r="I42" s="175"/>
-      <c r="J42" s="175"/>
-      <c r="K42" s="175"/>
-      <c r="L42" s="175"/>
-      <c r="M42" s="175"/>
+      <c r="B42" s="178"/>
+      <c r="C42" s="178"/>
+      <c r="D42" s="178"/>
+      <c r="E42" s="178"/>
+      <c r="F42" s="178"/>
+      <c r="G42" s="178"/>
+      <c r="H42" s="178"/>
+      <c r="I42" s="178"/>
+      <c r="J42" s="178"/>
+      <c r="K42" s="178"/>
+      <c r="L42" s="178"/>
+      <c r="M42" s="178"/>
       <c r="O42" s="98"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
